--- a/windfield_datarecords.xlsx
+++ b/windfield_datarecords.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahyder/Desktop/windfieldproject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A601CB-EFC0-1C4B-B8E4-55C9F9FE6986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776C8916-52FB-5348-B930-070341BADDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14780" yWindow="4860" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{42A9C88B-2997-EB4C-AFF6-033636F0CE16}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{42A9C88B-2997-EB4C-AFF6-033636F0CE16}"/>
   </bookViews>
   <sheets>
     <sheet name="5µ" sheetId="1" r:id="rId1"/>
@@ -8472,6 +8472,9 @@
       <c r="B108" s="1" t="s">
         <v>1302</v>
       </c>
+      <c r="C108" s="18" t="s">
+        <v>714</v>
+      </c>
       <c r="D108" s="17">
         <v>5</v>
       </c>
@@ -8491,9 +8494,6 @@
       </c>
       <c r="B109" t="s">
         <v>1287</v>
-      </c>
-      <c r="C109" s="18" t="s">
-        <v>714</v>
       </c>
       <c r="D109" s="17">
         <v>5</v>

--- a/windfield_datarecords.xlsx
+++ b/windfield_datarecords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahyder/Desktop/windfieldproject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776C8916-52FB-5348-B930-070341BADDFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F168156A-E2FE-2644-9FC7-407AF8DF972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{42A9C88B-2997-EB4C-AFF6-033636F0CE16}"/>
   </bookViews>
@@ -2267,9 +2267,6 @@
     <t>case used for ZWP_in_time</t>
   </si>
   <si>
-    <t>useful but shape was 180</t>
-  </si>
-  <si>
     <t>/prvt/juno1/spex/2023dec28/images/5.10/jupiter/jc507541</t>
   </si>
   <si>
@@ -4039,6 +4036,9 @@
   </si>
   <si>
     <t>very good full corr</t>
+  </si>
+  <si>
+    <t>Used this in HST comparison</t>
   </si>
 </sst>
 </file>
@@ -6661,7 +6661,7 @@
     </row>
     <row r="3" spans="1:13" ht="34" x14ac:dyDescent="0.2">
       <c r="B3" s="30" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="C3" s="18" t="s">
         <v>715</v>
@@ -6688,7 +6688,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="D4" s="17">
         <v>5</v>
@@ -6714,7 +6714,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D5" s="17">
         <v>5</v>
@@ -6740,7 +6740,7 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D6" s="17">
         <v>5</v>
@@ -6766,7 +6766,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D7" s="17">
         <v>5</v>
@@ -6792,7 +6792,7 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D8" s="17">
         <v>5</v>
@@ -6818,7 +6818,7 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D9" s="17">
         <v>5</v>
@@ -6844,7 +6844,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D10" s="17">
         <v>5</v>
@@ -6870,7 +6870,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D11" s="17">
         <v>5</v>
@@ -6896,7 +6896,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D12" s="17">
         <v>5</v>
@@ -6922,7 +6922,7 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="D13" s="17">
         <v>5</v>
@@ -6945,7 +6945,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="C14" s="18" t="s">
         <v>714</v>
@@ -6960,7 +6960,7 @@
         <v>428</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="J14" s="17">
         <v>1.06</v>
@@ -6971,7 +6971,7 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B15" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F15" s="10"/>
     </row>
@@ -6998,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D19" s="17">
         <v>5</v>
@@ -7021,7 +7021,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D20" s="17">
         <v>5</v>
@@ -7044,7 +7044,7 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D21" s="17">
         <v>5</v>
@@ -7067,7 +7067,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D22" s="17">
         <v>5</v>
@@ -7090,7 +7090,7 @@
         <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D23" s="17">
         <v>5</v>
@@ -7113,7 +7113,7 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D24" s="17">
         <v>5</v>
@@ -7125,7 +7125,7 @@
         <v>667</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="J24" s="17">
         <v>0.74</v>
@@ -7139,10 +7139,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D25" s="17">
         <v>5</v>
@@ -7165,10 +7165,10 @@
         <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="D26" s="17">
         <v>5</v>
@@ -7191,7 +7191,7 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D27" s="17">
         <v>5</v>
@@ -7214,7 +7214,7 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D28" s="17">
         <v>5</v>
@@ -7237,7 +7237,7 @@
         <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C29" s="18" t="s">
         <v>714</v>
@@ -7260,7 +7260,7 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B30" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D34" s="17">
         <v>5</v>
@@ -7306,7 +7306,7 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D35" s="17">
         <v>5</v>
@@ -7323,7 +7323,7 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C36" s="18" t="s">
         <v>714</v>
@@ -7343,7 +7343,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D37" s="17">
         <v>5</v>
@@ -7360,7 +7360,7 @@
         <v>4</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="D38" s="17">
         <v>5</v>
@@ -7377,7 +7377,7 @@
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D39" s="17">
         <v>5</v>
@@ -7391,7 +7391,7 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B40" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D44" s="17">
         <v>5</v>
@@ -7427,7 +7427,7 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D45" s="17">
         <v>5</v>
@@ -7447,7 +7447,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D46" s="21">
         <v>4</v>
@@ -7467,7 +7467,7 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D47" s="17">
         <v>5</v>
@@ -7487,7 +7487,7 @@
         <v>4</v>
       </c>
       <c r="B48" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D48" s="17">
         <v>5</v>
@@ -7507,7 +7507,7 @@
         <v>5</v>
       </c>
       <c r="B49" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D49" s="17">
         <v>5</v>
@@ -7527,7 +7527,7 @@
         <v>6</v>
       </c>
       <c r="B50" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="D50" s="17">
         <v>5</v>
@@ -7547,7 +7547,7 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D51" s="17">
         <v>5</v>
@@ -7567,7 +7567,7 @@
         <v>8</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="D52" s="17">
         <v>5</v>
@@ -7587,7 +7587,7 @@
         <v>9</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D53" s="17">
         <v>5</v>
@@ -7607,7 +7607,7 @@
         <v>10</v>
       </c>
       <c r="B54" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D54" s="17">
         <v>5</v>
@@ -7627,7 +7627,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D55" s="17">
         <v>5</v>
@@ -7647,7 +7647,7 @@
         <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D56" s="21">
         <v>3</v>
@@ -7667,7 +7667,7 @@
         <v>13</v>
       </c>
       <c r="B57" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="D57" s="17">
         <v>5</v>
@@ -7687,7 +7687,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D58" s="21">
         <v>3</v>
@@ -7707,7 +7707,7 @@
         <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D59" s="21">
         <v>3</v>
@@ -7727,7 +7727,7 @@
         <v>16</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="C60" s="18" t="s">
         <v>714</v>
@@ -7747,7 +7747,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B61" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
@@ -7766,7 +7766,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D65" s="17">
         <v>5</v>
@@ -7786,7 +7786,7 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D66" s="17">
         <v>5</v>
@@ -7806,7 +7806,7 @@
         <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D67" s="17">
         <v>5</v>
@@ -7826,7 +7826,7 @@
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D68" s="17">
         <v>5</v>
@@ -7866,7 +7866,7 @@
         <v>5</v>
       </c>
       <c r="B70" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D70" s="17">
         <v>5</v>
@@ -7886,7 +7886,10 @@
         <v>6</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>1306</v>
       </c>
       <c r="D71" s="17">
         <v>5</v>
@@ -7906,10 +7909,7 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C72" s="18" t="s">
-        <v>716</v>
+        <v>1295</v>
       </c>
       <c r="D72" s="22">
         <v>5</v>
@@ -7932,7 +7932,7 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D73" s="22">
         <v>5</v>
@@ -7955,7 +7955,7 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C74" s="18" t="s">
         <v>714</v>
@@ -7981,7 +7981,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D75" s="17">
         <v>5</v>
@@ -8001,7 +8001,7 @@
         <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="D76" s="17">
         <v>5</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B77" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="F77" s="10"/>
       <c r="G77" s="10"/>
@@ -8181,7 +8181,7 @@
         <v>8</v>
       </c>
       <c r="B89" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D89" s="17">
         <v>5</v>
@@ -8215,7 +8215,7 @@
         <v>10</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="C91" s="18" t="s">
         <v>714</v>
@@ -8238,7 +8238,7 @@
         <v>11</v>
       </c>
       <c r="B92" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D92" s="17">
         <v>5</v>
@@ -8255,7 +8255,7 @@
         <v>12</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="D93" s="17">
         <v>5</v>
@@ -8289,7 +8289,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D95" s="17">
         <v>5</v>
@@ -8309,7 +8309,7 @@
         <v>15</v>
       </c>
       <c r="B96" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D96" s="17">
         <v>5</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B97" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -8342,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D101" s="17">
         <v>5</v>
@@ -8362,7 +8362,7 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D102" s="17">
         <v>5</v>
@@ -8382,7 +8382,7 @@
         <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D103" s="17">
         <v>5</v>
@@ -8402,7 +8402,7 @@
         <v>3</v>
       </c>
       <c r="B104" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D104" s="17">
         <v>5</v>
@@ -8419,7 +8419,7 @@
         <v>4</v>
       </c>
       <c r="B105" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D105" s="17">
         <v>5</v>
@@ -8436,7 +8436,7 @@
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D106" s="17">
         <v>5</v>
@@ -8453,7 +8453,7 @@
         <v>6</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D107" s="17">
         <v>5</v>
@@ -8470,7 +8470,7 @@
         <v>7</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="C108" s="18" t="s">
         <v>714</v>
@@ -8493,7 +8493,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D109" s="17">
         <v>5</v>
@@ -8513,7 +8513,7 @@
         <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="D110" s="17">
         <v>5</v>
@@ -8530,7 +8530,7 @@
         <v>10</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D111" s="17">
         <v>5</v>
@@ -8547,7 +8547,7 @@
         <v>11</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D112" s="17">
         <v>5</v>
@@ -8578,7 +8578,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B114" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
@@ -8594,7 +8594,7 @@
         <v>0</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="D118" s="17">
         <v>5</v>
@@ -8611,7 +8611,7 @@
         <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D119" s="17">
         <v>5</v>
@@ -8634,7 +8634,7 @@
         <v>2</v>
       </c>
       <c r="B120" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="C120" s="18" t="s">
         <v>714</v>
@@ -8657,7 +8657,7 @@
         <v>3</v>
       </c>
       <c r="B121" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D121" s="17">
         <v>5</v>
@@ -8674,7 +8674,7 @@
         <v>4</v>
       </c>
       <c r="B122" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D122" s="17">
         <v>5</v>
@@ -8691,7 +8691,7 @@
         <v>5</v>
       </c>
       <c r="B123" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D123" s="17">
         <v>5</v>
@@ -8708,7 +8708,7 @@
         <v>6</v>
       </c>
       <c r="B124" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D124" s="17">
         <v>5</v>
@@ -8725,7 +8725,7 @@
         <v>7</v>
       </c>
       <c r="B125" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D125" s="17">
         <v>5</v>
@@ -8742,7 +8742,7 @@
         <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D126" s="17">
         <v>5</v>
@@ -8762,7 +8762,7 @@
         <v>9</v>
       </c>
       <c r="B127" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D127" s="17">
         <v>5</v>
@@ -8816,7 +8816,7 @@
         <v>12</v>
       </c>
       <c r="B130" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D130" s="17">
         <v>5</v>
@@ -8833,7 +8833,7 @@
         <v>13</v>
       </c>
       <c r="B131" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D131" s="17">
         <v>5</v>
@@ -8850,7 +8850,7 @@
         <v>14</v>
       </c>
       <c r="B132" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D132" s="17">
         <v>5</v>
@@ -8870,7 +8870,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D133" s="17">
         <v>5</v>
@@ -8887,7 +8887,7 @@
         <v>16</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D134" s="17">
         <v>5</v>
@@ -8904,7 +8904,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B135" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
@@ -8926,7 +8926,7 @@
         <v>479</v>
       </c>
       <c r="C139" s="18" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D139" s="17">
         <v>5</v>
@@ -8952,7 +8952,7 @@
         <v>479</v>
       </c>
       <c r="C140" s="18" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D140" s="17">
         <v>5</v>
@@ -8975,7 +8975,7 @@
         <v>479</v>
       </c>
       <c r="C141" s="18" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="D141" s="17">
         <v>5</v>
@@ -8995,7 +8995,7 @@
         <v>3</v>
       </c>
       <c r="B142" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D142" s="17">
         <v>5</v>
@@ -9015,7 +9015,7 @@
         <v>4</v>
       </c>
       <c r="B143" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D143" s="17">
         <v>5</v>
@@ -9035,7 +9035,7 @@
         <v>5</v>
       </c>
       <c r="B144" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="D144" s="17">
         <v>5</v>
@@ -9055,7 +9055,7 @@
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D145" s="17">
         <v>5</v>
@@ -9075,10 +9075,10 @@
         <v>7</v>
       </c>
       <c r="B146" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="C146" s="18" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="D146" s="17">
         <v>5</v>
@@ -9098,7 +9098,7 @@
         <v>8</v>
       </c>
       <c r="B147" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="D147" s="17">
         <v>5</v>
@@ -9118,7 +9118,7 @@
         <v>9</v>
       </c>
       <c r="B148" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D148" s="17">
         <v>5</v>
@@ -9138,7 +9138,7 @@
         <v>10</v>
       </c>
       <c r="B149" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D149" s="17">
         <v>5</v>
@@ -9158,7 +9158,7 @@
         <v>11</v>
       </c>
       <c r="B150" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="D150" s="17">
         <v>5</v>
@@ -9341,12 +9341,12 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B159" s="10" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B160" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="162" spans="6:23" ht="187" x14ac:dyDescent="0.2">
@@ -9364,43 +9364,43 @@
         <v>436</v>
       </c>
       <c r="H168" s="18" t="s">
+        <v>1272</v>
+      </c>
+      <c r="I168" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="J168" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="K168" s="18" t="s">
+        <v>755</v>
+      </c>
+      <c r="L168" s="18" t="s">
+        <v>756</v>
+      </c>
+      <c r="M168" s="18" t="s">
+        <v>757</v>
+      </c>
+      <c r="N168" s="18" t="s">
+        <v>758</v>
+      </c>
+      <c r="R168" t="s">
         <v>1273</v>
       </c>
-      <c r="I168" s="1" t="s">
-        <v>1276</v>
-      </c>
-      <c r="J168" s="1" t="s">
-        <v>1277</v>
-      </c>
-      <c r="K168" s="18" t="s">
+      <c r="S168" t="s">
+        <v>1274</v>
+      </c>
+      <c r="T168" t="s">
+        <v>755</v>
+      </c>
+      <c r="U168" t="s">
         <v>756</v>
       </c>
-      <c r="L168" s="18" t="s">
+      <c r="V168" t="s">
         <v>757</v>
       </c>
-      <c r="M168" s="18" t="s">
+      <c r="W168" t="s">
         <v>758</v>
-      </c>
-      <c r="N168" s="18" t="s">
-        <v>759</v>
-      </c>
-      <c r="R168" t="s">
-        <v>1274</v>
-      </c>
-      <c r="S168" t="s">
-        <v>1275</v>
-      </c>
-      <c r="T168" t="s">
-        <v>756</v>
-      </c>
-      <c r="U168" t="s">
-        <v>757</v>
-      </c>
-      <c r="V168" t="s">
-        <v>758</v>
-      </c>
-      <c r="W168" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="169" spans="6:23" x14ac:dyDescent="0.2">
@@ -9414,37 +9414,37 @@
         <v>45619</v>
       </c>
       <c r="J169" s="17" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="K169" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="L169" s="17" t="s">
         <v>760</v>
-      </c>
-      <c r="L169" s="17" t="s">
-        <v>761</v>
       </c>
       <c r="M169" s="17">
         <v>1.1013264</v>
       </c>
       <c r="N169" s="17" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="R169" s="24">
         <v>45984</v>
       </c>
       <c r="S169" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="T169" t="s">
+        <v>759</v>
+      </c>
+      <c r="U169" t="s">
         <v>760</v>
-      </c>
-      <c r="U169" t="s">
-        <v>761</v>
       </c>
       <c r="V169">
         <v>1.1013264</v>
       </c>
       <c r="W169" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="170" spans="6:23" x14ac:dyDescent="0.2">
@@ -9458,37 +9458,37 @@
         <v>45619</v>
       </c>
       <c r="J170" s="17" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="K170" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="L170" s="17" t="s">
         <v>763</v>
-      </c>
-      <c r="L170" s="17" t="s">
-        <v>764</v>
       </c>
       <c r="M170" s="17">
         <v>1.0968245999999999</v>
       </c>
       <c r="N170" s="17" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="R170" s="24">
         <v>45984</v>
       </c>
       <c r="S170" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="T170" t="s">
+        <v>762</v>
+      </c>
+      <c r="U170" t="s">
         <v>763</v>
-      </c>
-      <c r="U170" t="s">
-        <v>764</v>
       </c>
       <c r="V170">
         <v>1.0968245999999999</v>
       </c>
       <c r="W170" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="171" spans="6:23" x14ac:dyDescent="0.2">
@@ -9502,37 +9502,37 @@
         <v>45619</v>
       </c>
       <c r="J171" s="17" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="K171" s="17" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="L171" s="17" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="M171" s="17">
         <v>1.0998911</v>
       </c>
       <c r="N171" s="17" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="R171" s="24">
         <v>45984</v>
       </c>
       <c r="S171" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="T171" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="U171" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="V171">
         <v>1.0998911</v>
       </c>
       <c r="W171" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="172" spans="6:23" x14ac:dyDescent="0.2">
@@ -9546,37 +9546,37 @@
         <v>45620</v>
       </c>
       <c r="J172" s="17" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="K172" s="17" t="s">
+        <v>767</v>
+      </c>
+      <c r="L172" s="17" t="s">
         <v>768</v>
-      </c>
-      <c r="L172" s="17" t="s">
-        <v>769</v>
       </c>
       <c r="M172" s="17">
         <v>1.7573915</v>
       </c>
       <c r="N172" s="17" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="R172" s="24">
         <v>45985</v>
       </c>
       <c r="S172" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="T172" t="s">
+        <v>767</v>
+      </c>
+      <c r="U172" t="s">
         <v>768</v>
-      </c>
-      <c r="U172" t="s">
-        <v>769</v>
       </c>
       <c r="V172">
         <v>1.7573915</v>
       </c>
       <c r="W172" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="173" spans="6:23" x14ac:dyDescent="0.2">
@@ -9590,37 +9590,37 @@
         <v>45620</v>
       </c>
       <c r="J173" s="17" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="K173" s="17" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L173" s="17" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="M173" s="17">
         <v>1.7299635</v>
       </c>
       <c r="N173" s="17" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="R173" s="24">
         <v>45985</v>
       </c>
       <c r="S173" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="T173" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="U173" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="V173">
         <v>1.7299635</v>
       </c>
       <c r="W173" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="174" spans="6:23" x14ac:dyDescent="0.2">
@@ -9634,37 +9634,37 @@
         <v>45619</v>
       </c>
       <c r="J174" s="17" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="K174" s="17" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L174" s="17" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="M174" s="17">
         <v>1.0986370000000001</v>
       </c>
       <c r="N174" s="17" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="R174" s="24">
         <v>45984</v>
       </c>
       <c r="S174" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="T174" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="U174" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="V174">
         <v>1.0986370000000001</v>
       </c>
       <c r="W174" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="175" spans="6:23" x14ac:dyDescent="0.2">
@@ -9678,37 +9678,37 @@
         <v>45587</v>
       </c>
       <c r="J175" s="17" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="K175" s="17" t="s">
+        <v>774</v>
+      </c>
+      <c r="L175" s="17" t="s">
         <v>775</v>
-      </c>
-      <c r="L175" s="17" t="s">
-        <v>776</v>
       </c>
       <c r="M175" s="17">
         <v>1.004407</v>
       </c>
       <c r="N175" s="17" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="R175" s="24">
         <v>45952</v>
       </c>
       <c r="S175" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="T175" t="s">
+        <v>774</v>
+      </c>
+      <c r="U175" t="s">
         <v>775</v>
-      </c>
-      <c r="U175" t="s">
-        <v>776</v>
       </c>
       <c r="V175">
         <v>1.004407</v>
       </c>
       <c r="W175" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="176" spans="6:23" x14ac:dyDescent="0.2">
@@ -9722,37 +9722,37 @@
         <v>45588</v>
       </c>
       <c r="J176" s="17" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="K176" s="17" t="s">
+        <v>777</v>
+      </c>
+      <c r="L176" s="17" t="s">
         <v>778</v>
-      </c>
-      <c r="L176" s="17" t="s">
-        <v>779</v>
       </c>
       <c r="M176" s="17">
         <v>1.0823919</v>
       </c>
       <c r="N176" s="17" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="R176" s="24">
         <v>45953</v>
       </c>
       <c r="S176" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="T176" t="s">
+        <v>777</v>
+      </c>
+      <c r="U176" t="s">
         <v>778</v>
-      </c>
-      <c r="U176" t="s">
-        <v>779</v>
       </c>
       <c r="V176">
         <v>1.0823919</v>
       </c>
       <c r="W176" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="177" spans="6:23" x14ac:dyDescent="0.2">
@@ -9766,37 +9766,37 @@
         <v>45587</v>
       </c>
       <c r="J177" s="17" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="K177" s="17" t="s">
+        <v>780</v>
+      </c>
+      <c r="L177" s="17" t="s">
         <v>781</v>
-      </c>
-      <c r="L177" s="17" t="s">
-        <v>782</v>
       </c>
       <c r="M177" s="17">
         <v>1.4519206</v>
       </c>
       <c r="N177" s="17" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="R177" s="24">
         <v>45952</v>
       </c>
       <c r="S177" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="T177" t="s">
+        <v>780</v>
+      </c>
+      <c r="U177" t="s">
         <v>781</v>
-      </c>
-      <c r="U177" t="s">
-        <v>782</v>
       </c>
       <c r="V177">
         <v>1.4519206</v>
       </c>
       <c r="W177" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="178" spans="6:23" x14ac:dyDescent="0.2">
@@ -9807,37 +9807,37 @@
         <v>45588</v>
       </c>
       <c r="J178" s="17" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="K178" s="17" t="s">
+        <v>783</v>
+      </c>
+      <c r="L178" s="17" t="s">
         <v>784</v>
-      </c>
-      <c r="L178" s="17" t="s">
-        <v>785</v>
       </c>
       <c r="M178" s="17">
         <v>1.3307070999999999</v>
       </c>
       <c r="N178" s="17" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="R178" s="24">
         <v>45953</v>
       </c>
       <c r="S178" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="T178" t="s">
+        <v>783</v>
+      </c>
+      <c r="U178" t="s">
         <v>784</v>
-      </c>
-      <c r="U178" t="s">
-        <v>785</v>
       </c>
       <c r="V178">
         <v>1.3307070999999999</v>
       </c>
       <c r="W178" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="179" spans="6:23" x14ac:dyDescent="0.2">
@@ -9848,37 +9848,37 @@
         <v>45587</v>
       </c>
       <c r="J179" s="17" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="K179" s="17" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="L179" s="17" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M179" s="17">
         <v>1.0083826</v>
       </c>
       <c r="N179" s="17" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="R179" s="24">
         <v>45952</v>
       </c>
       <c r="S179" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="T179" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="U179" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="V179">
         <v>1.0083826</v>
       </c>
       <c r="W179" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="180" spans="6:23" x14ac:dyDescent="0.2">
@@ -9892,37 +9892,37 @@
         <v>45520</v>
       </c>
       <c r="J180" s="17" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="K180" s="17" t="s">
+        <v>788</v>
+      </c>
+      <c r="L180" s="17" t="s">
         <v>789</v>
-      </c>
-      <c r="L180" s="17" t="s">
-        <v>790</v>
       </c>
       <c r="M180" s="17">
         <v>1.0322026</v>
       </c>
       <c r="N180" s="17" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="R180" s="24">
         <v>45885</v>
       </c>
       <c r="S180" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="T180" t="s">
+        <v>788</v>
+      </c>
+      <c r="U180" t="s">
         <v>789</v>
-      </c>
-      <c r="U180" t="s">
-        <v>790</v>
       </c>
       <c r="V180">
         <v>1.0322026</v>
       </c>
       <c r="W180" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="181" spans="6:23" x14ac:dyDescent="0.2">
@@ -9936,37 +9936,37 @@
         <v>45520</v>
       </c>
       <c r="J181" s="17" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="K181" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="L181" s="17" t="s">
         <v>792</v>
-      </c>
-      <c r="L181" s="17" t="s">
-        <v>793</v>
       </c>
       <c r="M181" s="17">
         <v>1.1615051000000001</v>
       </c>
       <c r="N181" s="17" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="R181" s="24">
         <v>45885</v>
       </c>
       <c r="S181" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="T181" t="s">
+        <v>791</v>
+      </c>
+      <c r="U181" t="s">
         <v>792</v>
-      </c>
-      <c r="U181" t="s">
-        <v>793</v>
       </c>
       <c r="V181">
         <v>1.1615051000000001</v>
       </c>
       <c r="W181" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="182" spans="6:23" x14ac:dyDescent="0.2">
@@ -9980,37 +9980,37 @@
         <v>45520</v>
       </c>
       <c r="J182" s="17" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="K182" s="17" t="s">
+        <v>794</v>
+      </c>
+      <c r="L182" s="17" t="s">
         <v>795</v>
-      </c>
-      <c r="L182" s="17" t="s">
-        <v>796</v>
       </c>
       <c r="M182" s="17">
         <v>1.0105976000000001</v>
       </c>
       <c r="N182" s="17" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="R182" s="24">
         <v>45885</v>
       </c>
       <c r="S182" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="T182" t="s">
+        <v>794</v>
+      </c>
+      <c r="U182" t="s">
         <v>795</v>
-      </c>
-      <c r="U182" t="s">
-        <v>796</v>
       </c>
       <c r="V182">
         <v>1.0105976000000001</v>
       </c>
       <c r="W182" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="183" spans="6:23" x14ac:dyDescent="0.2">
@@ -10024,37 +10024,37 @@
         <v>45521</v>
       </c>
       <c r="J183" s="17" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="K183" s="17" t="s">
+        <v>797</v>
+      </c>
+      <c r="L183" s="17" t="s">
         <v>798</v>
-      </c>
-      <c r="L183" s="17" t="s">
-        <v>799</v>
       </c>
       <c r="M183" s="17">
         <v>1.2049342999999999</v>
       </c>
       <c r="N183" s="17" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="R183" s="24">
         <v>45886</v>
       </c>
       <c r="S183" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="T183" t="s">
+        <v>797</v>
+      </c>
+      <c r="U183" t="s">
         <v>798</v>
-      </c>
-      <c r="U183" t="s">
-        <v>799</v>
       </c>
       <c r="V183">
         <v>1.2049342999999999</v>
       </c>
       <c r="W183" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="184" spans="6:23" x14ac:dyDescent="0.2">
@@ -10068,37 +10068,37 @@
         <v>45521</v>
       </c>
       <c r="J184" s="17" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="K184" s="17" t="s">
+        <v>800</v>
+      </c>
+      <c r="L184" s="17" t="s">
         <v>801</v>
-      </c>
-      <c r="L184" s="17" t="s">
-        <v>802</v>
       </c>
       <c r="M184" s="17">
         <v>1.078786</v>
       </c>
       <c r="N184" s="17" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="R184" s="24">
         <v>45886</v>
       </c>
       <c r="S184" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="T184" t="s">
+        <v>800</v>
+      </c>
+      <c r="U184" t="s">
         <v>801</v>
-      </c>
-      <c r="U184" t="s">
-        <v>802</v>
       </c>
       <c r="V184">
         <v>1.078786</v>
       </c>
       <c r="W184" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="185" spans="6:23" x14ac:dyDescent="0.2">
@@ -10112,37 +10112,37 @@
         <v>45521</v>
       </c>
       <c r="J185" s="17" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="K185" s="17" t="s">
+        <v>803</v>
+      </c>
+      <c r="L185" s="17" t="s">
         <v>804</v>
-      </c>
-      <c r="L185" s="17" t="s">
-        <v>805</v>
       </c>
       <c r="M185" s="17">
         <v>1.3062362999999999</v>
       </c>
       <c r="N185" s="17" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="R185" s="24">
         <v>45886</v>
       </c>
       <c r="S185" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="T185" t="s">
+        <v>803</v>
+      </c>
+      <c r="U185" t="s">
         <v>804</v>
-      </c>
-      <c r="U185" t="s">
-        <v>805</v>
       </c>
       <c r="V185">
         <v>1.3062362999999999</v>
       </c>
       <c r="W185" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="186" spans="6:23" x14ac:dyDescent="0.2">
@@ -10156,37 +10156,37 @@
         <v>45520</v>
       </c>
       <c r="J186" s="17" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="K186" s="17" t="s">
+        <v>791</v>
+      </c>
+      <c r="L186" s="17" t="s">
         <v>792</v>
-      </c>
-      <c r="L186" s="17" t="s">
-        <v>793</v>
       </c>
       <c r="M186" s="17">
         <v>1.1622017</v>
       </c>
       <c r="N186" s="17" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="R186" s="24">
         <v>45885</v>
       </c>
       <c r="S186" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="T186" t="s">
+        <v>791</v>
+      </c>
+      <c r="U186" t="s">
         <v>792</v>
-      </c>
-      <c r="U186" t="s">
-        <v>793</v>
       </c>
       <c r="V186">
         <v>1.1622017</v>
       </c>
       <c r="W186" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="187" spans="6:23" x14ac:dyDescent="0.2">
@@ -10200,37 +10200,37 @@
         <v>45214</v>
       </c>
       <c r="J187" s="17" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="K187" s="17" t="s">
+        <v>807</v>
+      </c>
+      <c r="L187" s="17" t="s">
         <v>808</v>
-      </c>
-      <c r="L187" s="17" t="s">
-        <v>809</v>
       </c>
       <c r="M187" s="17">
         <v>1.0239123000000001</v>
       </c>
       <c r="N187" s="17" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="R187" s="24">
         <v>45945</v>
       </c>
       <c r="S187" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="T187" t="s">
+        <v>807</v>
+      </c>
+      <c r="U187" t="s">
         <v>808</v>
-      </c>
-      <c r="U187" t="s">
-        <v>809</v>
       </c>
       <c r="V187">
         <v>1.0239123000000001</v>
       </c>
       <c r="W187" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="188" spans="6:23" x14ac:dyDescent="0.2">
@@ -10244,37 +10244,37 @@
         <v>45213</v>
       </c>
       <c r="J188" s="17" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="K188" s="17" t="s">
+        <v>810</v>
+      </c>
+      <c r="L188" s="17" t="s">
         <v>811</v>
-      </c>
-      <c r="L188" s="17" t="s">
-        <v>812</v>
       </c>
       <c r="M188" s="17">
         <v>1.4935601999999999</v>
       </c>
       <c r="N188" s="17" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="R188" s="24">
         <v>45944</v>
       </c>
       <c r="S188" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="T188" t="s">
+        <v>810</v>
+      </c>
+      <c r="U188" t="s">
         <v>811</v>
-      </c>
-      <c r="U188" t="s">
-        <v>812</v>
       </c>
       <c r="V188">
         <v>1.4935601999999999</v>
       </c>
       <c r="W188" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="189" spans="6:23" x14ac:dyDescent="0.2">
@@ -10288,37 +10288,37 @@
         <v>45253</v>
       </c>
       <c r="J189" s="17" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="K189" s="17" t="s">
+        <v>813</v>
+      </c>
+      <c r="L189" s="17" t="s">
         <v>814</v>
-      </c>
-      <c r="L189" s="17" t="s">
-        <v>815</v>
       </c>
       <c r="M189" s="17">
         <v>1.0354473</v>
       </c>
       <c r="N189" s="17" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="R189" s="24">
         <v>45984</v>
       </c>
       <c r="S189" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="T189" t="s">
+        <v>813</v>
+      </c>
+      <c r="U189" t="s">
         <v>814</v>
-      </c>
-      <c r="U189" t="s">
-        <v>815</v>
       </c>
       <c r="V189">
         <v>1.0354473</v>
       </c>
       <c r="W189" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="190" spans="6:23" x14ac:dyDescent="0.2">
@@ -10332,37 +10332,37 @@
         <v>45254</v>
       </c>
       <c r="J190" s="17" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="K190" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="L190" s="17" t="s">
         <v>817</v>
-      </c>
-      <c r="L190" s="17" t="s">
-        <v>818</v>
       </c>
       <c r="M190" s="17">
         <v>1.3698440000000001</v>
       </c>
       <c r="N190" s="17" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="R190" s="24">
         <v>45985</v>
       </c>
       <c r="S190" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="T190" t="s">
+        <v>816</v>
+      </c>
+      <c r="U190" t="s">
         <v>817</v>
-      </c>
-      <c r="U190" t="s">
-        <v>818</v>
       </c>
       <c r="V190">
         <v>1.3698440000000001</v>
       </c>
       <c r="W190" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="191" spans="6:23" x14ac:dyDescent="0.2">
@@ -10376,37 +10376,37 @@
         <v>45253</v>
       </c>
       <c r="J191" s="17" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="K191" s="17" t="s">
+        <v>819</v>
+      </c>
+      <c r="L191" s="17" t="s">
         <v>820</v>
-      </c>
-      <c r="L191" s="17" t="s">
-        <v>821</v>
       </c>
       <c r="M191" s="17">
         <v>1.1126522999999999</v>
       </c>
       <c r="N191" s="17" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="R191" s="24">
         <v>45984</v>
       </c>
       <c r="S191" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="T191" t="s">
+        <v>819</v>
+      </c>
+      <c r="U191" t="s">
         <v>820</v>
-      </c>
-      <c r="U191" t="s">
-        <v>821</v>
       </c>
       <c r="V191">
         <v>1.1126522999999999</v>
       </c>
       <c r="W191" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="192" spans="6:23" x14ac:dyDescent="0.2">
@@ -10420,37 +10420,37 @@
         <v>45062</v>
       </c>
       <c r="J192" s="17" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="K192" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="L192" s="17" t="s">
         <v>823</v>
-      </c>
-      <c r="L192" s="17" t="s">
-        <v>824</v>
       </c>
       <c r="M192" s="17">
         <v>1.0252433999999999</v>
       </c>
       <c r="N192" s="17" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="R192" s="24">
         <v>45793</v>
       </c>
       <c r="S192" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="T192" t="s">
+        <v>822</v>
+      </c>
+      <c r="U192" t="s">
         <v>823</v>
-      </c>
-      <c r="U192" t="s">
-        <v>824</v>
       </c>
       <c r="V192">
         <v>1.0252433999999999</v>
       </c>
       <c r="W192" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="193" spans="6:23" x14ac:dyDescent="0.2">
@@ -10461,37 +10461,37 @@
         <v>45063</v>
       </c>
       <c r="J193" s="17" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="K193" s="17" t="s">
+        <v>825</v>
+      </c>
+      <c r="L193" s="17" t="s">
         <v>826</v>
-      </c>
-      <c r="L193" s="17" t="s">
-        <v>827</v>
       </c>
       <c r="M193" s="17">
         <v>1.1717900000000001</v>
       </c>
       <c r="N193" s="17" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="R193" s="24">
         <v>45794</v>
       </c>
       <c r="S193" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="T193" t="s">
+        <v>825</v>
+      </c>
+      <c r="U193" t="s">
         <v>826</v>
-      </c>
-      <c r="U193" t="s">
-        <v>827</v>
       </c>
       <c r="V193">
         <v>1.1717900000000001</v>
       </c>
       <c r="W193" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="194" spans="6:23" x14ac:dyDescent="0.2">
@@ -10502,37 +10502,37 @@
         <v>45063</v>
       </c>
       <c r="J194" s="17" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="K194" s="17" t="s">
+        <v>828</v>
+      </c>
+      <c r="L194" s="17" t="s">
         <v>829</v>
-      </c>
-      <c r="L194" s="17" t="s">
-        <v>830</v>
       </c>
       <c r="M194" s="17">
         <v>1.100063</v>
       </c>
       <c r="N194" s="17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="R194" s="24">
         <v>45794</v>
       </c>
       <c r="S194" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="T194" t="s">
+        <v>828</v>
+      </c>
+      <c r="U194" t="s">
         <v>829</v>
-      </c>
-      <c r="U194" t="s">
-        <v>830</v>
       </c>
       <c r="V194">
         <v>1.100063</v>
       </c>
       <c r="W194" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="195" spans="6:23" x14ac:dyDescent="0.2">
@@ -10546,37 +10546,37 @@
         <v>45063</v>
       </c>
       <c r="J195" s="17" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="K195" s="17" t="s">
+        <v>831</v>
+      </c>
+      <c r="L195" s="17" t="s">
         <v>832</v>
-      </c>
-      <c r="L195" s="17" t="s">
-        <v>833</v>
       </c>
       <c r="M195" s="17">
         <v>1.202771</v>
       </c>
       <c r="N195" s="17" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="R195" s="24">
         <v>45794</v>
       </c>
       <c r="S195" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="T195" t="s">
+        <v>831</v>
+      </c>
+      <c r="U195" t="s">
         <v>832</v>
-      </c>
-      <c r="U195" t="s">
-        <v>833</v>
       </c>
       <c r="V195">
         <v>1.202771</v>
       </c>
       <c r="W195" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="196" spans="6:23" x14ac:dyDescent="0.2">
@@ -10590,37 +10590,37 @@
         <v>45063</v>
       </c>
       <c r="J196" s="17" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="K196" s="17" t="s">
+        <v>834</v>
+      </c>
+      <c r="L196" s="17" t="s">
         <v>835</v>
-      </c>
-      <c r="L196" s="17" t="s">
-        <v>836</v>
       </c>
       <c r="M196" s="17">
         <v>1.1510309999999999</v>
       </c>
       <c r="N196" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="R196" s="24">
         <v>45794</v>
       </c>
       <c r="S196" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="T196" t="s">
+        <v>834</v>
+      </c>
+      <c r="U196" t="s">
         <v>835</v>
-      </c>
-      <c r="U196" t="s">
-        <v>836</v>
       </c>
       <c r="V196">
         <v>1.1510309999999999</v>
       </c>
       <c r="W196" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="197" spans="6:23" x14ac:dyDescent="0.2">
@@ -10634,37 +10634,37 @@
         <v>45063</v>
       </c>
       <c r="J197" s="17" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="K197" s="17" t="s">
+        <v>837</v>
+      </c>
+      <c r="L197" s="17" t="s">
         <v>838</v>
-      </c>
-      <c r="L197" s="17" t="s">
-        <v>839</v>
       </c>
       <c r="M197" s="17">
         <v>1.2205336</v>
       </c>
       <c r="N197" s="17" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="R197" s="24">
         <v>45794</v>
       </c>
       <c r="S197" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="T197" t="s">
+        <v>837</v>
+      </c>
+      <c r="U197" t="s">
         <v>838</v>
-      </c>
-      <c r="U197" t="s">
-        <v>839</v>
       </c>
       <c r="V197">
         <v>1.2205336</v>
       </c>
       <c r="W197" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="198" spans="6:23" x14ac:dyDescent="0.2">
@@ -10678,37 +10678,37 @@
         <v>45062</v>
       </c>
       <c r="J198" s="17" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="K198" s="17" t="s">
+        <v>840</v>
+      </c>
+      <c r="L198" s="17" t="s">
         <v>841</v>
-      </c>
-      <c r="L198" s="17" t="s">
-        <v>842</v>
       </c>
       <c r="M198" s="17">
         <v>1.646409</v>
       </c>
       <c r="N198" s="17" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="R198" s="24">
         <v>45793</v>
       </c>
       <c r="S198" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="T198" t="s">
+        <v>840</v>
+      </c>
+      <c r="U198" t="s">
         <v>841</v>
-      </c>
-      <c r="U198" t="s">
-        <v>842</v>
       </c>
       <c r="V198">
         <v>1.646409</v>
       </c>
       <c r="W198" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="199" spans="6:23" x14ac:dyDescent="0.2">
@@ -10722,37 +10722,37 @@
         <v>45063</v>
       </c>
       <c r="J199" s="17" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="K199" s="17" t="s">
+        <v>843</v>
+      </c>
+      <c r="L199" s="17" t="s">
         <v>844</v>
-      </c>
-      <c r="L199" s="17" t="s">
-        <v>845</v>
       </c>
       <c r="M199" s="17">
         <v>1.2806987000000001</v>
       </c>
       <c r="N199" s="17" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="R199" s="24">
         <v>45794</v>
       </c>
       <c r="S199" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="T199" t="s">
+        <v>843</v>
+      </c>
+      <c r="U199" t="s">
         <v>844</v>
-      </c>
-      <c r="U199" t="s">
-        <v>845</v>
       </c>
       <c r="V199">
         <v>1.2806987000000001</v>
       </c>
       <c r="W199" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="200" spans="6:23" x14ac:dyDescent="0.2">
@@ -10766,37 +10766,37 @@
         <v>45063</v>
       </c>
       <c r="J200" s="17" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="K200" s="17" t="s">
+        <v>846</v>
+      </c>
+      <c r="L200" s="17" t="s">
         <v>847</v>
-      </c>
-      <c r="L200" s="17" t="s">
-        <v>848</v>
       </c>
       <c r="M200" s="17">
         <v>1.4454194</v>
       </c>
       <c r="N200" s="17" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="R200" s="24">
         <v>45794</v>
       </c>
       <c r="S200" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="T200" t="s">
+        <v>846</v>
+      </c>
+      <c r="U200" t="s">
         <v>847</v>
-      </c>
-      <c r="U200" t="s">
-        <v>848</v>
       </c>
       <c r="V200">
         <v>1.4454194</v>
       </c>
       <c r="W200" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="201" spans="6:23" x14ac:dyDescent="0.2">
@@ -10807,37 +10807,37 @@
         <v>45063</v>
       </c>
       <c r="J201" s="17" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="K201" s="17" t="s">
+        <v>849</v>
+      </c>
+      <c r="L201" s="17" t="s">
         <v>850</v>
-      </c>
-      <c r="L201" s="17" t="s">
-        <v>851</v>
       </c>
       <c r="M201" s="17">
         <v>1.4898098</v>
       </c>
       <c r="N201" s="17" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="R201" s="24">
         <v>45794</v>
       </c>
       <c r="S201" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="T201" t="s">
+        <v>849</v>
+      </c>
+      <c r="U201" t="s">
         <v>850</v>
-      </c>
-      <c r="U201" t="s">
-        <v>851</v>
       </c>
       <c r="V201">
         <v>1.4898098</v>
       </c>
       <c r="W201" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="202" spans="6:23" x14ac:dyDescent="0.2">
@@ -10851,37 +10851,37 @@
         <v>45062</v>
       </c>
       <c r="J202" s="17" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="K202" s="17" t="s">
+        <v>822</v>
+      </c>
+      <c r="L202" s="17" t="s">
         <v>823</v>
-      </c>
-      <c r="L202" s="17" t="s">
-        <v>824</v>
       </c>
       <c r="M202" s="17">
         <v>1.0252433999999999</v>
       </c>
       <c r="N202" s="17" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="R202" s="24">
         <v>45793</v>
       </c>
       <c r="S202" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="T202" t="s">
+        <v>822</v>
+      </c>
+      <c r="U202" t="s">
         <v>823</v>
-      </c>
-      <c r="U202" t="s">
-        <v>824</v>
       </c>
       <c r="V202">
         <v>1.0252433999999999</v>
       </c>
       <c r="W202" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="203" spans="6:23" x14ac:dyDescent="0.2">
@@ -10895,37 +10895,37 @@
         <v>45100</v>
       </c>
       <c r="J203" s="17" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="K203" s="17" t="s">
+        <v>853</v>
+      </c>
+      <c r="L203" s="17" t="s">
         <v>854</v>
-      </c>
-      <c r="L203" s="17" t="s">
-        <v>855</v>
       </c>
       <c r="M203" s="17">
         <v>1.2452220000000001</v>
       </c>
       <c r="N203" s="17" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="R203" s="24">
         <v>45831</v>
       </c>
       <c r="S203" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="T203" t="s">
+        <v>853</v>
+      </c>
+      <c r="U203" t="s">
         <v>854</v>
-      </c>
-      <c r="U203" t="s">
-        <v>855</v>
       </c>
       <c r="V203">
         <v>1.2452220000000001</v>
       </c>
       <c r="W203" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="204" spans="6:23" x14ac:dyDescent="0.2">
@@ -10939,37 +10939,37 @@
         <v>45101</v>
       </c>
       <c r="J204" s="17" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="K204" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="L204" s="17" t="s">
         <v>857</v>
-      </c>
-      <c r="L204" s="17" t="s">
-        <v>858</v>
       </c>
       <c r="M204" s="17">
         <v>1.2380841</v>
       </c>
       <c r="N204" s="17" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="R204" s="24">
         <v>45832</v>
       </c>
       <c r="S204" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="T204" t="s">
+        <v>856</v>
+      </c>
+      <c r="U204" t="s">
         <v>857</v>
-      </c>
-      <c r="U204" t="s">
-        <v>858</v>
       </c>
       <c r="V204">
         <v>1.2380841</v>
       </c>
       <c r="W204" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="205" spans="6:23" x14ac:dyDescent="0.2">
@@ -10983,37 +10983,37 @@
         <v>45100</v>
       </c>
       <c r="J205" s="17" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="K205" s="17" t="s">
+        <v>859</v>
+      </c>
+      <c r="L205" s="17" t="s">
         <v>860</v>
-      </c>
-      <c r="L205" s="17" t="s">
-        <v>861</v>
       </c>
       <c r="M205" s="17">
         <v>1.2735544999999999</v>
       </c>
       <c r="N205" s="17" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="R205" s="24">
         <v>45831</v>
       </c>
       <c r="S205" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="T205" t="s">
+        <v>859</v>
+      </c>
+      <c r="U205" t="s">
         <v>860</v>
-      </c>
-      <c r="U205" t="s">
-        <v>861</v>
       </c>
       <c r="V205">
         <v>1.2735544999999999</v>
       </c>
       <c r="W205" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="206" spans="6:23" x14ac:dyDescent="0.2">
@@ -11027,37 +11027,37 @@
         <v>45289</v>
       </c>
       <c r="J206" s="17" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="K206" s="17" t="s">
+        <v>862</v>
+      </c>
+      <c r="L206" s="17" t="s">
         <v>863</v>
-      </c>
-      <c r="L206" s="17" t="s">
-        <v>864</v>
       </c>
       <c r="M206" s="17">
         <v>1.1644471999999999</v>
       </c>
       <c r="N206" s="17" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="R206" s="24">
         <v>46020</v>
       </c>
       <c r="S206" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="T206" t="s">
+        <v>862</v>
+      </c>
+      <c r="U206" t="s">
         <v>863</v>
-      </c>
-      <c r="U206" t="s">
-        <v>864</v>
       </c>
       <c r="V206">
         <v>1.1644471999999999</v>
       </c>
       <c r="W206" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="207" spans="6:23" x14ac:dyDescent="0.2">
@@ -11071,37 +11071,37 @@
         <v>45288</v>
       </c>
       <c r="J207" s="17" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="K207" s="17" t="s">
+        <v>865</v>
+      </c>
+      <c r="L207" s="17" t="s">
         <v>866</v>
-      </c>
-      <c r="L207" s="17" t="s">
-        <v>867</v>
       </c>
       <c r="M207" s="17">
         <v>1.2263607999999999</v>
       </c>
       <c r="N207" s="17" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="R207" s="24">
         <v>46019</v>
       </c>
       <c r="S207" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="T207" t="s">
+        <v>865</v>
+      </c>
+      <c r="U207" t="s">
         <v>866</v>
-      </c>
-      <c r="U207" t="s">
-        <v>867</v>
       </c>
       <c r="V207">
         <v>1.2263607999999999</v>
       </c>
       <c r="W207" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="208" spans="6:23" x14ac:dyDescent="0.2">
@@ -11115,37 +11115,37 @@
         <v>44703</v>
       </c>
       <c r="J208" s="17" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="K208" s="17" t="s">
+        <v>868</v>
+      </c>
+      <c r="L208" s="17" t="s">
         <v>869</v>
-      </c>
-      <c r="L208" s="17" t="s">
-        <v>870</v>
       </c>
       <c r="M208" s="17">
         <v>1.1898799</v>
       </c>
       <c r="N208" s="17" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="R208" s="24">
         <v>45799</v>
       </c>
       <c r="S208" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="T208" t="s">
+        <v>868</v>
+      </c>
+      <c r="U208" t="s">
         <v>869</v>
-      </c>
-      <c r="U208" t="s">
-        <v>870</v>
       </c>
       <c r="V208">
         <v>1.1898799</v>
       </c>
       <c r="W208" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="209" spans="6:23" x14ac:dyDescent="0.2">
@@ -11159,37 +11159,37 @@
         <v>44702</v>
       </c>
       <c r="J209" s="17" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="K209" s="17" t="s">
+        <v>871</v>
+      </c>
+      <c r="L209" s="17" t="s">
         <v>872</v>
-      </c>
-      <c r="L209" s="17" t="s">
-        <v>873</v>
       </c>
       <c r="M209" s="17">
         <v>1.1728333</v>
       </c>
       <c r="N209" s="17" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="R209" s="24">
         <v>45798</v>
       </c>
       <c r="S209" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="T209" t="s">
+        <v>871</v>
+      </c>
+      <c r="U209" t="s">
         <v>872</v>
-      </c>
-      <c r="U209" t="s">
-        <v>873</v>
       </c>
       <c r="V209">
         <v>1.1728333</v>
       </c>
       <c r="W209" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="210" spans="6:23" x14ac:dyDescent="0.2">
@@ -11203,37 +11203,37 @@
         <v>44751</v>
       </c>
       <c r="J210" s="17" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="K210" s="17" t="s">
+        <v>874</v>
+      </c>
+      <c r="L210" s="17" t="s">
         <v>875</v>
-      </c>
-      <c r="L210" s="17" t="s">
-        <v>876</v>
       </c>
       <c r="M210" s="17">
         <v>1.2536700999999999</v>
       </c>
       <c r="N210" s="17" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="R210" s="24">
         <v>45847</v>
       </c>
       <c r="S210" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="T210" t="s">
+        <v>874</v>
+      </c>
+      <c r="U210" t="s">
         <v>875</v>
-      </c>
-      <c r="U210" t="s">
-        <v>876</v>
       </c>
       <c r="V210">
         <v>1.2536700999999999</v>
       </c>
       <c r="W210" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="211" spans="6:23" x14ac:dyDescent="0.2">
@@ -11247,37 +11247,37 @@
         <v>44751</v>
       </c>
       <c r="J211" s="17" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="K211" s="17" t="s">
+        <v>877</v>
+      </c>
+      <c r="L211" s="17" t="s">
         <v>878</v>
-      </c>
-      <c r="L211" s="17" t="s">
-        <v>879</v>
       </c>
       <c r="M211" s="17">
         <v>1.3792546999999999</v>
       </c>
       <c r="N211" s="17" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="R211" s="24">
         <v>45847</v>
       </c>
       <c r="S211" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="T211" t="s">
+        <v>877</v>
+      </c>
+      <c r="U211" t="s">
         <v>878</v>
-      </c>
-      <c r="U211" t="s">
-        <v>879</v>
       </c>
       <c r="V211">
         <v>1.3792546999999999</v>
       </c>
       <c r="W211" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="212" spans="6:23" x14ac:dyDescent="0.2">
@@ -11291,37 +11291,37 @@
         <v>44751</v>
       </c>
       <c r="J212" s="17" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="K212" s="17" t="s">
+        <v>880</v>
+      </c>
+      <c r="L212" s="17" t="s">
         <v>881</v>
-      </c>
-      <c r="L212" s="17" t="s">
-        <v>882</v>
       </c>
       <c r="M212" s="17">
         <v>1.5390637</v>
       </c>
       <c r="N212" s="17" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="R212" s="24">
         <v>45847</v>
       </c>
       <c r="S212" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="T212" t="s">
+        <v>880</v>
+      </c>
+      <c r="U212" t="s">
         <v>881</v>
-      </c>
-      <c r="U212" t="s">
-        <v>882</v>
       </c>
       <c r="V212">
         <v>1.5390637</v>
       </c>
       <c r="W212" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="213" spans="6:23" x14ac:dyDescent="0.2">
@@ -11335,37 +11335,37 @@
         <v>44750</v>
       </c>
       <c r="J213" s="17" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="K213" s="17" t="s">
+        <v>883</v>
+      </c>
+      <c r="L213" s="17" t="s">
         <v>884</v>
-      </c>
-      <c r="L213" s="17" t="s">
-        <v>885</v>
       </c>
       <c r="M213" s="17">
         <v>1.1874081000000001</v>
       </c>
       <c r="N213" s="17" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="R213" s="24">
         <v>45846</v>
       </c>
       <c r="S213" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="T213" t="s">
+        <v>883</v>
+      </c>
+      <c r="U213" t="s">
         <v>884</v>
-      </c>
-      <c r="U213" t="s">
-        <v>885</v>
       </c>
       <c r="V213">
         <v>1.1874081000000001</v>
       </c>
       <c r="W213" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="214" spans="6:23" x14ac:dyDescent="0.2">
@@ -11379,37 +11379,37 @@
         <v>44750</v>
       </c>
       <c r="J214" s="17" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="K214" s="17" t="s">
+        <v>886</v>
+      </c>
+      <c r="L214" s="17" t="s">
         <v>887</v>
-      </c>
-      <c r="L214" s="17" t="s">
-        <v>888</v>
       </c>
       <c r="M214" s="17">
         <v>1.4707878000000001</v>
       </c>
       <c r="N214" s="17" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="R214" s="24">
         <v>45846</v>
       </c>
       <c r="S214" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="T214" t="s">
+        <v>886</v>
+      </c>
+      <c r="U214" t="s">
         <v>887</v>
-      </c>
-      <c r="U214" t="s">
-        <v>888</v>
       </c>
       <c r="V214">
         <v>1.4707878000000001</v>
       </c>
       <c r="W214" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="215" spans="6:23" x14ac:dyDescent="0.2">
@@ -11423,37 +11423,37 @@
         <v>44576</v>
       </c>
       <c r="J215" s="17" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="K215" s="17" t="s">
+        <v>889</v>
+      </c>
+      <c r="L215" s="17" t="s">
         <v>890</v>
-      </c>
-      <c r="L215" s="17" t="s">
-        <v>891</v>
       </c>
       <c r="M215" s="17">
         <v>1.2154286000000001</v>
       </c>
       <c r="N215" s="17" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="R215" s="24">
         <v>45672</v>
       </c>
       <c r="S215" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="T215" t="s">
+        <v>889</v>
+      </c>
+      <c r="U215" t="s">
         <v>890</v>
-      </c>
-      <c r="U215" t="s">
-        <v>891</v>
       </c>
       <c r="V215">
         <v>1.2154286000000001</v>
       </c>
       <c r="W215" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="216" spans="6:23" x14ac:dyDescent="0.2">
@@ -11464,37 +11464,37 @@
         <v>44575</v>
       </c>
       <c r="J216" s="17" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="K216" s="17" t="s">
+        <v>892</v>
+      </c>
+      <c r="L216" s="17" t="s">
         <v>893</v>
-      </c>
-      <c r="L216" s="17" t="s">
-        <v>894</v>
       </c>
       <c r="M216" s="17">
         <v>1.7519902999999999</v>
       </c>
       <c r="N216" s="17" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="R216" s="24">
         <v>45671</v>
       </c>
       <c r="S216" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="T216" t="s">
+        <v>892</v>
+      </c>
+      <c r="U216" t="s">
         <v>893</v>
-      </c>
-      <c r="U216" t="s">
-        <v>894</v>
       </c>
       <c r="V216">
         <v>1.7519902999999999</v>
       </c>
       <c r="W216" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="217" spans="6:23" x14ac:dyDescent="0.2">
@@ -11508,37 +11508,37 @@
         <v>44791</v>
       </c>
       <c r="J217" s="17" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="K217" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="L217" s="17" t="s">
         <v>896</v>
-      </c>
-      <c r="L217" s="17" t="s">
-        <v>897</v>
       </c>
       <c r="M217" s="17">
         <v>1.056799</v>
       </c>
       <c r="N217" s="17" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="R217" s="24">
         <v>45887</v>
       </c>
       <c r="S217" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="T217" t="s">
+        <v>895</v>
+      </c>
+      <c r="U217" t="s">
         <v>896</v>
-      </c>
-      <c r="U217" t="s">
-        <v>897</v>
       </c>
       <c r="V217">
         <v>1.056799</v>
       </c>
       <c r="W217" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="218" spans="6:23" x14ac:dyDescent="0.2">
@@ -11552,37 +11552,37 @@
         <v>44791</v>
       </c>
       <c r="J218" s="17" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="K218" s="17" t="s">
+        <v>898</v>
+      </c>
+      <c r="L218" s="17" t="s">
         <v>899</v>
-      </c>
-      <c r="L218" s="17" t="s">
-        <v>900</v>
       </c>
       <c r="M218" s="17">
         <v>1.1725570000000001</v>
       </c>
       <c r="N218" s="17" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="R218" s="24">
         <v>45887</v>
       </c>
       <c r="S218" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="T218" t="s">
+        <v>898</v>
+      </c>
+      <c r="U218" t="s">
         <v>899</v>
-      </c>
-      <c r="U218" t="s">
-        <v>900</v>
       </c>
       <c r="V218">
         <v>1.1725570000000001</v>
       </c>
       <c r="W218" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="219" spans="6:23" x14ac:dyDescent="0.2">
@@ -11596,37 +11596,37 @@
         <v>44790</v>
       </c>
       <c r="J219" s="17" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="K219" s="17" t="s">
+        <v>901</v>
+      </c>
+      <c r="L219" s="17" t="s">
         <v>902</v>
-      </c>
-      <c r="L219" s="17" t="s">
-        <v>903</v>
       </c>
       <c r="M219" s="17">
         <v>1.4673160000000001</v>
       </c>
       <c r="N219" s="17" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="R219" s="24">
         <v>45886</v>
       </c>
       <c r="S219" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="T219" t="s">
+        <v>901</v>
+      </c>
+      <c r="U219" t="s">
         <v>902</v>
-      </c>
-      <c r="U219" t="s">
-        <v>903</v>
       </c>
       <c r="V219">
         <v>1.4673160000000001</v>
       </c>
       <c r="W219" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="220" spans="6:23" x14ac:dyDescent="0.2">
@@ -11640,37 +11640,37 @@
         <v>44660</v>
       </c>
       <c r="J220" s="17" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="K220" s="17" t="s">
+        <v>904</v>
+      </c>
+      <c r="L220" s="17" t="s">
         <v>905</v>
-      </c>
-      <c r="L220" s="17" t="s">
-        <v>906</v>
       </c>
       <c r="M220" s="17">
         <v>1.4774377999999999</v>
       </c>
       <c r="N220" s="17" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="R220" s="24">
         <v>45756</v>
       </c>
       <c r="S220" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="T220" t="s">
+        <v>904</v>
+      </c>
+      <c r="U220" t="s">
         <v>905</v>
-      </c>
-      <c r="U220" t="s">
-        <v>906</v>
       </c>
       <c r="V220">
         <v>1.4774377999999999</v>
       </c>
       <c r="W220" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="221" spans="6:23" x14ac:dyDescent="0.2">
@@ -11684,37 +11684,37 @@
         <v>44660</v>
       </c>
       <c r="J221" s="17" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="K221" s="17" t="s">
+        <v>907</v>
+      </c>
+      <c r="L221" s="17" t="s">
         <v>908</v>
-      </c>
-      <c r="L221" s="17" t="s">
-        <v>909</v>
       </c>
       <c r="M221" s="17">
         <v>1.4134035</v>
       </c>
       <c r="N221" s="17" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="R221" s="24">
         <v>45756</v>
       </c>
       <c r="S221" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="T221" t="s">
+        <v>907</v>
+      </c>
+      <c r="U221" t="s">
         <v>908</v>
-      </c>
-      <c r="U221" t="s">
-        <v>909</v>
       </c>
       <c r="V221">
         <v>1.4134035</v>
       </c>
       <c r="W221" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="222" spans="6:23" x14ac:dyDescent="0.2">
@@ -11728,37 +11728,37 @@
         <v>44660</v>
       </c>
       <c r="J222" s="17" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K222" s="17" t="s">
+        <v>910</v>
+      </c>
+      <c r="L222" s="17" t="s">
         <v>911</v>
-      </c>
-      <c r="L222" s="17" t="s">
-        <v>912</v>
       </c>
       <c r="M222" s="17">
         <v>2.1235175000000002</v>
       </c>
       <c r="N222" s="17" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="R222" s="24">
         <v>45756</v>
       </c>
       <c r="S222" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="T222" t="s">
+        <v>910</v>
+      </c>
+      <c r="U222" t="s">
         <v>911</v>
-      </c>
-      <c r="U222" t="s">
-        <v>912</v>
       </c>
       <c r="V222">
         <v>2.1235175000000002</v>
       </c>
       <c r="W222" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="223" spans="6:23" x14ac:dyDescent="0.2">
@@ -11772,37 +11772,37 @@
         <v>44659</v>
       </c>
       <c r="J223" s="17" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="K223" s="17" t="s">
+        <v>913</v>
+      </c>
+      <c r="L223" s="17" t="s">
         <v>914</v>
-      </c>
-      <c r="L223" s="17" t="s">
-        <v>915</v>
       </c>
       <c r="M223" s="17">
         <v>1.1041605000000001</v>
       </c>
       <c r="N223" s="17" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="R223" s="24">
         <v>45755</v>
       </c>
       <c r="S223" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="T223" t="s">
+        <v>913</v>
+      </c>
+      <c r="U223" t="s">
         <v>914</v>
-      </c>
-      <c r="U223" t="s">
-        <v>915</v>
       </c>
       <c r="V223">
         <v>1.1041605000000001</v>
       </c>
       <c r="W223" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="224" spans="6:23" x14ac:dyDescent="0.2">
@@ -11816,37 +11816,37 @@
         <v>44659</v>
       </c>
       <c r="J224" s="17" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="K224" s="17" t="s">
+        <v>916</v>
+      </c>
+      <c r="L224" s="17" t="s">
         <v>917</v>
-      </c>
-      <c r="L224" s="17" t="s">
-        <v>918</v>
       </c>
       <c r="M224" s="17">
         <v>1.0926659000000001</v>
       </c>
       <c r="N224" s="17" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="R224" s="24">
         <v>45755</v>
       </c>
       <c r="S224" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="T224" t="s">
+        <v>916</v>
+      </c>
+      <c r="U224" t="s">
         <v>917</v>
-      </c>
-      <c r="U224" t="s">
-        <v>918</v>
       </c>
       <c r="V224">
         <v>1.0926659000000001</v>
       </c>
       <c r="W224" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="225" spans="6:23" x14ac:dyDescent="0.2">
@@ -11860,37 +11860,37 @@
         <v>44659</v>
       </c>
       <c r="J225" s="17" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="K225" s="17" t="s">
+        <v>919</v>
+      </c>
+      <c r="L225" s="17" t="s">
         <v>920</v>
-      </c>
-      <c r="L225" s="17" t="s">
-        <v>921</v>
       </c>
       <c r="M225" s="17">
         <v>1.1012309</v>
       </c>
       <c r="N225" s="17" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="R225" s="24">
         <v>45755</v>
       </c>
       <c r="S225" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="T225" t="s">
+        <v>919</v>
+      </c>
+      <c r="U225" t="s">
         <v>920</v>
-      </c>
-      <c r="U225" t="s">
-        <v>921</v>
       </c>
       <c r="V225">
         <v>1.1012309</v>
       </c>
       <c r="W225" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="226" spans="6:23" x14ac:dyDescent="0.2">
@@ -11904,37 +11904,37 @@
         <v>44659</v>
       </c>
       <c r="J226" s="17" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="K226" s="17" t="s">
+        <v>922</v>
+      </c>
+      <c r="L226" s="17" t="s">
         <v>923</v>
-      </c>
-      <c r="L226" s="17" t="s">
-        <v>924</v>
       </c>
       <c r="M226" s="17">
         <v>1.5934718999999999</v>
       </c>
       <c r="N226" s="17" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="R226" s="24">
         <v>45755</v>
       </c>
       <c r="S226" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="T226" t="s">
+        <v>922</v>
+      </c>
+      <c r="U226" t="s">
         <v>923</v>
-      </c>
-      <c r="U226" t="s">
-        <v>924</v>
       </c>
       <c r="V226">
         <v>1.5934718999999999</v>
       </c>
       <c r="W226" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="227" spans="6:23" x14ac:dyDescent="0.2">
@@ -11948,37 +11948,37 @@
         <v>44444</v>
       </c>
       <c r="J227" s="17" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="K227" s="17" t="s">
+        <v>925</v>
+      </c>
+      <c r="L227" s="17" t="s">
         <v>926</v>
-      </c>
-      <c r="L227" s="17" t="s">
-        <v>927</v>
       </c>
       <c r="M227" s="17">
         <v>1.2583127999999999</v>
       </c>
       <c r="N227" s="17" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="R227" s="24">
         <v>45905</v>
       </c>
       <c r="S227" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="T227" t="s">
+        <v>925</v>
+      </c>
+      <c r="U227" t="s">
         <v>926</v>
-      </c>
-      <c r="U227" t="s">
-        <v>927</v>
       </c>
       <c r="V227">
         <v>1.2583127999999999</v>
       </c>
       <c r="W227" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="228" spans="6:23" x14ac:dyDescent="0.2">
@@ -11992,37 +11992,37 @@
         <v>44444</v>
       </c>
       <c r="J228" s="17" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="K228" s="17" t="s">
+        <v>928</v>
+      </c>
+      <c r="L228" s="17" t="s">
         <v>929</v>
-      </c>
-      <c r="L228" s="17" t="s">
-        <v>930</v>
       </c>
       <c r="M228" s="17">
         <v>1.6065252000000001</v>
       </c>
       <c r="N228" s="17" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="R228" s="24">
         <v>45905</v>
       </c>
       <c r="S228" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="T228" t="s">
+        <v>928</v>
+      </c>
+      <c r="U228" t="s">
         <v>929</v>
-      </c>
-      <c r="U228" t="s">
-        <v>930</v>
       </c>
       <c r="V228">
         <v>1.6065252000000001</v>
       </c>
       <c r="W228" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="229" spans="6:23" x14ac:dyDescent="0.2">
@@ -12036,37 +12036,37 @@
         <v>44487</v>
       </c>
       <c r="J229" s="17" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="K229" s="17" t="s">
+        <v>931</v>
+      </c>
+      <c r="L229" s="17" t="s">
         <v>932</v>
-      </c>
-      <c r="L229" s="17" t="s">
-        <v>933</v>
       </c>
       <c r="M229" s="17">
         <v>1.5719418999999999</v>
       </c>
       <c r="N229" s="17" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="R229" s="24">
         <v>45948</v>
       </c>
       <c r="S229" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="T229" t="s">
+        <v>931</v>
+      </c>
+      <c r="U229" t="s">
         <v>932</v>
-      </c>
-      <c r="U229" t="s">
-        <v>933</v>
       </c>
       <c r="V229">
         <v>1.5719418999999999</v>
       </c>
       <c r="W229" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="230" spans="6:23" x14ac:dyDescent="0.2">
@@ -12080,37 +12080,37 @@
         <v>44487</v>
       </c>
       <c r="J230" s="17" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="K230" s="17" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="L230" s="17" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="M230" s="17">
         <v>1.5199448</v>
       </c>
       <c r="N230" s="17" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="R230" s="24">
         <v>45948</v>
       </c>
       <c r="S230" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="T230" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="U230" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="V230">
         <v>1.5199448</v>
       </c>
       <c r="W230" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="231" spans="6:23" x14ac:dyDescent="0.2">
@@ -12124,37 +12124,37 @@
         <v>44355</v>
       </c>
       <c r="J231" s="17" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="K231" s="17" t="s">
+        <v>936</v>
+      </c>
+      <c r="L231" s="17" t="s">
         <v>937</v>
-      </c>
-      <c r="L231" s="17" t="s">
-        <v>938</v>
       </c>
       <c r="M231" s="17">
         <v>1.3366358</v>
       </c>
       <c r="N231" s="17" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="R231" s="24">
         <v>45816</v>
       </c>
       <c r="S231" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="T231" t="s">
+        <v>936</v>
+      </c>
+      <c r="U231" t="s">
         <v>937</v>
-      </c>
-      <c r="U231" t="s">
-        <v>938</v>
       </c>
       <c r="V231">
         <v>1.3366358</v>
       </c>
       <c r="W231" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="232" spans="6:23" x14ac:dyDescent="0.2">
@@ -12165,37 +12165,37 @@
         <v>44355</v>
       </c>
       <c r="J232" s="17" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="K232" s="17" t="s">
+        <v>939</v>
+      </c>
+      <c r="L232" s="17" t="s">
         <v>940</v>
-      </c>
-      <c r="L232" s="17" t="s">
-        <v>941</v>
       </c>
       <c r="M232" s="17">
         <v>1.8916166000000001</v>
       </c>
       <c r="N232" s="17" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="R232" s="24">
         <v>45816</v>
       </c>
       <c r="S232" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="T232" t="s">
+        <v>939</v>
+      </c>
+      <c r="U232" t="s">
         <v>940</v>
-      </c>
-      <c r="U232" t="s">
-        <v>941</v>
       </c>
       <c r="V232">
         <v>1.8916166000000001</v>
       </c>
       <c r="W232" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="233" spans="6:23" x14ac:dyDescent="0.2">
@@ -12209,37 +12209,37 @@
         <v>44399</v>
       </c>
       <c r="J233" s="17" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="K233" s="17" t="s">
+        <v>942</v>
+      </c>
+      <c r="L233" s="17" t="s">
         <v>943</v>
-      </c>
-      <c r="L233" s="17" t="s">
-        <v>944</v>
       </c>
       <c r="M233" s="17">
         <v>1.5616235999999999</v>
       </c>
       <c r="N233" s="17" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="R233" s="24">
         <v>45860</v>
       </c>
       <c r="S233" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="T233" t="s">
+        <v>942</v>
+      </c>
+      <c r="U233" t="s">
         <v>943</v>
-      </c>
-      <c r="U233" t="s">
-        <v>944</v>
       </c>
       <c r="V233">
         <v>1.5616235999999999</v>
       </c>
       <c r="W233" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="234" spans="6:23" x14ac:dyDescent="0.2">
@@ -12253,37 +12253,37 @@
         <v>44399</v>
       </c>
       <c r="J234" s="17" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="K234" s="17" t="s">
+        <v>945</v>
+      </c>
+      <c r="L234" s="17" t="s">
         <v>946</v>
-      </c>
-      <c r="L234" s="17" t="s">
-        <v>947</v>
       </c>
       <c r="M234" s="17">
         <v>1.1843096</v>
       </c>
       <c r="N234" s="17" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="R234" s="24">
         <v>45860</v>
       </c>
       <c r="S234" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="T234" t="s">
+        <v>945</v>
+      </c>
+      <c r="U234" t="s">
         <v>946</v>
-      </c>
-      <c r="U234" t="s">
-        <v>947</v>
       </c>
       <c r="V234">
         <v>1.1843096</v>
       </c>
       <c r="W234" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="235" spans="6:23" x14ac:dyDescent="0.2">
@@ -12297,37 +12297,37 @@
         <v>44399</v>
       </c>
       <c r="J235" s="17" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="K235" s="17" t="s">
+        <v>948</v>
+      </c>
+      <c r="L235" s="17" t="s">
         <v>949</v>
-      </c>
-      <c r="L235" s="17" t="s">
-        <v>950</v>
       </c>
       <c r="M235" s="17">
         <v>1.2036353</v>
       </c>
       <c r="N235" s="17" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="R235" s="24">
         <v>45860</v>
       </c>
       <c r="S235" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="T235" t="s">
+        <v>948</v>
+      </c>
+      <c r="U235" t="s">
         <v>949</v>
-      </c>
-      <c r="U235" t="s">
-        <v>950</v>
       </c>
       <c r="V235">
         <v>1.2036353</v>
       </c>
       <c r="W235" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="236" spans="6:23" x14ac:dyDescent="0.2">
@@ -12341,37 +12341,37 @@
         <v>44399</v>
       </c>
       <c r="J236" s="17" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="K236" s="17" t="s">
+        <v>951</v>
+      </c>
+      <c r="L236" s="17" t="s">
         <v>952</v>
-      </c>
-      <c r="L236" s="17" t="s">
-        <v>953</v>
       </c>
       <c r="M236" s="17">
         <v>1.3503057000000001</v>
       </c>
       <c r="N236" s="17" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="R236" s="24">
         <v>45860</v>
       </c>
       <c r="S236" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="T236" t="s">
+        <v>951</v>
+      </c>
+      <c r="U236" t="s">
         <v>952</v>
-      </c>
-      <c r="U236" t="s">
-        <v>953</v>
       </c>
       <c r="V236">
         <v>1.3503057000000001</v>
       </c>
       <c r="W236" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="237" spans="6:23" x14ac:dyDescent="0.2">
@@ -12385,37 +12385,37 @@
         <v>44399</v>
       </c>
       <c r="J237" s="17" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="K237" s="17" t="s">
+        <v>954</v>
+      </c>
+      <c r="L237" s="17" t="s">
         <v>955</v>
-      </c>
-      <c r="L237" s="17" t="s">
-        <v>956</v>
       </c>
       <c r="M237" s="17">
         <v>1.6111401000000001</v>
       </c>
       <c r="N237" s="17" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="R237" s="24">
         <v>45860</v>
       </c>
       <c r="S237" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="T237" t="s">
+        <v>954</v>
+      </c>
+      <c r="U237" t="s">
         <v>955</v>
-      </c>
-      <c r="U237" t="s">
-        <v>956</v>
       </c>
       <c r="V237">
         <v>1.6111401000000001</v>
       </c>
       <c r="W237" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="238" spans="6:23" x14ac:dyDescent="0.2">
@@ -12429,37 +12429,37 @@
         <v>44443</v>
       </c>
       <c r="J238" s="17" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="K238" s="17" t="s">
+        <v>956</v>
+      </c>
+      <c r="L238" s="17" t="s">
         <v>957</v>
-      </c>
-      <c r="L238" s="17" t="s">
-        <v>958</v>
       </c>
       <c r="M238" s="17">
         <v>1.6240193000000001</v>
       </c>
       <c r="N238" s="17" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="R238" s="24">
         <v>45904</v>
       </c>
       <c r="S238" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="T238" t="s">
+        <v>956</v>
+      </c>
+      <c r="U238" t="s">
         <v>957</v>
-      </c>
-      <c r="U238" t="s">
-        <v>958</v>
       </c>
       <c r="V238">
         <v>1.6240193000000001</v>
       </c>
       <c r="W238" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="239" spans="6:23" x14ac:dyDescent="0.2">
@@ -12473,37 +12473,37 @@
         <v>44443</v>
       </c>
       <c r="J239" s="17" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="K239" s="17" t="s">
+        <v>959</v>
+      </c>
+      <c r="L239" s="17" t="s">
         <v>960</v>
-      </c>
-      <c r="L239" s="17" t="s">
-        <v>961</v>
       </c>
       <c r="M239" s="17">
         <v>1.2725857</v>
       </c>
       <c r="N239" s="17" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="R239" s="24">
         <v>45904</v>
       </c>
       <c r="S239" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="T239" t="s">
+        <v>959</v>
+      </c>
+      <c r="U239" t="s">
         <v>960</v>
-      </c>
-      <c r="U239" t="s">
-        <v>961</v>
       </c>
       <c r="V239">
         <v>1.2725857</v>
       </c>
       <c r="W239" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="240" spans="6:23" x14ac:dyDescent="0.2">
@@ -12517,37 +12517,37 @@
         <v>44486</v>
       </c>
       <c r="J240" s="17" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="K240" s="17" t="s">
+        <v>962</v>
+      </c>
+      <c r="L240" s="17" t="s">
         <v>963</v>
-      </c>
-      <c r="L240" s="17" t="s">
-        <v>964</v>
       </c>
       <c r="M240" s="17">
         <v>1.3515691999999999</v>
       </c>
       <c r="N240" s="17" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="R240" s="24">
         <v>45947</v>
       </c>
       <c r="S240" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="T240" t="s">
+        <v>962</v>
+      </c>
+      <c r="U240" t="s">
         <v>963</v>
-      </c>
-      <c r="U240" t="s">
-        <v>964</v>
       </c>
       <c r="V240">
         <v>1.3515691999999999</v>
       </c>
       <c r="W240" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="241" spans="6:23" x14ac:dyDescent="0.2">
@@ -12561,37 +12561,37 @@
         <v>44486</v>
       </c>
       <c r="J241" s="17" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="K241" s="17" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="L241" s="17" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="M241" s="17">
         <v>1.7066178000000001</v>
       </c>
       <c r="N241" s="17" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="R241" s="24">
         <v>45947</v>
       </c>
       <c r="S241" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="T241" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="U241" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="V241">
         <v>1.7066178000000001</v>
       </c>
       <c r="W241" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="242" spans="6:23" x14ac:dyDescent="0.2">
@@ -12605,37 +12605,37 @@
         <v>44354</v>
       </c>
       <c r="J242" s="17" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="K242" s="17" t="s">
+        <v>967</v>
+      </c>
+      <c r="L242" s="17" t="s">
         <v>968</v>
-      </c>
-      <c r="L242" s="17" t="s">
-        <v>969</v>
       </c>
       <c r="M242" s="17">
         <v>1.2615983</v>
       </c>
       <c r="N242" s="17" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="R242" s="24">
         <v>45815</v>
       </c>
       <c r="S242" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="T242" t="s">
+        <v>967</v>
+      </c>
+      <c r="U242" t="s">
         <v>968</v>
-      </c>
-      <c r="U242" t="s">
-        <v>969</v>
       </c>
       <c r="V242">
         <v>1.2615983</v>
       </c>
       <c r="W242" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="243" spans="6:23" x14ac:dyDescent="0.2">
@@ -12649,37 +12649,37 @@
         <v>44354</v>
       </c>
       <c r="J243" s="17" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="K243" s="17" t="s">
+        <v>970</v>
+      </c>
+      <c r="L243" s="17" t="s">
         <v>971</v>
-      </c>
-      <c r="L243" s="17" t="s">
-        <v>972</v>
       </c>
       <c r="M243" s="17">
         <v>2.2228183000000001</v>
       </c>
       <c r="N243" s="17" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="R243" s="24">
         <v>45815</v>
       </c>
       <c r="S243" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="T243" t="s">
+        <v>970</v>
+      </c>
+      <c r="U243" t="s">
         <v>971</v>
-      </c>
-      <c r="U243" t="s">
-        <v>972</v>
       </c>
       <c r="V243">
         <v>2.2228183000000001</v>
       </c>
       <c r="W243" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="244" spans="6:23" x14ac:dyDescent="0.2">
@@ -12693,37 +12693,37 @@
         <v>44398</v>
       </c>
       <c r="J244" s="17" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="K244" s="17" t="s">
+        <v>973</v>
+      </c>
+      <c r="L244" s="17" t="s">
         <v>974</v>
-      </c>
-      <c r="L244" s="17" t="s">
-        <v>975</v>
       </c>
       <c r="M244" s="17">
         <v>1.6068905</v>
       </c>
       <c r="N244" s="17" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="R244" s="24">
         <v>45859</v>
       </c>
       <c r="S244" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="T244" t="s">
+        <v>973</v>
+      </c>
+      <c r="U244" t="s">
         <v>974</v>
-      </c>
-      <c r="U244" t="s">
-        <v>975</v>
       </c>
       <c r="V244">
         <v>1.6068905</v>
       </c>
       <c r="W244" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="245" spans="6:23" x14ac:dyDescent="0.2">
@@ -12737,37 +12737,37 @@
         <v>44398</v>
       </c>
       <c r="J245" s="17" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="K245" s="17" t="s">
+        <v>976</v>
+      </c>
+      <c r="L245" s="17" t="s">
         <v>977</v>
-      </c>
-      <c r="L245" s="17" t="s">
-        <v>978</v>
       </c>
       <c r="M245" s="17">
         <v>1.3805523</v>
       </c>
       <c r="N245" s="17" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="R245" s="24">
         <v>45859</v>
       </c>
       <c r="S245" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="T245" t="s">
+        <v>976</v>
+      </c>
+      <c r="U245" t="s">
         <v>977</v>
-      </c>
-      <c r="U245" t="s">
-        <v>978</v>
       </c>
       <c r="V245">
         <v>1.3805523</v>
       </c>
       <c r="W245" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="246" spans="6:23" x14ac:dyDescent="0.2">
@@ -12781,37 +12781,37 @@
         <v>44398</v>
       </c>
       <c r="J246" s="17" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="K246" s="17" t="s">
+        <v>979</v>
+      </c>
+      <c r="L246" s="17" t="s">
         <v>980</v>
-      </c>
-      <c r="L246" s="17" t="s">
-        <v>981</v>
       </c>
       <c r="M246" s="17">
         <v>1.2608678</v>
       </c>
       <c r="N246" s="17" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="R246" s="24">
         <v>45859</v>
       </c>
       <c r="S246" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="T246" t="s">
+        <v>979</v>
+      </c>
+      <c r="U246" t="s">
         <v>980</v>
-      </c>
-      <c r="U246" t="s">
-        <v>981</v>
       </c>
       <c r="V246">
         <v>1.2608678</v>
       </c>
       <c r="W246" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="247" spans="6:23" x14ac:dyDescent="0.2">
@@ -12825,37 +12825,37 @@
         <v>44398</v>
       </c>
       <c r="J247" s="17" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="K247" s="17" t="s">
+        <v>982</v>
+      </c>
+      <c r="L247" s="17" t="s">
         <v>983</v>
-      </c>
-      <c r="L247" s="17" t="s">
-        <v>984</v>
       </c>
       <c r="M247" s="17">
         <v>1.2068447</v>
       </c>
       <c r="N247" s="17" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="R247" s="24">
         <v>45859</v>
       </c>
       <c r="S247" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="T247" t="s">
+        <v>982</v>
+      </c>
+      <c r="U247" t="s">
         <v>983</v>
-      </c>
-      <c r="U247" t="s">
-        <v>984</v>
       </c>
       <c r="V247">
         <v>1.2068447</v>
       </c>
       <c r="W247" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="248" spans="6:23" x14ac:dyDescent="0.2">
@@ -12869,37 +12869,37 @@
         <v>44398</v>
       </c>
       <c r="J248" s="17" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="K248" s="17" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="L248" s="17" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M248" s="17">
         <v>1.1973085999999999</v>
       </c>
       <c r="N248" s="17" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="R248" s="24">
         <v>45859</v>
       </c>
       <c r="S248" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="T248" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="U248" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="V248">
         <v>1.1973085999999999</v>
       </c>
       <c r="W248" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="249" spans="6:23" x14ac:dyDescent="0.2">
@@ -12913,37 +12913,37 @@
         <v>44398</v>
       </c>
       <c r="J249" s="17" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="K249" s="17" t="s">
+        <v>987</v>
+      </c>
+      <c r="L249" s="17" t="s">
         <v>988</v>
-      </c>
-      <c r="L249" s="17" t="s">
-        <v>989</v>
       </c>
       <c r="M249" s="17">
         <v>1.6192648000000001</v>
       </c>
       <c r="N249" s="17" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="R249" s="24">
         <v>45859</v>
       </c>
       <c r="S249" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="T249" t="s">
+        <v>987</v>
+      </c>
+      <c r="U249" t="s">
         <v>988</v>
-      </c>
-      <c r="U249" t="s">
-        <v>989</v>
       </c>
       <c r="V249">
         <v>1.6192648000000001</v>
       </c>
       <c r="W249" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="250" spans="6:23" x14ac:dyDescent="0.2">
@@ -12957,37 +12957,37 @@
         <v>44143</v>
       </c>
       <c r="J250" s="17" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="K250" s="17" t="s">
+        <v>989</v>
+      </c>
+      <c r="L250" s="17" t="s">
         <v>990</v>
-      </c>
-      <c r="L250" s="17" t="s">
-        <v>991</v>
       </c>
       <c r="M250" s="17">
         <v>1.8621312999999999</v>
       </c>
       <c r="N250" s="17" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="R250" s="24">
         <v>45969</v>
       </c>
       <c r="S250" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="T250" t="s">
+        <v>989</v>
+      </c>
+      <c r="U250" t="s">
         <v>990</v>
-      </c>
-      <c r="U250" t="s">
-        <v>991</v>
       </c>
       <c r="V250">
         <v>1.8621312999999999</v>
       </c>
       <c r="W250" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="251" spans="6:23" x14ac:dyDescent="0.2">
@@ -13001,37 +13001,37 @@
         <v>44142</v>
       </c>
       <c r="J251" s="17" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="K251" s="17" t="s">
+        <v>992</v>
+      </c>
+      <c r="L251" s="17" t="s">
         <v>993</v>
-      </c>
-      <c r="L251" s="17" t="s">
-        <v>994</v>
       </c>
       <c r="M251" s="17">
         <v>1.6940672000000001</v>
       </c>
       <c r="N251" s="17" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="R251" s="24">
         <v>45968</v>
       </c>
       <c r="S251" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="T251" t="s">
+        <v>992</v>
+      </c>
+      <c r="U251" t="s">
         <v>993</v>
-      </c>
-      <c r="U251" t="s">
-        <v>994</v>
       </c>
       <c r="V251">
         <v>1.6940672000000001</v>
       </c>
       <c r="W251" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="252" spans="6:23" x14ac:dyDescent="0.2">
@@ -13045,37 +13045,37 @@
         <v>44142</v>
       </c>
       <c r="J252" s="17" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="K252" s="17" t="s">
+        <v>995</v>
+      </c>
+      <c r="L252" s="17" t="s">
         <v>996</v>
-      </c>
-      <c r="L252" s="17" t="s">
-        <v>997</v>
       </c>
       <c r="M252" s="17">
         <v>1.5353939000000001</v>
       </c>
       <c r="N252" s="17" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="R252" s="24">
         <v>45968</v>
       </c>
       <c r="S252" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="T252" t="s">
+        <v>995</v>
+      </c>
+      <c r="U252" t="s">
         <v>996</v>
-      </c>
-      <c r="U252" t="s">
-        <v>997</v>
       </c>
       <c r="V252">
         <v>1.5353939000000001</v>
       </c>
       <c r="W252" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="253" spans="6:23" x14ac:dyDescent="0.2">
@@ -13089,37 +13089,37 @@
         <v>44146</v>
       </c>
       <c r="J253" s="17" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="K253" s="17" t="s">
+        <v>998</v>
+      </c>
+      <c r="L253" s="17" t="s">
         <v>999</v>
-      </c>
-      <c r="L253" s="17" t="s">
-        <v>1000</v>
       </c>
       <c r="M253" s="17">
         <v>1.7808611999999999</v>
       </c>
       <c r="N253" s="17" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="R253" s="24">
         <v>45972</v>
       </c>
       <c r="S253" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="T253" t="s">
+        <v>998</v>
+      </c>
+      <c r="U253" t="s">
         <v>999</v>
-      </c>
-      <c r="U253" t="s">
-        <v>1000</v>
       </c>
       <c r="V253">
         <v>1.7808611999999999</v>
       </c>
       <c r="W253" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="254" spans="6:23" x14ac:dyDescent="0.2">
@@ -13133,37 +13133,37 @@
         <v>44145</v>
       </c>
       <c r="J254" s="17" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="K254" s="17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="L254" s="17" t="s">
         <v>1002</v>
-      </c>
-      <c r="L254" s="17" t="s">
-        <v>1003</v>
       </c>
       <c r="M254" s="17">
         <v>1.5929922000000001</v>
       </c>
       <c r="N254" s="17" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="R254" s="24">
         <v>45971</v>
       </c>
       <c r="S254" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="T254" t="s">
+        <v>1001</v>
+      </c>
+      <c r="U254" t="s">
         <v>1002</v>
-      </c>
-      <c r="U254" t="s">
-        <v>1003</v>
       </c>
       <c r="V254">
         <v>1.5929922000000001</v>
       </c>
       <c r="W254" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="255" spans="6:23" x14ac:dyDescent="0.2">
@@ -13177,37 +13177,37 @@
         <v>44017</v>
       </c>
       <c r="J255" s="17" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="K255" s="17" t="s">
+        <v>1004</v>
+      </c>
+      <c r="L255" s="17" t="s">
         <v>1005</v>
-      </c>
-      <c r="L255" s="17" t="s">
-        <v>1006</v>
       </c>
       <c r="M255" s="17">
         <v>1.5276727000000001</v>
       </c>
       <c r="N255" s="17" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="R255" s="24">
         <v>45843</v>
       </c>
       <c r="S255" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="T255" t="s">
+        <v>1004</v>
+      </c>
+      <c r="U255" t="s">
         <v>1005</v>
-      </c>
-      <c r="U255" t="s">
-        <v>1006</v>
       </c>
       <c r="V255">
         <v>1.5276727000000001</v>
       </c>
       <c r="W255" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="256" spans="6:23" x14ac:dyDescent="0.2">
@@ -13221,37 +13221,37 @@
         <v>44017</v>
       </c>
       <c r="J256" s="17" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="K256" s="17" t="s">
+        <v>1006</v>
+      </c>
+      <c r="L256" s="17" t="s">
         <v>1007</v>
-      </c>
-      <c r="L256" s="17" t="s">
-        <v>1008</v>
       </c>
       <c r="M256" s="17">
         <v>1.5576570000000001</v>
       </c>
       <c r="N256" s="17" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="R256" s="24">
         <v>45843</v>
       </c>
       <c r="S256" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="T256" t="s">
+        <v>1006</v>
+      </c>
+      <c r="U256" t="s">
         <v>1007</v>
-      </c>
-      <c r="U256" t="s">
-        <v>1008</v>
       </c>
       <c r="V256">
         <v>1.5576570000000001</v>
       </c>
       <c r="W256" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="257" spans="6:23" x14ac:dyDescent="0.2">
@@ -13262,37 +13262,37 @@
         <v>44016</v>
       </c>
       <c r="J257" s="17" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="K257" s="17" t="s">
+        <v>1009</v>
+      </c>
+      <c r="L257" s="17" t="s">
         <v>1010</v>
-      </c>
-      <c r="L257" s="17" t="s">
-        <v>1011</v>
       </c>
       <c r="M257" s="17">
         <v>1.4473488999999999</v>
       </c>
       <c r="N257" s="17" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="R257" s="24">
         <v>45842</v>
       </c>
       <c r="S257" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="T257" t="s">
+        <v>1009</v>
+      </c>
+      <c r="U257" t="s">
         <v>1010</v>
-      </c>
-      <c r="U257" t="s">
-        <v>1011</v>
       </c>
       <c r="V257">
         <v>1.4473488999999999</v>
       </c>
       <c r="W257" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="258" spans="6:23" x14ac:dyDescent="0.2">
@@ -13306,37 +13306,37 @@
         <v>44016</v>
       </c>
       <c r="J258" s="17" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="K258" s="17" t="s">
+        <v>1012</v>
+      </c>
+      <c r="L258" s="17" t="s">
         <v>1013</v>
-      </c>
-      <c r="L258" s="17" t="s">
-        <v>1014</v>
       </c>
       <c r="M258" s="17">
         <v>1.6473275999999999</v>
       </c>
       <c r="N258" s="17" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="R258" s="24">
         <v>45842</v>
       </c>
       <c r="S258" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="T258" t="s">
+        <v>1012</v>
+      </c>
+      <c r="U258" t="s">
         <v>1013</v>
-      </c>
-      <c r="U258" t="s">
-        <v>1014</v>
       </c>
       <c r="V258">
         <v>1.6473275999999999</v>
       </c>
       <c r="W258" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="259" spans="6:23" x14ac:dyDescent="0.2">
@@ -13350,37 +13350,37 @@
         <v>44189</v>
       </c>
       <c r="J259" s="17" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="K259" s="17" t="s">
+        <v>1015</v>
+      </c>
+      <c r="L259" s="17" t="s">
         <v>1016</v>
-      </c>
-      <c r="L259" s="17" t="s">
-        <v>1017</v>
       </c>
       <c r="M259" s="17">
         <v>1.3096884</v>
       </c>
       <c r="N259" s="17" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="R259" s="24">
         <v>46015</v>
       </c>
       <c r="S259" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="T259" t="s">
+        <v>1015</v>
+      </c>
+      <c r="U259" t="s">
         <v>1016</v>
-      </c>
-      <c r="U259" t="s">
-        <v>1017</v>
       </c>
       <c r="V259">
         <v>1.3096884</v>
       </c>
       <c r="W259" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="260" spans="6:23" x14ac:dyDescent="0.2">
@@ -13394,37 +13394,37 @@
         <v>44188</v>
       </c>
       <c r="J260" s="17" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="K260" s="17" t="s">
+        <v>1018</v>
+      </c>
+      <c r="L260" s="17" t="s">
         <v>1019</v>
-      </c>
-      <c r="L260" s="17" t="s">
-        <v>1020</v>
       </c>
       <c r="M260" s="17">
         <v>1.3397516</v>
       </c>
       <c r="N260" s="17" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="R260" s="24">
         <v>46014</v>
       </c>
       <c r="S260" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="T260" t="s">
+        <v>1018</v>
+      </c>
+      <c r="U260" t="s">
         <v>1019</v>
-      </c>
-      <c r="U260" t="s">
-        <v>1020</v>
       </c>
       <c r="V260">
         <v>1.3397516</v>
       </c>
       <c r="W260" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="261" spans="6:23" x14ac:dyDescent="0.2">
@@ -13438,37 +13438,37 @@
         <v>44188</v>
       </c>
       <c r="J261" s="17" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="K261" s="17" t="s">
+        <v>1021</v>
+      </c>
+      <c r="L261" s="17" t="s">
         <v>1022</v>
-      </c>
-      <c r="L261" s="17" t="s">
-        <v>1023</v>
       </c>
       <c r="M261" s="17">
         <v>1.3545707</v>
       </c>
       <c r="N261" s="17" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="R261" s="24">
         <v>46014</v>
       </c>
       <c r="S261" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="T261" t="s">
+        <v>1021</v>
+      </c>
+      <c r="U261" t="s">
         <v>1022</v>
-      </c>
-      <c r="U261" t="s">
-        <v>1023</v>
       </c>
       <c r="V261">
         <v>1.3545707</v>
       </c>
       <c r="W261" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="262" spans="6:23" x14ac:dyDescent="0.2">
@@ -13482,37 +13482,37 @@
         <v>44188</v>
       </c>
       <c r="J262" s="17" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="K262" s="17" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L262" s="17" t="s">
         <v>1025</v>
-      </c>
-      <c r="L262" s="17" t="s">
-        <v>1026</v>
       </c>
       <c r="M262" s="17">
         <v>2.1324662000000001</v>
       </c>
       <c r="N262" s="17" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="R262" s="24">
         <v>46014</v>
       </c>
       <c r="S262" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="T262" t="s">
+        <v>1024</v>
+      </c>
+      <c r="U262" t="s">
         <v>1025</v>
-      </c>
-      <c r="U262" t="s">
-        <v>1026</v>
       </c>
       <c r="V262">
         <v>2.1324662000000001</v>
       </c>
       <c r="W262" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="263" spans="6:23" x14ac:dyDescent="0.2">
@@ -13526,37 +13526,37 @@
         <v>44188</v>
       </c>
       <c r="J263" s="17" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="K263" s="17" t="s">
+        <v>1027</v>
+      </c>
+      <c r="L263" s="17" t="s">
         <v>1028</v>
-      </c>
-      <c r="L263" s="17" t="s">
-        <v>1029</v>
       </c>
       <c r="M263" s="17">
         <v>1.8972617000000001</v>
       </c>
       <c r="N263" s="17" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="R263" s="24">
         <v>46014</v>
       </c>
       <c r="S263" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="T263" t="s">
+        <v>1027</v>
+      </c>
+      <c r="U263" t="s">
         <v>1028</v>
-      </c>
-      <c r="U263" t="s">
-        <v>1029</v>
       </c>
       <c r="V263">
         <v>1.8972617000000001</v>
       </c>
       <c r="W263" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="264" spans="6:23" x14ac:dyDescent="0.2">
@@ -13570,37 +13570,37 @@
         <v>43482</v>
       </c>
       <c r="J264" s="17" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="K264" s="17" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L264" s="17" t="s">
         <v>1031</v>
-      </c>
-      <c r="L264" s="17" t="s">
-        <v>1032</v>
       </c>
       <c r="M264" s="17">
         <v>1.3527285</v>
       </c>
       <c r="N264" s="17" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="R264" s="24">
         <v>45674</v>
       </c>
       <c r="S264" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="T264" t="s">
+        <v>1030</v>
+      </c>
+      <c r="U264" t="s">
         <v>1031</v>
-      </c>
-      <c r="U264" t="s">
-        <v>1032</v>
       </c>
       <c r="V264">
         <v>1.3527285</v>
       </c>
       <c r="W264" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="265" spans="6:23" x14ac:dyDescent="0.2">
@@ -13614,37 +13614,37 @@
         <v>43482</v>
       </c>
       <c r="J265" s="17" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="K265" s="17" t="s">
+        <v>1033</v>
+      </c>
+      <c r="L265" s="17" t="s">
         <v>1034</v>
-      </c>
-      <c r="L265" s="17" t="s">
-        <v>1035</v>
       </c>
       <c r="M265" s="17">
         <v>1.3717834</v>
       </c>
       <c r="N265" s="17" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="R265" s="24">
         <v>45674</v>
       </c>
       <c r="S265" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="T265" t="s">
+        <v>1033</v>
+      </c>
+      <c r="U265" t="s">
         <v>1034</v>
-      </c>
-      <c r="U265" t="s">
-        <v>1035</v>
       </c>
       <c r="V265">
         <v>1.3717834</v>
       </c>
       <c r="W265" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="266" spans="6:23" x14ac:dyDescent="0.2">
@@ -13658,37 +13658,37 @@
         <v>43482</v>
       </c>
       <c r="J266" s="17" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="K266" s="17" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L266" s="17" t="s">
         <v>1037</v>
-      </c>
-      <c r="L266" s="17" t="s">
-        <v>1038</v>
       </c>
       <c r="M266" s="17">
         <v>1.4576948999999999</v>
       </c>
       <c r="N266" s="17" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="R266" s="24">
         <v>45674</v>
       </c>
       <c r="S266" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="T266" t="s">
+        <v>1036</v>
+      </c>
+      <c r="U266" t="s">
         <v>1037</v>
-      </c>
-      <c r="U266" t="s">
-        <v>1038</v>
       </c>
       <c r="V266">
         <v>1.4576948999999999</v>
       </c>
       <c r="W266" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="267" spans="6:23" x14ac:dyDescent="0.2">
@@ -13702,37 +13702,37 @@
         <v>43482</v>
       </c>
       <c r="J267" s="17" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="K267" s="17" t="s">
+        <v>1039</v>
+      </c>
+      <c r="L267" s="17" t="s">
         <v>1040</v>
-      </c>
-      <c r="L267" s="17" t="s">
-        <v>1041</v>
       </c>
       <c r="M267" s="17">
         <v>1.4954050000000001</v>
       </c>
       <c r="N267" s="17" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="R267" s="24">
         <v>45674</v>
       </c>
       <c r="S267" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="T267" t="s">
+        <v>1039</v>
+      </c>
+      <c r="U267" t="s">
         <v>1040</v>
-      </c>
-      <c r="U267" t="s">
-        <v>1041</v>
       </c>
       <c r="V267">
         <v>1.4954050000000001</v>
       </c>
       <c r="W267" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="268" spans="6:23" x14ac:dyDescent="0.2">
@@ -13746,37 +13746,37 @@
         <v>43482</v>
       </c>
       <c r="J268" s="17" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="K268" s="17" t="s">
+        <v>1042</v>
+      </c>
+      <c r="L268" s="17" t="s">
         <v>1043</v>
-      </c>
-      <c r="L268" s="17" t="s">
-        <v>1044</v>
       </c>
       <c r="M268" s="17">
         <v>1.7403309</v>
       </c>
       <c r="N268" s="17" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="R268" s="24">
         <v>45674</v>
       </c>
       <c r="S268" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="T268" t="s">
+        <v>1042</v>
+      </c>
+      <c r="U268" t="s">
         <v>1043</v>
-      </c>
-      <c r="U268" t="s">
-        <v>1044</v>
       </c>
       <c r="V268">
         <v>1.7403309</v>
       </c>
       <c r="W268" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="269" spans="6:23" x14ac:dyDescent="0.2">
@@ -13790,37 +13790,37 @@
         <v>43482</v>
       </c>
       <c r="J269" s="17" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="K269" s="17" t="s">
+        <v>1045</v>
+      </c>
+      <c r="L269" s="17" t="s">
         <v>1046</v>
-      </c>
-      <c r="L269" s="17" t="s">
-        <v>1047</v>
       </c>
       <c r="M269" s="17">
         <v>1.8176920999999999</v>
       </c>
       <c r="N269" s="17" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="R269" s="24">
         <v>45674</v>
       </c>
       <c r="S269" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="T269" t="s">
+        <v>1045</v>
+      </c>
+      <c r="U269" t="s">
         <v>1046</v>
-      </c>
-      <c r="U269" t="s">
-        <v>1047</v>
       </c>
       <c r="V269">
         <v>1.8176920999999999</v>
       </c>
       <c r="W269" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="270" spans="6:23" x14ac:dyDescent="0.2">
@@ -13834,37 +13834,37 @@
         <v>43481</v>
       </c>
       <c r="J270" s="17" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="K270" s="17" t="s">
+        <v>1048</v>
+      </c>
+      <c r="L270" s="17" t="s">
         <v>1049</v>
-      </c>
-      <c r="L270" s="17" t="s">
-        <v>1050</v>
       </c>
       <c r="M270" s="17">
         <v>1.4138792</v>
       </c>
       <c r="N270" s="17" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="R270" s="24">
         <v>45673</v>
       </c>
       <c r="S270" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="T270" t="s">
+        <v>1048</v>
+      </c>
+      <c r="U270" t="s">
         <v>1049</v>
-      </c>
-      <c r="U270" t="s">
-        <v>1050</v>
       </c>
       <c r="V270">
         <v>1.4138792</v>
       </c>
       <c r="W270" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="271" spans="6:23" x14ac:dyDescent="0.2">
@@ -13878,37 +13878,37 @@
         <v>43481</v>
       </c>
       <c r="J271" s="17" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="K271" s="17" t="s">
+        <v>1051</v>
+      </c>
+      <c r="L271" s="17" t="s">
         <v>1052</v>
-      </c>
-      <c r="L271" s="17" t="s">
-        <v>1053</v>
       </c>
       <c r="M271" s="17">
         <v>1.4515434</v>
       </c>
       <c r="N271" s="17" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="R271" s="24">
         <v>45673</v>
       </c>
       <c r="S271" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="T271" t="s">
+        <v>1051</v>
+      </c>
+      <c r="U271" t="s">
         <v>1052</v>
-      </c>
-      <c r="U271" t="s">
-        <v>1053</v>
       </c>
       <c r="V271">
         <v>1.4515434</v>
       </c>
       <c r="W271" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="272" spans="6:23" x14ac:dyDescent="0.2">
@@ -13922,37 +13922,37 @@
         <v>43481</v>
       </c>
       <c r="J272" s="17" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="K272" s="17" t="s">
+        <v>1054</v>
+      </c>
+      <c r="L272" s="17" t="s">
         <v>1055</v>
-      </c>
-      <c r="L272" s="17" t="s">
-        <v>1056</v>
       </c>
       <c r="M272" s="17">
         <v>1.3697168</v>
       </c>
       <c r="N272" s="17" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="R272" s="24">
         <v>45673</v>
       </c>
       <c r="S272" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="T272" t="s">
+        <v>1054</v>
+      </c>
+      <c r="U272" t="s">
         <v>1055</v>
-      </c>
-      <c r="U272" t="s">
-        <v>1056</v>
       </c>
       <c r="V272">
         <v>1.3697168</v>
       </c>
       <c r="W272" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="273" spans="6:23" x14ac:dyDescent="0.2">
@@ -13966,37 +13966,37 @@
         <v>43481</v>
       </c>
       <c r="J273" s="17" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="K273" s="17" t="s">
+        <v>1057</v>
+      </c>
+      <c r="L273" s="17" t="s">
         <v>1058</v>
-      </c>
-      <c r="L273" s="17" t="s">
-        <v>1059</v>
       </c>
       <c r="M273" s="17">
         <v>1.3547161000000001</v>
       </c>
       <c r="N273" s="17" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="R273" s="24">
         <v>45673</v>
       </c>
       <c r="S273" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="T273" t="s">
+        <v>1057</v>
+      </c>
+      <c r="U273" t="s">
         <v>1058</v>
-      </c>
-      <c r="U273" t="s">
-        <v>1059</v>
       </c>
       <c r="V273">
         <v>1.3547161000000001</v>
       </c>
       <c r="W273" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="274" spans="6:23" x14ac:dyDescent="0.2">
@@ -14010,37 +14010,37 @@
         <v>43481</v>
       </c>
       <c r="J274" s="17" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="K274" s="17" t="s">
+        <v>1060</v>
+      </c>
+      <c r="L274" s="17" t="s">
         <v>1061</v>
-      </c>
-      <c r="L274" s="17" t="s">
-        <v>1062</v>
       </c>
       <c r="M274" s="17">
         <v>1.8353286</v>
       </c>
       <c r="N274" s="17" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="R274" s="24">
         <v>45673</v>
       </c>
       <c r="S274" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="T274" t="s">
+        <v>1060</v>
+      </c>
+      <c r="U274" t="s">
         <v>1061</v>
-      </c>
-      <c r="U274" t="s">
-        <v>1062</v>
       </c>
       <c r="V274">
         <v>1.8353286</v>
       </c>
       <c r="W274" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="275" spans="6:23" x14ac:dyDescent="0.2">
@@ -14054,37 +14054,37 @@
         <v>43481</v>
       </c>
       <c r="J275" s="17" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="K275" s="17" t="s">
+        <v>1063</v>
+      </c>
+      <c r="L275" s="17" t="s">
         <v>1064</v>
-      </c>
-      <c r="L275" s="17" t="s">
-        <v>1065</v>
       </c>
       <c r="M275" s="17">
         <v>1.7327911</v>
       </c>
       <c r="N275" s="17" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="R275" s="24">
         <v>45673</v>
       </c>
       <c r="S275" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="T275" t="s">
+        <v>1063</v>
+      </c>
+      <c r="U275" t="s">
         <v>1064</v>
-      </c>
-      <c r="U275" t="s">
-        <v>1065</v>
       </c>
       <c r="V275">
         <v>1.7327911</v>
       </c>
       <c r="W275" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="276" spans="6:23" x14ac:dyDescent="0.2">
@@ -14098,37 +14098,37 @@
         <v>43481</v>
       </c>
       <c r="J276" s="17" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="K276" s="17" t="s">
+        <v>1066</v>
+      </c>
+      <c r="L276" s="17" t="s">
         <v>1067</v>
-      </c>
-      <c r="L276" s="17" t="s">
-        <v>1068</v>
       </c>
       <c r="M276" s="17">
         <v>1.7980571000000001</v>
       </c>
       <c r="N276" s="17" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="R276" s="24">
         <v>45673</v>
       </c>
       <c r="S276" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="T276" t="s">
+        <v>1066</v>
+      </c>
+      <c r="U276" t="s">
         <v>1067</v>
-      </c>
-      <c r="U276" t="s">
-        <v>1068</v>
       </c>
       <c r="V276">
         <v>1.7980571000000001</v>
       </c>
       <c r="W276" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="277" spans="6:23" x14ac:dyDescent="0.2">
@@ -14142,37 +14142,37 @@
         <v>43302</v>
       </c>
       <c r="J277" s="17" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="K277" s="17" t="s">
+        <v>1069</v>
+      </c>
+      <c r="L277" s="17" t="s">
         <v>1070</v>
-      </c>
-      <c r="L277" s="17" t="s">
-        <v>1071</v>
       </c>
       <c r="M277" s="17">
         <v>1.0061370000000001</v>
       </c>
       <c r="N277" s="17" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="R277" s="24">
         <v>45859</v>
       </c>
       <c r="S277" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="T277" t="s">
+        <v>1069</v>
+      </c>
+      <c r="U277" t="s">
         <v>1070</v>
-      </c>
-      <c r="U277" t="s">
-        <v>1071</v>
       </c>
       <c r="V277">
         <v>1.0061370000000001</v>
       </c>
       <c r="W277" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="278" spans="6:23" x14ac:dyDescent="0.2">
@@ -14183,37 +14183,37 @@
         <v>43302</v>
       </c>
       <c r="J278" s="17" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="K278" s="17" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="L278" s="17" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="M278" s="17">
         <v>1.0192787000000001</v>
       </c>
       <c r="N278" s="17" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="R278" s="24">
         <v>45859</v>
       </c>
       <c r="S278" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="T278" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="U278" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="V278">
         <v>1.0192787000000001</v>
       </c>
       <c r="W278" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="279" spans="6:23" x14ac:dyDescent="0.2">
@@ -14227,42 +14227,42 @@
         <v>43302</v>
       </c>
       <c r="J279" s="17" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="K279" s="17" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="L279" s="17" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="M279" s="17">
         <v>1.0262792999999999</v>
       </c>
       <c r="N279" s="17" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="R279" s="24">
         <v>45859</v>
       </c>
       <c r="S279" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="T279" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="U279" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="V279">
         <v>1.0262792999999999</v>
       </c>
       <c r="W279" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="280" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F280" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H280" s="17">
         <v>2018</v>
@@ -14271,42 +14271,42 @@
         <v>43301</v>
       </c>
       <c r="J280" s="17" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="K280" s="17" t="s">
+        <v>1076</v>
+      </c>
+      <c r="L280" s="17" t="s">
         <v>1077</v>
-      </c>
-      <c r="L280" s="17" t="s">
-        <v>1078</v>
       </c>
       <c r="M280" s="17">
         <v>1.8938547999999999</v>
       </c>
       <c r="N280" s="17" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="R280" s="24">
         <v>45858</v>
       </c>
       <c r="S280" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="T280" t="s">
+        <v>1076</v>
+      </c>
+      <c r="U280" t="s">
         <v>1077</v>
-      </c>
-      <c r="U280" t="s">
-        <v>1078</v>
       </c>
       <c r="V280">
         <v>1.8938547999999999</v>
       </c>
       <c r="W280" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="281" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F281" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H281" s="17">
         <v>2018</v>
@@ -14315,42 +14315,42 @@
         <v>43301</v>
       </c>
       <c r="J281" s="17" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="K281" s="17" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="L281" s="17" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="M281" s="17">
         <v>1.7752838</v>
       </c>
       <c r="N281" s="17" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="R281" s="24">
         <v>45858</v>
       </c>
       <c r="S281" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="T281" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="U281" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="V281">
         <v>1.7752838</v>
       </c>
       <c r="W281" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="282" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F282" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H282" s="17">
         <v>2017</v>
@@ -14359,42 +14359,42 @@
         <v>42875</v>
       </c>
       <c r="J282" s="17" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="K282" s="17" t="s">
+        <v>1081</v>
+      </c>
+      <c r="L282" s="17" t="s">
         <v>1082</v>
-      </c>
-      <c r="L282" s="17" t="s">
-        <v>1083</v>
       </c>
       <c r="M282" s="17">
         <v>1.2397396000000001</v>
       </c>
       <c r="N282" s="17" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="R282" s="24">
         <v>45797</v>
       </c>
       <c r="S282" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="T282" t="s">
+        <v>1081</v>
+      </c>
+      <c r="U282" t="s">
         <v>1082</v>
-      </c>
-      <c r="U282" t="s">
-        <v>1083</v>
       </c>
       <c r="V282">
         <v>1.2397396000000001</v>
       </c>
       <c r="W282" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="283" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F283" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H283" s="17">
         <v>2017</v>
@@ -14403,42 +14403,42 @@
         <v>42875</v>
       </c>
       <c r="J283" s="17" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="K283" s="17" t="s">
+        <v>1084</v>
+      </c>
+      <c r="L283" s="17" t="s">
         <v>1085</v>
-      </c>
-      <c r="L283" s="17" t="s">
-        <v>1086</v>
       </c>
       <c r="M283" s="17">
         <v>1.3277483000000001</v>
       </c>
       <c r="N283" s="17" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="R283" s="24">
         <v>45797</v>
       </c>
       <c r="S283" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="T283" t="s">
+        <v>1084</v>
+      </c>
+      <c r="U283" t="s">
         <v>1085</v>
-      </c>
-      <c r="U283" t="s">
-        <v>1086</v>
       </c>
       <c r="V283">
         <v>1.3277483000000001</v>
       </c>
       <c r="W283" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="284" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F284" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H284" s="17">
         <v>2017</v>
@@ -14447,42 +14447,42 @@
         <v>42874</v>
       </c>
       <c r="J284" s="17" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="K284" s="17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="L284" s="17" t="s">
         <v>1088</v>
-      </c>
-      <c r="L284" s="17" t="s">
-        <v>1089</v>
       </c>
       <c r="M284" s="17">
         <v>1.4952688999999999</v>
       </c>
       <c r="N284" s="17" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="R284" s="24">
         <v>45796</v>
       </c>
       <c r="S284" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="T284" t="s">
+        <v>1087</v>
+      </c>
+      <c r="U284" t="s">
         <v>1088</v>
-      </c>
-      <c r="U284" t="s">
-        <v>1089</v>
       </c>
       <c r="V284">
         <v>1.4952688999999999</v>
       </c>
       <c r="W284" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="285" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F285" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H285" s="17">
         <v>2017</v>
@@ -14491,42 +14491,42 @@
         <v>42874</v>
       </c>
       <c r="J285" s="17" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="K285" s="17" t="s">
+        <v>1090</v>
+      </c>
+      <c r="L285" s="17" t="s">
         <v>1091</v>
-      </c>
-      <c r="L285" s="17" t="s">
-        <v>1092</v>
       </c>
       <c r="M285" s="17">
         <v>1.2547427</v>
       </c>
       <c r="N285" s="17" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="R285" s="24">
         <v>45796</v>
       </c>
       <c r="S285" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="T285" t="s">
+        <v>1090</v>
+      </c>
+      <c r="U285" t="s">
         <v>1091</v>
-      </c>
-      <c r="U285" t="s">
-        <v>1092</v>
       </c>
       <c r="V285">
         <v>1.2547427</v>
       </c>
       <c r="W285" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="286" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F286" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H286" s="17">
         <v>2017</v>
@@ -14535,42 +14535,42 @@
         <v>42874</v>
       </c>
       <c r="J286" s="17" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="K286" s="17" t="s">
+        <v>1093</v>
+      </c>
+      <c r="L286" s="17" t="s">
         <v>1094</v>
-      </c>
-      <c r="L286" s="17" t="s">
-        <v>1095</v>
       </c>
       <c r="M286" s="17">
         <v>1.1663190000000001</v>
       </c>
       <c r="N286" s="17" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="R286" s="24">
         <v>45796</v>
       </c>
       <c r="S286" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="T286" t="s">
+        <v>1093</v>
+      </c>
+      <c r="U286" t="s">
         <v>1094</v>
-      </c>
-      <c r="U286" t="s">
-        <v>1095</v>
       </c>
       <c r="V286">
         <v>1.1663190000000001</v>
       </c>
       <c r="W286" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="287" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F287" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H287" s="17">
         <v>2017</v>
@@ -14579,42 +14579,42 @@
         <v>42927</v>
       </c>
       <c r="J287" s="17" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="K287" s="17" t="s">
+        <v>1095</v>
+      </c>
+      <c r="L287" s="17" t="s">
         <v>1096</v>
-      </c>
-      <c r="L287" s="17" t="s">
-        <v>1097</v>
       </c>
       <c r="M287" s="17">
         <v>1.1658386000000001</v>
       </c>
       <c r="N287" s="17" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="R287" s="24">
         <v>45849</v>
       </c>
       <c r="S287" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="T287" t="s">
+        <v>1095</v>
+      </c>
+      <c r="U287" t="s">
         <v>1096</v>
-      </c>
-      <c r="U287" t="s">
-        <v>1097</v>
       </c>
       <c r="V287">
         <v>1.1658386000000001</v>
       </c>
       <c r="W287" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="288" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F288" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H288" s="26">
         <v>2017</v>
@@ -14623,42 +14623,42 @@
         <v>42927</v>
       </c>
       <c r="J288" s="26" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="K288" s="26" t="s">
+        <v>1095</v>
+      </c>
+      <c r="L288" s="26" t="s">
         <v>1096</v>
-      </c>
-      <c r="L288" s="26" t="s">
-        <v>1097</v>
       </c>
       <c r="M288" s="26">
         <v>1.1658386000000001</v>
       </c>
       <c r="N288" s="26" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="R288" s="28">
         <v>45849</v>
       </c>
       <c r="S288" s="10" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="T288" s="10" t="s">
+        <v>1095</v>
+      </c>
+      <c r="U288" s="10" t="s">
         <v>1096</v>
-      </c>
-      <c r="U288" s="10" t="s">
-        <v>1097</v>
       </c>
       <c r="V288" s="10">
         <v>1.1658386000000001</v>
       </c>
       <c r="W288" s="10" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="289" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F289" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H289" s="17">
         <v>2017</v>
@@ -14667,42 +14667,42 @@
         <v>42927</v>
       </c>
       <c r="J289" s="17" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="K289" s="17" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="L289" s="17" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="M289" s="17">
         <v>1.1806829000000001</v>
       </c>
       <c r="N289" s="17" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="R289" s="24">
         <v>45849</v>
       </c>
       <c r="S289" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="T289" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="U289" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="V289">
         <v>1.1806829000000001</v>
       </c>
       <c r="W289" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="290" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F290" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H290" s="17">
         <v>2017</v>
@@ -14711,42 +14711,42 @@
         <v>42927</v>
       </c>
       <c r="J290" s="17" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="K290" s="17" t="s">
+        <v>1101</v>
+      </c>
+      <c r="L290" s="17" t="s">
         <v>1102</v>
-      </c>
-      <c r="L290" s="17" t="s">
-        <v>1103</v>
       </c>
       <c r="M290" s="17">
         <v>1.2610512</v>
       </c>
       <c r="N290" s="17" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="R290" s="24">
         <v>45849</v>
       </c>
       <c r="S290" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="T290" t="s">
+        <v>1101</v>
+      </c>
+      <c r="U290" t="s">
         <v>1102</v>
-      </c>
-      <c r="U290" t="s">
-        <v>1103</v>
       </c>
       <c r="V290">
         <v>1.2610512</v>
       </c>
       <c r="W290" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="291" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F291" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H291" s="17">
         <v>2017</v>
@@ -14755,42 +14755,42 @@
         <v>42927</v>
       </c>
       <c r="J291" s="17" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="K291" s="17" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="L291" s="17" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="M291" s="17">
         <v>1.280257</v>
       </c>
       <c r="N291" s="17" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="R291" s="24">
         <v>45849</v>
       </c>
       <c r="S291" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="T291" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="U291" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="V291">
         <v>1.280257</v>
       </c>
       <c r="W291" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="292" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F292" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H292" s="17">
         <v>2017</v>
@@ -14799,42 +14799,42 @@
         <v>42927</v>
       </c>
       <c r="J292" s="17" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="K292" s="17" t="s">
+        <v>1106</v>
+      </c>
+      <c r="L292" s="17" t="s">
         <v>1107</v>
-      </c>
-      <c r="L292" s="17" t="s">
-        <v>1108</v>
       </c>
       <c r="M292" s="17">
         <v>1.5042374999999999</v>
       </c>
       <c r="N292" s="17" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="R292" s="24">
         <v>45849</v>
       </c>
       <c r="S292" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="T292" t="s">
+        <v>1106</v>
+      </c>
+      <c r="U292" t="s">
         <v>1107</v>
-      </c>
-      <c r="U292" t="s">
-        <v>1108</v>
       </c>
       <c r="V292">
         <v>1.5042374999999999</v>
       </c>
       <c r="W292" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="293" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F293" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H293" s="17">
         <v>2017</v>
@@ -14843,42 +14843,42 @@
         <v>42926</v>
       </c>
       <c r="J293" s="17" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="K293" s="17" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L293" s="17" t="s">
         <v>1110</v>
-      </c>
-      <c r="L293" s="17" t="s">
-        <v>1111</v>
       </c>
       <c r="M293" s="17">
         <v>1.2899497574800001</v>
       </c>
       <c r="N293" s="17" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="R293" s="24">
         <v>45848</v>
       </c>
       <c r="S293" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="T293" t="s">
+        <v>1109</v>
+      </c>
+      <c r="U293" t="s">
         <v>1110</v>
-      </c>
-      <c r="U293" t="s">
-        <v>1111</v>
       </c>
       <c r="V293">
         <v>1.2899497574800001</v>
       </c>
       <c r="W293" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="294" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F294" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H294" s="17">
         <v>2016</v>
@@ -14887,42 +14887,42 @@
         <v>42676</v>
       </c>
       <c r="J294" s="17" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="K294" s="17" t="s">
+        <v>1112</v>
+      </c>
+      <c r="L294" s="17" t="s">
         <v>1113</v>
-      </c>
-      <c r="L294" s="17" t="s">
-        <v>1114</v>
       </c>
       <c r="M294" s="17">
         <v>1.6155265999999999</v>
       </c>
       <c r="N294" s="17" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="R294" s="24">
         <v>45963</v>
       </c>
       <c r="S294" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="T294" t="s">
+        <v>1112</v>
+      </c>
+      <c r="U294" t="s">
         <v>1113</v>
-      </c>
-      <c r="U294" t="s">
-        <v>1114</v>
       </c>
       <c r="V294">
         <v>1.6155265999999999</v>
       </c>
       <c r="W294" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="295" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F295" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H295" s="17">
         <v>2016</v>
@@ -14931,42 +14931,42 @@
         <v>42676</v>
       </c>
       <c r="J295" s="17" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="K295" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="L295" s="17" t="s">
         <v>1116</v>
-      </c>
-      <c r="L295" s="17" t="s">
-        <v>1117</v>
       </c>
       <c r="M295" s="17">
         <v>1.6854796999999999</v>
       </c>
       <c r="N295" s="17" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="R295" s="24">
         <v>45963</v>
       </c>
       <c r="S295" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="T295" t="s">
+        <v>1115</v>
+      </c>
+      <c r="U295" t="s">
         <v>1116</v>
-      </c>
-      <c r="U295" t="s">
-        <v>1117</v>
       </c>
       <c r="V295">
         <v>1.6854796999999999</v>
       </c>
       <c r="W295" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="296" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F296" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H296" s="17">
         <v>2016</v>
@@ -14975,42 +14975,42 @@
         <v>42675</v>
       </c>
       <c r="J296" s="17" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="K296" s="17" t="s">
+        <v>1118</v>
+      </c>
+      <c r="L296" s="17" t="s">
         <v>1119</v>
-      </c>
-      <c r="L296" s="17" t="s">
-        <v>1120</v>
       </c>
       <c r="M296" s="17">
         <v>1.1026252000000001</v>
       </c>
       <c r="N296" s="17" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="R296" s="24">
         <v>45962</v>
       </c>
       <c r="S296" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="T296" t="s">
+        <v>1118</v>
+      </c>
+      <c r="U296" t="s">
         <v>1119</v>
-      </c>
-      <c r="U296" t="s">
-        <v>1120</v>
       </c>
       <c r="V296">
         <v>1.1026252000000001</v>
       </c>
       <c r="W296" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="297" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F297" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H297" s="17">
         <v>2016</v>
@@ -15019,42 +15019,42 @@
         <v>42502</v>
       </c>
       <c r="J297" s="17" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="K297" s="17" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L297" s="17" t="s">
         <v>1122</v>
-      </c>
-      <c r="L297" s="17" t="s">
-        <v>1123</v>
       </c>
       <c r="M297" s="17">
         <v>1.0357352</v>
       </c>
       <c r="N297" s="17" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="R297" s="24">
         <v>45789</v>
       </c>
       <c r="S297" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="T297" t="s">
+        <v>1121</v>
+      </c>
+      <c r="U297" t="s">
         <v>1122</v>
-      </c>
-      <c r="U297" t="s">
-        <v>1123</v>
       </c>
       <c r="V297">
         <v>1.0357352</v>
       </c>
       <c r="W297" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="298" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F298" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H298" s="17">
         <v>2016</v>
@@ -15063,42 +15063,42 @@
         <v>42502</v>
       </c>
       <c r="J298" s="17" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="K298" s="17" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="L298" s="17" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="M298" s="17">
         <v>1.0283884999999999</v>
       </c>
       <c r="N298" s="17" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="R298" s="24">
         <v>45789</v>
       </c>
       <c r="S298" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="T298" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="U298" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="V298">
         <v>1.0283884999999999</v>
       </c>
       <c r="W298" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="299" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F299" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H299" s="17">
         <v>2016</v>
@@ -15107,42 +15107,42 @@
         <v>42502</v>
       </c>
       <c r="J299" s="17" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="K299" s="17" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="L299" s="17" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="M299" s="17">
         <v>1.0366308</v>
       </c>
       <c r="N299" s="17" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="R299" s="24">
         <v>45789</v>
       </c>
       <c r="S299" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="T299" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="U299" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="V299">
         <v>1.0366308</v>
       </c>
       <c r="W299" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="300" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F300" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H300" s="17">
         <v>2016</v>
@@ -15151,37 +15151,37 @@
         <v>42502</v>
       </c>
       <c r="J300" s="17" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="K300" s="17" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="L300" s="17" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="M300" s="17">
         <v>1.0457704000000001</v>
       </c>
       <c r="N300" s="17" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="R300" s="24">
         <v>45789</v>
       </c>
       <c r="S300" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="T300" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="U300" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="V300">
         <v>1.0457704000000001</v>
       </c>
       <c r="W300" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="301" spans="6:23" x14ac:dyDescent="0.2">
@@ -15192,37 +15192,37 @@
         <v>42501</v>
       </c>
       <c r="J301" s="17" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="K301" s="17" t="s">
+        <v>1130</v>
+      </c>
+      <c r="L301" s="17" t="s">
         <v>1131</v>
-      </c>
-      <c r="L301" s="17" t="s">
-        <v>1132</v>
       </c>
       <c r="M301" s="17">
         <v>1.8897699396000001</v>
       </c>
       <c r="N301" s="17" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="R301" s="24">
         <v>45788</v>
       </c>
       <c r="S301" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="T301" t="s">
+        <v>1130</v>
+      </c>
+      <c r="U301" t="s">
         <v>1131</v>
-      </c>
-      <c r="U301" t="s">
-        <v>1132</v>
       </c>
       <c r="V301">
         <v>1.8897699396000001</v>
       </c>
       <c r="W301" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="302" spans="6:23" x14ac:dyDescent="0.2">
@@ -15236,42 +15236,42 @@
         <v>42501</v>
       </c>
       <c r="J302" s="17" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="K302" s="17" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="L302" s="17" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="M302" s="17">
         <v>1.3443974320600001</v>
       </c>
       <c r="N302" s="17" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="R302" s="24">
         <v>45788</v>
       </c>
       <c r="S302" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="T302" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="U302" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="V302">
         <v>1.3443974320600001</v>
       </c>
       <c r="W302" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="303" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F303" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H303" s="17">
         <v>2016</v>
@@ -15280,122 +15280,122 @@
         <v>42501</v>
       </c>
       <c r="J303" s="17" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="K303" s="17" t="s">
+        <v>1135</v>
+      </c>
+      <c r="L303" s="17" t="s">
         <v>1136</v>
-      </c>
-      <c r="L303" s="17" t="s">
-        <v>1137</v>
       </c>
       <c r="M303" s="17">
         <v>1.30832837642</v>
       </c>
       <c r="N303" s="17" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="R303" s="24">
         <v>45788</v>
       </c>
       <c r="S303" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="T303" t="s">
+        <v>1135</v>
+      </c>
+      <c r="U303" t="s">
         <v>1136</v>
-      </c>
-      <c r="U303" t="s">
-        <v>1137</v>
       </c>
       <c r="V303">
         <v>1.30832837642</v>
       </c>
       <c r="W303" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="304" spans="6:23" x14ac:dyDescent="0.2">
       <c r="F304" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="305" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F305" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="306" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F306" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="307" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F307" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="308" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F308" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="309" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F309" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="310" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F310" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="311" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F311" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="312" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F312" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="313" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F313" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="314" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F314" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="315" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F315" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="316" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F316" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="317" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F317" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="318" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F318" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="319" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F319" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="320" spans="6:6" x14ac:dyDescent="0.2">
       <c r="F320" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
   </sheetData>

--- a/windfield_datarecords.xlsx
+++ b/windfield_datarecords.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ahyder/Desktop/windfieldproject/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F168156A-E2FE-2644-9FC7-407AF8DF972D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1CF47E-50F0-2E4A-AF1F-AFFADE31116C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="34560" windowHeight="19880" activeTab="1" xr2:uid="{42A9C88B-2997-EB4C-AFF6-033636F0CE16}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="34560" windowHeight="19880" activeTab="2" xr2:uid="{42A9C88B-2997-EB4C-AFF6-033636F0CE16}"/>
   </bookViews>
   <sheets>
     <sheet name="5µ" sheetId="1" r:id="rId1"/>
     <sheet name="5µ usable by date" sheetId="6" r:id="rId2"/>
-    <sheet name="3.8µ" sheetId="4" r:id="rId3"/>
-    <sheet name="1.69" sheetId="5" r:id="rId4"/>
-    <sheet name="1.64" sheetId="3" r:id="rId5"/>
-    <sheet name="1.58µ" sheetId="2" r:id="rId6"/>
+    <sheet name="5.1µ data tables for paper" sheetId="7" r:id="rId3"/>
+    <sheet name="3.8µ" sheetId="4" r:id="rId4"/>
+    <sheet name="1.69" sheetId="5" r:id="rId5"/>
+    <sheet name="1.64" sheetId="3" r:id="rId6"/>
+    <sheet name="1.58µ" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2768" uniqueCount="1307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="1728">
   <si>
     <t>'''</t>
   </si>
@@ -4040,12 +4041,1275 @@
   <si>
     <t>Used this in HST comparison</t>
   </si>
+  <si>
+    <t>2024-08-17 15:12:28.843750</t>
+  </si>
+  <si>
+    <t>2024-08-17 16:02:25.585940</t>
+  </si>
+  <si>
+    <t>2024-10-23 10:33:15.972660</t>
+  </si>
+  <si>
+    <t>2024-11-24 15:07:04.968750</t>
+  </si>
+  <si>
+    <t>2024-10-23 15:04:59.125000</t>
+  </si>
+  <si>
+    <t>2024-11-24 15:04:35.812500</t>
+  </si>
+  <si>
+    <t>2024-08-17 14:45:15.226560</t>
+  </si>
+  <si>
+    <t>2024-11-23 09:30:52.835940</t>
+  </si>
+  <si>
+    <t>2024-10-22 10:15:05.882810</t>
+  </si>
+  <si>
+    <t>2024-11-23 09:31:41.054690</t>
+  </si>
+  <si>
+    <t>2024-08-16 19:50:05.203120</t>
+  </si>
+  <si>
+    <t>2024-08-16 18:39:46.617190</t>
+  </si>
+  <si>
+    <t>2024-11-23 09:30:10.769530</t>
+  </si>
+  <si>
+    <t>2024-08-16 19:50:08.632810</t>
+  </si>
+  <si>
+    <t>2024-10-22 13:53:25.375000</t>
+  </si>
+  <si>
+    <t>2024-08-16 18:13:34.265620</t>
+  </si>
+  <si>
+    <t>2024-11-23 09:29:27.968750</t>
+  </si>
+  <si>
+    <t>2024-10-22 14:01:56.875000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date [Y/M/D] UTC [hh:mm:ss] </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Filename </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Coadded Images</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc790794 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc763767 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc056062 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc046054 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc039045 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc031037 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc833859 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc057087 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc505516 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc451486 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc055090 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc329353 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc148182 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc042065 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc815843 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc183201 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc649676 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc523554 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc173208 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc507541 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc165200 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc759785 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc575609 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc119154 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc631664 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc773774 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc121154 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc089090 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc19792030 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc19191920 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc18111876 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc17371764 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc16591674 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc347414 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc089118 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc011012 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc786797 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc786793 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc031054 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc265296 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc037056 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc549580 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc10191086 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc895930 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc031066 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc634661 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc031064 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc301326 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc371397 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc10291032 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc233256 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc043076 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc601602 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc491506 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc371372 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc049050 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc090091 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc713732 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc579614 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc081116 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc867902 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc045070 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc231260 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc033055 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc635662 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc483512 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc10491082 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc549584 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc433468 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc193228 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc10251060 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc909922 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc727756 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc607618 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc551572 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc722751 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc065092 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc585618 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc031062 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc155168 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc061096 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc001020 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc721738 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc647666 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc041076 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc633668 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc183206 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc689700 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc585602 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 19:40:14.63 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -21:45:00.71 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc613648 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc001010 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc683718 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc039069 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 16:54:52.80 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -21:58:01.20 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc953894 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc469502 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc383426 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc249282 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc181206 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc069094 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc015034 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc12271254 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc11471172 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc8911014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc925038 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc825860 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc756782 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jc008026 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0017500209 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0004900083 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0000100018 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0137501379 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0129101339 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf08230828 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0078100784 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0061300628 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0056700568 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0031300328 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0011900121 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf149181 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf031065 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf343377 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf161195 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0003700060 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0000100014 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0022700356 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0017700194 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0009900116 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0003100048 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0000100008 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0072300740 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0057500592 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> jcf0053300544 </t>
+  </si>
+  <si>
+    <t>2023-12-29 03:59:21.253910</t>
+  </si>
+  <si>
+    <t>2023-12-28 08:32:28.195310</t>
+  </si>
+  <si>
+    <t>2023-11-24 05:31:46.972660</t>
+  </si>
+  <si>
+    <t>2023-11-23 10:19:39.058590</t>
+  </si>
+  <si>
+    <t>2023-11-23 09:31:30.417970</t>
+  </si>
+  <si>
+    <t>2023-10-15 10:41:36.074220</t>
+  </si>
+  <si>
+    <t>2023-10-14 14:53:00.656250</t>
+  </si>
+  <si>
+    <t>2023-06-24 21:00:39.964683</t>
+  </si>
+  <si>
+    <t>2023-06-23 16:07:05.968750</t>
+  </si>
+  <si>
+    <t>2023-06-23 15:58:38.880361</t>
+  </si>
+  <si>
+    <t>2023-05-17 22:53:42.296880</t>
+  </si>
+  <si>
+    <t>2023-05-17 22:46:13.829701</t>
+  </si>
+  <si>
+    <t>2023-05-17 22:38:47.343750</t>
+  </si>
+  <si>
+    <t>2023-05-17 22:29:52.406250</t>
+  </si>
+  <si>
+    <t>2023-05-17 22:06:58.750000</t>
+  </si>
+  <si>
+    <t>2023-05-17 17:57:56.812500</t>
+  </si>
+  <si>
+    <t>2023-05-17 17:25:30.007810</t>
+  </si>
+  <si>
+    <t>2023-05-17 17:16:47.444566</t>
+  </si>
+  <si>
+    <t>2023-05-16 21:12:07.234380</t>
+  </si>
+  <si>
+    <t>2023-05-16 21:11:50.031250</t>
+  </si>
+  <si>
+    <t>2023-05-16 17:00:52.210940</t>
+  </si>
+  <si>
+    <t>2022-08-18 12:39:31.585940</t>
+  </si>
+  <si>
+    <t>2022-08-18 11:18:53.781250</t>
+  </si>
+  <si>
+    <t>2022-08-17 16:07:14.179690</t>
+  </si>
+  <si>
+    <t>2022-07-09 18:26:03.234380</t>
+  </si>
+  <si>
+    <t>2022-07-09 17:55:44.761720</t>
+  </si>
+  <si>
+    <t>2022-07-09 12:33:54.128910</t>
+  </si>
+  <si>
+    <t>2022-07-08 17:38:07.363280</t>
+  </si>
+  <si>
+    <t>2022-07-08 12:47:34.738280</t>
+  </si>
+  <si>
+    <t>2022-05-22 16:40:38.324220</t>
+  </si>
+  <si>
+    <t>2022-05-21 20:14:36.031250</t>
+  </si>
+  <si>
+    <t>2022-04-09 23:21:04.023440</t>
+  </si>
+  <si>
+    <t>2022-04-09 17:57:11.941410</t>
+  </si>
+  <si>
+    <t>2022-04-09 16:52:32.156250</t>
+  </si>
+  <si>
+    <t>2022-04-08 21:25:34.638229</t>
+  </si>
+  <si>
+    <t>2022-04-08 21:08:07.242190</t>
+  </si>
+  <si>
+    <t>2022-04-08 20:13:19.176874</t>
+  </si>
+  <si>
+    <t>2022-04-08 17:42:41.700440</t>
+  </si>
+  <si>
+    <t>2022-01-15 00:15:28.269233</t>
+  </si>
+  <si>
+    <t>2022-01-14 04:13:52.182620</t>
+  </si>
+  <si>
+    <t>2021-10-18 08:42:59.710940</t>
+  </si>
+  <si>
+    <t>2021-10-18 03:55:02.334960</t>
+  </si>
+  <si>
+    <t>2021-10-17 07:56:01.660160</t>
+  </si>
+  <si>
+    <t>2021-10-17 03:29:26.625000</t>
+  </si>
+  <si>
+    <t>2021-09-05 08:10:11.347660</t>
+  </si>
+  <si>
+    <t>2021-09-05 06:36:38.208980</t>
+  </si>
+  <si>
+    <t>2021-09-04 11:58:34.988280</t>
+  </si>
+  <si>
+    <t>2021-09-04 10:30:38.296880</t>
+  </si>
+  <si>
+    <t>2021-07-22 15:09:04.832000</t>
+  </si>
+  <si>
+    <t>2021-07-22 12:09:23.296880</t>
+  </si>
+  <si>
+    <t>2021-07-22 11:45:25.445310</t>
+  </si>
+  <si>
+    <t>2021-07-22 10:40:13.078120</t>
+  </si>
+  <si>
+    <t>2021-07-22 09:47:48.296880</t>
+  </si>
+  <si>
+    <t>2021-07-21 15:20:34.046880</t>
+  </si>
+  <si>
+    <t>2021-07-21 14:36:14.429690</t>
+  </si>
+  <si>
+    <t>2021-07-21 13:56:38.527340</t>
+  </si>
+  <si>
+    <t>2021-07-21 13:24:14.777340</t>
+  </si>
+  <si>
+    <t>2021-07-21 13:15:43.636720</t>
+  </si>
+  <si>
+    <t>2021-07-21 09:50:37.890620</t>
+  </si>
+  <si>
+    <t>2021-06-08 17:21:07.027340</t>
+  </si>
+  <si>
+    <t>2021-06-08 12:11:29.679690</t>
+  </si>
+  <si>
+    <t>2021-06-07 16:58:28.917970</t>
+  </si>
+  <si>
+    <t>2021-06-07 11:50:44.687500</t>
+  </si>
+  <si>
+    <t>2020-12-24 00:00:57.779740</t>
+  </si>
+  <si>
+    <t>2020-12-23 23:31:09.750000</t>
+  </si>
+  <si>
+    <t>2020-12-23 23:21:49.359380</t>
+  </si>
+  <si>
+    <t>2020-12-23 03:35:57.003910</t>
+  </si>
+  <si>
+    <t>2020-12-23 03:14:53.317380</t>
+  </si>
+  <si>
+    <t>2020-11-11 00:31:54.515260</t>
+  </si>
+  <si>
+    <t>2020-11-10 04:38:25.332030</t>
+  </si>
+  <si>
+    <t>2020-11-08 00:55:56.841800</t>
+  </si>
+  <si>
+    <t>2020-11-07 05:05:15.681640</t>
+  </si>
+  <si>
+    <t>2020-11-07 04:34:30.998050</t>
+  </si>
+  <si>
+    <t>2020-07-05 14:14:03.515620</t>
+  </si>
+  <si>
+    <t>2020-07-05 09:15:51.390620</t>
+  </si>
+  <si>
+    <t>2020-07-05 09:07:51.238280</t>
+  </si>
+  <si>
+    <t>2020-07-04 12:35:00.214840</t>
+  </si>
+  <si>
+    <t>2020-07-04 08:55:42.371090</t>
+  </si>
+  <si>
+    <t>2019-01-17 21:45:18.164060</t>
+  </si>
+  <si>
+    <t>2019-01-17 18:53:07.531250</t>
+  </si>
+  <si>
+    <t>2019-01-17 18:42:09.320310</t>
+  </si>
+  <si>
+    <t>2019-01-17 18:00:25.484380</t>
+  </si>
+  <si>
+    <t>2019-01-17 17:50:09.089840</t>
+  </si>
+  <si>
+    <t>2019-01-17 17:00:46.753910</t>
+  </si>
+  <si>
+    <t>2019-01-17 16:50:59.847660</t>
+  </si>
+  <si>
+    <t>2019-01-16 22:10:21.445310</t>
+  </si>
+  <si>
+    <t>2019-01-16 21:58:21.218750</t>
+  </si>
+  <si>
+    <t>2019-01-16 20:56:58.039060</t>
+  </si>
+  <si>
+    <t>2019-01-16 20:44:11.492190</t>
+  </si>
+  <si>
+    <t>2019-01-16 20:19:46.851560</t>
+  </si>
+  <si>
+    <t>2019-01-16 20:08:55.546880</t>
+  </si>
+  <si>
+    <t>2019-01-16 16:56:25.027340</t>
+  </si>
+  <si>
+    <t>2018-07-21 04:52:48.203120</t>
+  </si>
+  <si>
+    <t>2018-07-21 04:28:23.199220</t>
+  </si>
+  <si>
+    <t>2018-07-21 04:19:20.524410</t>
+  </si>
+  <si>
+    <t>2018-07-20 09:16:21.941410</t>
+  </si>
+  <si>
+    <t>2018-07-20 09:08:39.593750</t>
+  </si>
+  <si>
+    <t>2017-07-11 02:42:58.856450</t>
+  </si>
+  <si>
+    <t>2017-07-11 02:36:27.965820</t>
+  </si>
+  <si>
+    <t>2017-07-11 02:04:58.041500</t>
+  </si>
+  <si>
+    <t>2017-07-11 01:58:27.312303</t>
+  </si>
+  <si>
+    <t>2017-07-11 01:12:26.207520</t>
+  </si>
+  <si>
+    <t>2017-07-10 06:08:46.478520</t>
+  </si>
+  <si>
+    <t>2017-05-20 05:32:27.144530</t>
+  </si>
+  <si>
+    <t>2017-05-20 05:07:17.119140</t>
+  </si>
+  <si>
+    <t>2017-05-19 10:16:58.750000</t>
+  </si>
+  <si>
+    <t>2017-05-19 09:23:22.753910</t>
+  </si>
+  <si>
+    <t>2017-05-19 08:47:58.861330</t>
+  </si>
+  <si>
+    <t>2016-11-02 17:10:07.617190</t>
+  </si>
+  <si>
+    <t>2016-11-02 16:57:24.753910</t>
+  </si>
+  <si>
+    <t>2016-11-01 20:53:38.921880</t>
+  </si>
+  <si>
+    <t>2016-05-12 06:36:01.701170</t>
+  </si>
+  <si>
+    <t>2016-05-12 05:31:39.191410</t>
+  </si>
+  <si>
+    <t>2016-05-12 05:18:23.761720</t>
+  </si>
+  <si>
+    <t>2016-05-12 05:08:57.457030</t>
+  </si>
+  <si>
+    <t>2016-05-11 09:56:21.390620</t>
+  </si>
+  <si>
+    <t>2016-05-11 08:47:33.927730</t>
+  </si>
+  <si>
+    <t>2016-05-11 08:39:34.177730</t>
+  </si>
+  <si>
+    <t>Descending</t>
+  </si>
+  <si>
+    <t>Ascending</t>
+  </si>
+  <si>
+    <t>Sub-Observer Longitude</t>
+  </si>
+  <si>
+    <t>Heliocentric Longitude</t>
+  </si>
+  <si>
+    <t>missing from other table…</t>
+  </si>
+  <si>
+    <t>should be included</t>
+  </si>
+  <si>
+    <t>08:39:34.17</t>
+  </si>
+  <si>
+    <t>08:47:33.92</t>
+  </si>
+  <si>
+    <t>09:56:21.39</t>
+  </si>
+  <si>
+    <t>05:08:57.45</t>
+  </si>
+  <si>
+    <t>05:18:23.76</t>
+  </si>
+  <si>
+    <t>05:31:39.19</t>
+  </si>
+  <si>
+    <t>06:36:01.70</t>
+  </si>
+  <si>
+    <t>20:53:38.92</t>
+  </si>
+  <si>
+    <t>16:57:24.75</t>
+  </si>
+  <si>
+    <t>17:10:07.61</t>
+  </si>
+  <si>
+    <t>08:47:58.86</t>
+  </si>
+  <si>
+    <t>09:23:22.75</t>
+  </si>
+  <si>
+    <t>10:16:58.75</t>
+  </si>
+  <si>
+    <t>05:07:17.11</t>
+  </si>
+  <si>
+    <t>05:32:27.14</t>
+  </si>
+  <si>
+    <t>06:08:46.47</t>
+  </si>
+  <si>
+    <t>01:12:26.20</t>
+  </si>
+  <si>
+    <t>01:58:27.31</t>
+  </si>
+  <si>
+    <t>02:04:58.04</t>
+  </si>
+  <si>
+    <t>02:36:27.96</t>
+  </si>
+  <si>
+    <t>02:42:58.85</t>
+  </si>
+  <si>
+    <t>09:08:39.59</t>
+  </si>
+  <si>
+    <t>09:16:21.94</t>
+  </si>
+  <si>
+    <t>04:19:20.52</t>
+  </si>
+  <si>
+    <t>04:28:23.19</t>
+  </si>
+  <si>
+    <t>04:52:48.20</t>
+  </si>
+  <si>
+    <t>16:56:25.02</t>
+  </si>
+  <si>
+    <t>20:08:55.54</t>
+  </si>
+  <si>
+    <t>20:19:46.85</t>
+  </si>
+  <si>
+    <t>20:44:11.49</t>
+  </si>
+  <si>
+    <t>20:56:58.03</t>
+  </si>
+  <si>
+    <t>21:58:21.21</t>
+  </si>
+  <si>
+    <t>22:10:21.44</t>
+  </si>
+  <si>
+    <t>16:50:59.84</t>
+  </si>
+  <si>
+    <t>17:00:46.75</t>
+  </si>
+  <si>
+    <t>17:50:09.08</t>
+  </si>
+  <si>
+    <t>18:00:25.48</t>
+  </si>
+  <si>
+    <t>18:42:09.32</t>
+  </si>
+  <si>
+    <t>18:53:07.53</t>
+  </si>
+  <si>
+    <t>21:45:18.16</t>
+  </si>
+  <si>
+    <t>08:55:42.37</t>
+  </si>
+  <si>
+    <t>12:35:00.21</t>
+  </si>
+  <si>
+    <t>09:07:51.23</t>
+  </si>
+  <si>
+    <t>09:15:51.39</t>
+  </si>
+  <si>
+    <t>14:14:03.51</t>
+  </si>
+  <si>
+    <t>04:34:30.99</t>
+  </si>
+  <si>
+    <t>05:05:15.68</t>
+  </si>
+  <si>
+    <t>00:55:56.84</t>
+  </si>
+  <si>
+    <t>04:38:25.33</t>
+  </si>
+  <si>
+    <t>00:31:54.51</t>
+  </si>
+  <si>
+    <t>03:14:53.31</t>
+  </si>
+  <si>
+    <t>03:35:57.00</t>
+  </si>
+  <si>
+    <t>23:21:49.35</t>
+  </si>
+  <si>
+    <t>23:31:09.75</t>
+  </si>
+  <si>
+    <t>00:00:57.77</t>
+  </si>
+  <si>
+    <t>11:50:44.68</t>
+  </si>
+  <si>
+    <t>16:58:28.91</t>
+  </si>
+  <si>
+    <t>12:11:29.67</t>
+  </si>
+  <si>
+    <t>17:21:07.02</t>
+  </si>
+  <si>
+    <t>09:50:37.89</t>
+  </si>
+  <si>
+    <t>13:15:43.63</t>
+  </si>
+  <si>
+    <t>13:24:14.77</t>
+  </si>
+  <si>
+    <t>13:56:38.52</t>
+  </si>
+  <si>
+    <t>14:36:14.42</t>
+  </si>
+  <si>
+    <t>15:20:34.04</t>
+  </si>
+  <si>
+    <t>09:47:48.29</t>
+  </si>
+  <si>
+    <t>10:40:13.07</t>
+  </si>
+  <si>
+    <t>11:45:25.44</t>
+  </si>
+  <si>
+    <t>12:09:23.29</t>
+  </si>
+  <si>
+    <t>15:09:04.83</t>
+  </si>
+  <si>
+    <t>10:30:38.29</t>
+  </si>
+  <si>
+    <t>11:58:34.98</t>
+  </si>
+  <si>
+    <t>06:36:38.20</t>
+  </si>
+  <si>
+    <t>08:10:11.34</t>
+  </si>
+  <si>
+    <t>03:29:26.62</t>
+  </si>
+  <si>
+    <t>07:56:01.66</t>
+  </si>
+  <si>
+    <t>03:55:02.33</t>
+  </si>
+  <si>
+    <t>08:42:59.71</t>
+  </si>
+  <si>
+    <t>04:13:52.18</t>
+  </si>
+  <si>
+    <t>00:15:28.26</t>
+  </si>
+  <si>
+    <t>17:42:41.70</t>
+  </si>
+  <si>
+    <t>20:13:19.17</t>
+  </si>
+  <si>
+    <t>21:08:07.24</t>
+  </si>
+  <si>
+    <t>21:25:34.63</t>
+  </si>
+  <si>
+    <t>16:52:32.15</t>
+  </si>
+  <si>
+    <t>17:57:11.94</t>
+  </si>
+  <si>
+    <t>23:21:04.02</t>
+  </si>
+  <si>
+    <t>20:14:36.03</t>
+  </si>
+  <si>
+    <t>16:40:38.32</t>
+  </si>
+  <si>
+    <t>12:47:34.73</t>
+  </si>
+  <si>
+    <t>17:38:07.36</t>
+  </si>
+  <si>
+    <t>12:33:54.12</t>
+  </si>
+  <si>
+    <t>17:55:44.76</t>
+  </si>
+  <si>
+    <t>18:26:03.23</t>
+  </si>
+  <si>
+    <t>16:07:14.17</t>
+  </si>
+  <si>
+    <t>11:18:53.78</t>
+  </si>
+  <si>
+    <t>12:39:31.58</t>
+  </si>
+  <si>
+    <t>17:00:52.21</t>
+  </si>
+  <si>
+    <t>21:11:50.03</t>
+  </si>
+  <si>
+    <t>21:12:07.23</t>
+  </si>
+  <si>
+    <t>17:16:47.44</t>
+  </si>
+  <si>
+    <t>17:25:30.00</t>
+  </si>
+  <si>
+    <t>17:57:56.81</t>
+  </si>
+  <si>
+    <t>22:06:58.75</t>
+  </si>
+  <si>
+    <t>22:29:52.40</t>
+  </si>
+  <si>
+    <t>22:38:47.34</t>
+  </si>
+  <si>
+    <t>22:46:13.82</t>
+  </si>
+  <si>
+    <t>22:53:42.29</t>
+  </si>
+  <si>
+    <t>15:58:38.88</t>
+  </si>
+  <si>
+    <t>16:07:05.96</t>
+  </si>
+  <si>
+    <t>21:00:39.96</t>
+  </si>
+  <si>
+    <t>14:53:00.65</t>
+  </si>
+  <si>
+    <t>10:41:36.07</t>
+  </si>
+  <si>
+    <t>09:31:30.41</t>
+  </si>
+  <si>
+    <t>10:19:39.05</t>
+  </si>
+  <si>
+    <t>05:31:46.97</t>
+  </si>
+  <si>
+    <t>08:32:28.19</t>
+  </si>
+  <si>
+    <t>03:59:21.25</t>
+  </si>
+  <si>
+    <t>18:13:34.26</t>
+  </si>
+  <si>
+    <t>18:39:46.61</t>
+  </si>
+  <si>
+    <t>19:50:05.20</t>
+  </si>
+  <si>
+    <t>19:50:08.63</t>
+  </si>
+  <si>
+    <t>14:45:15.22</t>
+  </si>
+  <si>
+    <t>15:12:28.84</t>
+  </si>
+  <si>
+    <t>16:02:25.58</t>
+  </si>
+  <si>
+    <t>10:15:05.88</t>
+  </si>
+  <si>
+    <t>13:53:25.37</t>
+  </si>
+  <si>
+    <t>14:01:56.87</t>
+  </si>
+  <si>
+    <t>10:33:15.97</t>
+  </si>
+  <si>
+    <t>15:04:59.12</t>
+  </si>
+  <si>
+    <t>09:29:27.96</t>
+  </si>
+  <si>
+    <t>09:30:10.76</t>
+  </si>
+  <si>
+    <t>09:30:52.83</t>
+  </si>
+  <si>
+    <t>09:31:41.05</t>
+  </si>
+  <si>
+    <t>15:04:35.81</t>
+  </si>
+  <si>
+    <t>15:07:04.96</t>
+  </si>
+  <si>
+    <t>UTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> # Coadded Images</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>M/D/Y</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4169,6 +5433,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4208,7 +5479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4265,6 +5536,34 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6652,6 +7951,7 @@
     <col min="21" max="21" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="24.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.2">
@@ -15410,6 +16710,8189 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB650485-41F4-5A4A-A307-ABFD22C1FD52}">
+  <dimension ref="C1:AC141"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.83203125" style="17"/>
+    <col min="22" max="22" width="8.5" style="40" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.6640625" style="40" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21" style="17" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.83203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.83203125" style="40" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20" style="17" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.1640625" style="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+    </row>
+    <row r="2" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="Z2" s="17"/>
+    </row>
+    <row r="3" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C3" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="Z3" s="17"/>
+    </row>
+    <row r="4" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C4" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="Z4" s="17"/>
+    </row>
+    <row r="5" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C5" s="33" t="s">
+        <v>1310</v>
+      </c>
+      <c r="D5" t="s">
+        <v>767</v>
+      </c>
+      <c r="E5" t="s">
+        <v>768</v>
+      </c>
+      <c r="F5">
+        <v>1.7573915</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1328</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="U5" s="18" t="s">
+        <v>1726</v>
+      </c>
+      <c r="V5" s="18" t="s">
+        <v>1727</v>
+      </c>
+      <c r="W5" s="18" t="s">
+        <v>1724</v>
+      </c>
+      <c r="X5" s="18" t="s">
+        <v>1584</v>
+      </c>
+      <c r="Y5" s="18" t="s">
+        <v>1725</v>
+      </c>
+      <c r="Z5" s="18" t="s">
+        <v>1326</v>
+      </c>
+      <c r="AB5" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="AC5" s="1" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="6" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C6" s="33" t="s">
+        <v>1312</v>
+      </c>
+      <c r="D6" t="s">
+        <v>770</v>
+      </c>
+      <c r="E6" t="s">
+        <v>768</v>
+      </c>
+      <c r="F6">
+        <v>1.7299635</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1329</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>1581</v>
+      </c>
+      <c r="L6" s="34">
+        <v>327.31366400000002</v>
+      </c>
+      <c r="M6" s="34">
+        <v>172.94</v>
+      </c>
+      <c r="N6">
+        <v>1.30832837642</v>
+      </c>
+      <c r="O6">
+        <v>6</v>
+      </c>
+      <c r="P6" t="s">
+        <v>1463</v>
+      </c>
+      <c r="U6" s="17">
+        <v>2016</v>
+      </c>
+      <c r="V6" s="38">
+        <v>42501</v>
+      </c>
+      <c r="W6" s="39" t="s">
+        <v>1588</v>
+      </c>
+      <c r="X6" s="46">
+        <v>327.31366400000002</v>
+      </c>
+      <c r="Y6" s="17">
+        <v>6</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>1463</v>
+      </c>
+      <c r="AB6" s="34">
+        <v>172.94</v>
+      </c>
+      <c r="AC6">
+        <v>1.30832837642</v>
+      </c>
+    </row>
+    <row r="7" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C7" s="33" t="s">
+        <v>1316</v>
+      </c>
+      <c r="D7" t="s">
+        <v>762</v>
+      </c>
+      <c r="E7" t="s">
+        <v>763</v>
+      </c>
+      <c r="F7">
+        <v>1.0968245999999999</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="K7" s="33" t="s">
+        <v>1580</v>
+      </c>
+      <c r="L7" s="34">
+        <v>332.14702</v>
+      </c>
+      <c r="M7" s="34">
+        <v>172.94040000000001</v>
+      </c>
+      <c r="N7">
+        <v>1.3443974320600001</v>
+      </c>
+      <c r="O7">
+        <v>9</v>
+      </c>
+      <c r="P7" t="s">
+        <v>1462</v>
+      </c>
+      <c r="V7" s="38">
+        <v>42501</v>
+      </c>
+      <c r="W7" s="39" t="s">
+        <v>1589</v>
+      </c>
+      <c r="X7" s="46">
+        <v>332.14702</v>
+      </c>
+      <c r="Y7" s="17">
+        <v>9</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>1462</v>
+      </c>
+      <c r="AB7" s="34">
+        <v>172.94040000000001</v>
+      </c>
+      <c r="AC7">
+        <v>1.3443974320600001</v>
+      </c>
+    </row>
+    <row r="8" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C8" s="33" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D8" t="s">
+        <v>772</v>
+      </c>
+      <c r="E8" t="s">
+        <v>763</v>
+      </c>
+      <c r="F8">
+        <v>1.0986370000000001</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>1579</v>
+      </c>
+      <c r="L8" s="34">
+        <v>13.730130000000001</v>
+      </c>
+      <c r="M8" s="34">
+        <v>172.94409999999999</v>
+      </c>
+      <c r="N8">
+        <v>1.8897699396000001</v>
+      </c>
+      <c r="O8">
+        <v>9</v>
+      </c>
+      <c r="P8" t="s">
+        <v>1461</v>
+      </c>
+      <c r="V8" s="38">
+        <v>42501</v>
+      </c>
+      <c r="W8" s="39" t="s">
+        <v>1590</v>
+      </c>
+      <c r="X8" s="46">
+        <v>13.730130000000001</v>
+      </c>
+      <c r="Y8" s="17">
+        <v>9</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>1461</v>
+      </c>
+      <c r="AB8" s="34">
+        <v>172.94409999999999</v>
+      </c>
+      <c r="AC8">
+        <v>1.8897699396000001</v>
+      </c>
+    </row>
+    <row r="9" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C9" s="33" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D9" t="s">
+        <v>765</v>
+      </c>
+      <c r="E9" t="s">
+        <v>760</v>
+      </c>
+      <c r="F9">
+        <v>1.0998911</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>1578</v>
+      </c>
+      <c r="L9" s="34">
+        <v>350.45736699999998</v>
+      </c>
+      <c r="M9" s="34">
+        <v>173.00489999999999</v>
+      </c>
+      <c r="N9">
+        <v>1.0457704000000001</v>
+      </c>
+      <c r="O9">
+        <v>4</v>
+      </c>
+      <c r="P9" t="s">
+        <v>1460</v>
+      </c>
+      <c r="V9" s="38">
+        <v>42502</v>
+      </c>
+      <c r="W9" s="39" t="s">
+        <v>1591</v>
+      </c>
+      <c r="X9" s="46">
+        <v>350.45736699999998</v>
+      </c>
+      <c r="Y9" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>1460</v>
+      </c>
+      <c r="AB9" s="34">
+        <v>173.00489999999999</v>
+      </c>
+      <c r="AC9">
+        <v>1.0457704000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C10" s="33" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D10" t="s">
+        <v>759</v>
+      </c>
+      <c r="E10" t="s">
+        <v>760</v>
+      </c>
+      <c r="F10">
+        <v>1.1013264</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1333</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="K10" s="33" t="s">
+        <v>1577</v>
+      </c>
+      <c r="L10" s="34">
+        <v>356.162734</v>
+      </c>
+      <c r="M10" s="34">
+        <v>173.00540000000001</v>
+      </c>
+      <c r="N10">
+        <v>1.0366308</v>
+      </c>
+      <c r="O10">
+        <v>9</v>
+      </c>
+      <c r="P10" t="s">
+        <v>1459</v>
+      </c>
+      <c r="V10" s="38">
+        <v>42502</v>
+      </c>
+      <c r="W10" s="39" t="s">
+        <v>1592</v>
+      </c>
+      <c r="X10" s="46">
+        <v>356.162734</v>
+      </c>
+      <c r="Y10" s="17">
+        <v>9</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>1459</v>
+      </c>
+      <c r="AB10" s="34">
+        <v>173.00540000000001</v>
+      </c>
+      <c r="AC10">
+        <v>1.0366308</v>
+      </c>
+    </row>
+    <row r="11" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C11" s="33" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D11" t="s">
+        <v>777</v>
+      </c>
+      <c r="E11" t="s">
+        <v>778</v>
+      </c>
+      <c r="F11">
+        <v>1.0823919</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H11">
+        <v>12</v>
+      </c>
+      <c r="K11" s="33" t="s">
+        <v>1576</v>
+      </c>
+      <c r="L11" s="34">
+        <v>4.1764729999999997</v>
+      </c>
+      <c r="M11" s="34">
+        <v>173.0061</v>
+      </c>
+      <c r="N11">
+        <v>1.0283884999999999</v>
+      </c>
+      <c r="O11">
+        <v>9</v>
+      </c>
+      <c r="P11" t="s">
+        <v>1458</v>
+      </c>
+      <c r="V11" s="38">
+        <v>42502</v>
+      </c>
+      <c r="W11" s="39" t="s">
+        <v>1593</v>
+      </c>
+      <c r="X11" s="46">
+        <v>4.1764729999999997</v>
+      </c>
+      <c r="Y11" s="17">
+        <v>9</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>1458</v>
+      </c>
+      <c r="AB11" s="34">
+        <v>173.0061</v>
+      </c>
+      <c r="AC11">
+        <v>1.0283884999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C12" s="33" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D12" t="s">
+        <v>783</v>
+      </c>
+      <c r="E12" t="s">
+        <v>784</v>
+      </c>
+      <c r="F12">
+        <v>1.3307070999999999</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1335</v>
+      </c>
+      <c r="H12">
+        <v>9</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>1575</v>
+      </c>
+      <c r="L12" s="34">
+        <v>43.090201999999998</v>
+      </c>
+      <c r="M12" s="34">
+        <v>173.0095</v>
+      </c>
+      <c r="N12">
+        <v>1.0357352</v>
+      </c>
+      <c r="O12">
+        <v>9</v>
+      </c>
+      <c r="P12" t="s">
+        <v>1457</v>
+      </c>
+      <c r="V12" s="38">
+        <v>42502</v>
+      </c>
+      <c r="W12" s="39" t="s">
+        <v>1594</v>
+      </c>
+      <c r="X12" s="46">
+        <v>43.090201999999998</v>
+      </c>
+      <c r="Y12" s="17">
+        <v>9</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>1457</v>
+      </c>
+      <c r="AB12" s="34">
+        <v>173.0095</v>
+      </c>
+      <c r="AC12">
+        <v>1.0357352</v>
+      </c>
+    </row>
+    <row r="13" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C13" s="33" t="s">
+        <v>1324</v>
+      </c>
+      <c r="D13" t="s">
+        <v>786</v>
+      </c>
+      <c r="E13" t="s">
+        <v>775</v>
+      </c>
+      <c r="F13">
+        <v>1.0083826</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1336</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="K13" s="33" t="s">
+        <v>1574</v>
+      </c>
+      <c r="L13" s="34">
+        <v>289.564031</v>
+      </c>
+      <c r="M13" s="34">
+        <v>186.15629999999999</v>
+      </c>
+      <c r="N13">
+        <v>1.1026252000000001</v>
+      </c>
+      <c r="O13">
+        <v>6</v>
+      </c>
+      <c r="P13" t="s">
+        <v>1456</v>
+      </c>
+      <c r="V13" s="38">
+        <v>42675</v>
+      </c>
+      <c r="W13" s="39" t="s">
+        <v>1595</v>
+      </c>
+      <c r="X13" s="46">
+        <v>289.564031</v>
+      </c>
+      <c r="Y13" s="17">
+        <v>6</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>1456</v>
+      </c>
+      <c r="AB13" s="34">
+        <v>186.15629999999999</v>
+      </c>
+      <c r="AC13">
+        <v>1.1026252000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C14" s="33" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D14" t="s">
+        <v>774</v>
+      </c>
+      <c r="E14" t="s">
+        <v>775</v>
+      </c>
+      <c r="F14">
+        <v>1.004407</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H14">
+        <v>16</v>
+      </c>
+      <c r="K14" s="33" t="s">
+        <v>1573</v>
+      </c>
+      <c r="L14" s="34">
+        <v>297.150037</v>
+      </c>
+      <c r="M14" s="34">
+        <v>186.21950000000001</v>
+      </c>
+      <c r="N14">
+        <v>1.6854796999999999</v>
+      </c>
+      <c r="O14">
+        <v>7</v>
+      </c>
+      <c r="P14" t="s">
+        <v>1455</v>
+      </c>
+      <c r="V14" s="38">
+        <v>42676</v>
+      </c>
+      <c r="W14" s="39" t="s">
+        <v>1596</v>
+      </c>
+      <c r="X14" s="46">
+        <v>297.150037</v>
+      </c>
+      <c r="Y14" s="17">
+        <v>7</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>1455</v>
+      </c>
+      <c r="AB14" s="34">
+        <v>186.21950000000001</v>
+      </c>
+      <c r="AC14">
+        <v>1.6854796999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C15" s="33" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D15" t="s">
+        <v>780</v>
+      </c>
+      <c r="E15" t="s">
+        <v>781</v>
+      </c>
+      <c r="F15">
+        <v>1.4519206</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H15">
+        <v>7</v>
+      </c>
+      <c r="K15" s="33" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L15" s="34">
+        <v>304.83497299999999</v>
+      </c>
+      <c r="M15" s="34">
+        <v>186.22020000000001</v>
+      </c>
+      <c r="N15">
+        <v>1.6155265999999999</v>
+      </c>
+      <c r="O15">
+        <v>8</v>
+      </c>
+      <c r="P15" t="s">
+        <v>1454</v>
+      </c>
+      <c r="V15" s="38">
+        <v>42676</v>
+      </c>
+      <c r="W15" s="39" t="s">
+        <v>1597</v>
+      </c>
+      <c r="X15" s="46">
+        <v>304.83497299999999</v>
+      </c>
+      <c r="Y15" s="17">
+        <v>8</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>1454</v>
+      </c>
+      <c r="AB15" s="34">
+        <v>186.22020000000001</v>
+      </c>
+      <c r="AC15">
+        <v>1.6155265999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C16" s="33" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D16" t="s">
+        <v>800</v>
+      </c>
+      <c r="E16" t="s">
+        <v>801</v>
+      </c>
+      <c r="F16">
+        <v>1.078786</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1339</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>1571</v>
+      </c>
+      <c r="L16" s="34">
+        <v>293.17469899999998</v>
+      </c>
+      <c r="M16" s="34">
+        <v>201.14160000000001</v>
+      </c>
+      <c r="N16">
+        <v>1.1663190000000001</v>
+      </c>
+      <c r="O16">
+        <v>15</v>
+      </c>
+      <c r="P16" t="s">
+        <v>1451</v>
+      </c>
+      <c r="U16" s="17">
+        <v>2017</v>
+      </c>
+      <c r="V16" s="38">
+        <v>42874</v>
+      </c>
+      <c r="W16" s="39" t="s">
+        <v>1598</v>
+      </c>
+      <c r="X16" s="44">
+        <v>293.17469899999998</v>
+      </c>
+      <c r="Y16" s="17">
+        <v>15</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>1451</v>
+      </c>
+      <c r="AB16" s="34">
+        <v>201.14160000000001</v>
+      </c>
+      <c r="AC16">
+        <v>1.1663190000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C17" s="33" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D17" t="s">
+        <v>797</v>
+      </c>
+      <c r="E17" t="s">
+        <v>798</v>
+      </c>
+      <c r="F17">
+        <v>1.2049342999999999</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="K17" s="33" t="s">
+        <v>1570</v>
+      </c>
+      <c r="L17" s="34">
+        <v>314.57454000000001</v>
+      </c>
+      <c r="M17" s="34">
+        <v>201.14340000000001</v>
+      </c>
+      <c r="N17">
+        <v>1.2547427</v>
+      </c>
+      <c r="O17">
+        <v>15</v>
+      </c>
+      <c r="P17" t="s">
+        <v>1453</v>
+      </c>
+      <c r="V17" s="38">
+        <v>42874</v>
+      </c>
+      <c r="W17" s="39" t="s">
+        <v>1599</v>
+      </c>
+      <c r="X17" s="44">
+        <v>314.57454000000001</v>
+      </c>
+      <c r="Y17" s="17">
+        <v>15</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>1453</v>
+      </c>
+      <c r="AB17" s="34">
+        <v>201.14340000000001</v>
+      </c>
+      <c r="AC17">
+        <v>1.2547427</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C18" s="33" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D18" t="s">
+        <v>803</v>
+      </c>
+      <c r="E18" t="s">
+        <v>804</v>
+      </c>
+      <c r="F18">
+        <v>1.3062362999999999</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
+      <c r="K18" s="33" t="s">
+        <v>1569</v>
+      </c>
+      <c r="L18" s="34">
+        <v>346.97813400000001</v>
+      </c>
+      <c r="M18" s="34">
+        <v>201.1463</v>
+      </c>
+      <c r="N18">
+        <v>1.4952688999999999</v>
+      </c>
+      <c r="O18">
+        <v>16</v>
+      </c>
+      <c r="P18" t="s">
+        <v>1452</v>
+      </c>
+      <c r="V18" s="38">
+        <v>42874</v>
+      </c>
+      <c r="W18" s="39" t="s">
+        <v>1600</v>
+      </c>
+      <c r="X18" s="44">
+        <v>346.97813400000001</v>
+      </c>
+      <c r="Y18" s="17">
+        <v>16</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>1452</v>
+      </c>
+      <c r="AB18" s="34">
+        <v>201.1463</v>
+      </c>
+      <c r="AC18">
+        <v>1.4952688999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C19" s="33" t="s">
+        <v>1320</v>
+      </c>
+      <c r="D19" t="s">
+        <v>791</v>
+      </c>
+      <c r="E19" t="s">
+        <v>792</v>
+      </c>
+      <c r="F19">
+        <v>1.1615051000000001</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1342</v>
+      </c>
+      <c r="H19">
+        <v>8</v>
+      </c>
+      <c r="K19" s="33" t="s">
+        <v>1568</v>
+      </c>
+      <c r="L19" s="34">
+        <v>310.29655000000002</v>
+      </c>
+      <c r="M19" s="34">
+        <v>201.2055</v>
+      </c>
+      <c r="N19">
+        <v>1.3277483000000001</v>
+      </c>
+      <c r="O19">
+        <v>14</v>
+      </c>
+      <c r="P19" t="s">
+        <v>1451</v>
+      </c>
+      <c r="V19" s="38">
+        <v>42875</v>
+      </c>
+      <c r="W19" s="39" t="s">
+        <v>1601</v>
+      </c>
+      <c r="X19" s="44">
+        <v>310.29655000000002</v>
+      </c>
+      <c r="Y19" s="17">
+        <v>14</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>1451</v>
+      </c>
+      <c r="AB19" s="34">
+        <v>201.2055</v>
+      </c>
+      <c r="AC19">
+        <v>1.3277483000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C20" s="33" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D20" t="s">
+        <v>791</v>
+      </c>
+      <c r="E20" t="s">
+        <v>792</v>
+      </c>
+      <c r="F20">
+        <v>1.1622017</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1343</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
+      <c r="K20" s="33" t="s">
+        <v>1567</v>
+      </c>
+      <c r="L20" s="34">
+        <v>325.51117099999999</v>
+      </c>
+      <c r="M20" s="34">
+        <v>201.20679999999999</v>
+      </c>
+      <c r="N20">
+        <v>1.2397396000000001</v>
+      </c>
+      <c r="O20">
+        <v>14</v>
+      </c>
+      <c r="P20" t="s">
+        <v>1450</v>
+      </c>
+      <c r="V20" s="38">
+        <v>42875</v>
+      </c>
+      <c r="W20" s="39" t="s">
+        <v>1602</v>
+      </c>
+      <c r="X20" s="44">
+        <v>325.51117099999999</v>
+      </c>
+      <c r="Y20" s="17">
+        <v>14</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>1450</v>
+      </c>
+      <c r="AB20" s="34">
+        <v>201.20679999999999</v>
+      </c>
+      <c r="AC20">
+        <v>1.2397396000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C21" s="33" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D21" t="s">
+        <v>788</v>
+      </c>
+      <c r="E21" t="s">
+        <v>789</v>
+      </c>
+      <c r="F21">
+        <v>1.0322026</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H21">
+        <v>9</v>
+      </c>
+      <c r="K21" s="33" t="s">
+        <v>1566</v>
+      </c>
+      <c r="L21" s="34">
+        <v>100.42516000000001</v>
+      </c>
+      <c r="M21" s="34">
+        <v>205.06209999999999</v>
+      </c>
+      <c r="N21">
+        <v>1.2899497574800001</v>
+      </c>
+      <c r="O21">
+        <v>2</v>
+      </c>
+      <c r="P21" t="s">
+        <v>1449</v>
+      </c>
+      <c r="V21" s="38">
+        <v>42926</v>
+      </c>
+      <c r="W21" s="39" t="s">
+        <v>1603</v>
+      </c>
+      <c r="X21" s="44">
+        <v>100.42516000000001</v>
+      </c>
+      <c r="Y21" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>1449</v>
+      </c>
+      <c r="AB21" s="34">
+        <v>205.06209999999999</v>
+      </c>
+      <c r="AC21">
+        <v>1.2899497574800001</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C22" s="33" t="s">
+        <v>1322</v>
+      </c>
+      <c r="D22" t="s">
+        <v>794</v>
+      </c>
+      <c r="E22" t="s">
+        <v>795</v>
+      </c>
+      <c r="F22">
+        <v>1.0105976000000001</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H22">
+        <v>11</v>
+      </c>
+      <c r="K22" s="33" t="s">
+        <v>1565</v>
+      </c>
+      <c r="L22" s="34">
+        <v>71.681901999999994</v>
+      </c>
+      <c r="M22" s="34">
+        <v>205.12209999999999</v>
+      </c>
+      <c r="N22">
+        <v>1.5042374999999999</v>
+      </c>
+      <c r="O22">
+        <v>3</v>
+      </c>
+      <c r="P22" t="s">
+        <v>1448</v>
+      </c>
+      <c r="V22" s="38">
+        <v>42927</v>
+      </c>
+      <c r="W22" s="39" t="s">
+        <v>1604</v>
+      </c>
+      <c r="X22" s="44">
+        <v>71.681901999999994</v>
+      </c>
+      <c r="Y22" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>1448</v>
+      </c>
+      <c r="AB22" s="34">
+        <v>205.12209999999999</v>
+      </c>
+      <c r="AC22">
+        <v>1.5042374999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C23" s="33" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D23" t="s">
+        <v>862</v>
+      </c>
+      <c r="E23" t="s">
+        <v>863</v>
+      </c>
+      <c r="F23">
+        <v>1.1644471999999999</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1346</v>
+      </c>
+      <c r="H23">
+        <v>3</v>
+      </c>
+      <c r="K23" s="33" t="s">
+        <v>1564</v>
+      </c>
+      <c r="L23" s="34">
+        <v>99.496602999999993</v>
+      </c>
+      <c r="M23" s="34">
+        <v>205.12450000000001</v>
+      </c>
+      <c r="N23">
+        <v>1.280257</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23" t="s">
+        <v>1447</v>
+      </c>
+      <c r="V23" s="38">
+        <v>42927</v>
+      </c>
+      <c r="W23" s="39" t="s">
+        <v>1605</v>
+      </c>
+      <c r="X23" s="44">
+        <v>99.496602999999993</v>
+      </c>
+      <c r="Y23" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>1447</v>
+      </c>
+      <c r="AB23" s="34">
+        <v>205.12450000000001</v>
+      </c>
+      <c r="AC23">
+        <v>1.280257</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C24" s="33" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D24" t="s">
+        <v>865</v>
+      </c>
+      <c r="E24" t="s">
+        <v>866</v>
+      </c>
+      <c r="F24">
+        <v>1.2263607999999999</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H24">
+        <v>13</v>
+      </c>
+      <c r="K24" s="33" t="s">
+        <v>1563</v>
+      </c>
+      <c r="L24" s="34">
+        <v>103.432714</v>
+      </c>
+      <c r="M24" s="34">
+        <v>205.1249</v>
+      </c>
+      <c r="N24">
+        <v>1.2610512</v>
+      </c>
+      <c r="O24">
+        <v>3</v>
+      </c>
+      <c r="P24" t="s">
+        <v>1446</v>
+      </c>
+      <c r="V24" s="38">
+        <v>42927</v>
+      </c>
+      <c r="W24" s="39" t="s">
+        <v>1606</v>
+      </c>
+      <c r="X24" s="44">
+        <v>103.432714</v>
+      </c>
+      <c r="Y24" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>1446</v>
+      </c>
+      <c r="AB24" s="34">
+        <v>205.1249</v>
+      </c>
+      <c r="AC24">
+        <v>1.2610512</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C25" s="33" t="s">
+        <v>1466</v>
+      </c>
+      <c r="D25" t="s">
+        <v>816</v>
+      </c>
+      <c r="E25" t="s">
+        <v>817</v>
+      </c>
+      <c r="F25">
+        <v>1.3698440000000001</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+      <c r="K25" s="33" t="s">
+        <v>1562</v>
+      </c>
+      <c r="L25" s="34">
+        <v>122.47135400000001</v>
+      </c>
+      <c r="M25" s="34">
+        <v>205.12649999999999</v>
+      </c>
+      <c r="N25">
+        <v>1.1806829000000001</v>
+      </c>
+      <c r="O25">
+        <v>2</v>
+      </c>
+      <c r="P25" t="s">
+        <v>1445</v>
+      </c>
+      <c r="V25" s="38">
+        <v>42927</v>
+      </c>
+      <c r="W25" s="39" t="s">
+        <v>1607</v>
+      </c>
+      <c r="X25" s="44">
+        <v>122.47135400000001</v>
+      </c>
+      <c r="Y25" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>1445</v>
+      </c>
+      <c r="AB25" s="34">
+        <v>205.12649999999999</v>
+      </c>
+      <c r="AC25">
+        <v>1.1806829000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C26" s="33" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D26" t="s">
+        <v>819</v>
+      </c>
+      <c r="E26" t="s">
+        <v>820</v>
+      </c>
+      <c r="F26">
+        <v>1.1126522999999999</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1349</v>
+      </c>
+      <c r="H26">
+        <v>10</v>
+      </c>
+      <c r="K26" s="33" t="s">
+        <v>1561</v>
+      </c>
+      <c r="L26" s="34">
+        <v>126.409091</v>
+      </c>
+      <c r="M26" s="34">
+        <v>205.1268</v>
+      </c>
+      <c r="N26">
+        <v>1.1658386000000001</v>
+      </c>
+      <c r="O26">
+        <v>3</v>
+      </c>
+      <c r="P26" t="s">
+        <v>1444</v>
+      </c>
+      <c r="V26" s="38">
+        <v>42927</v>
+      </c>
+      <c r="W26" s="39" t="s">
+        <v>1608</v>
+      </c>
+      <c r="X26" s="44">
+        <v>126.409091</v>
+      </c>
+      <c r="Y26" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>1444</v>
+      </c>
+      <c r="AB26" s="34">
+        <v>205.1268</v>
+      </c>
+      <c r="AC26">
+        <v>1.1658386000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C27" s="33" t="s">
+        <v>1468</v>
+      </c>
+      <c r="D27" t="s">
+        <v>813</v>
+      </c>
+      <c r="E27" t="s">
+        <v>814</v>
+      </c>
+      <c r="F27">
+        <v>1.0354473</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1350</v>
+      </c>
+      <c r="H27">
+        <v>15</v>
+      </c>
+      <c r="K27" s="33" t="s">
+        <v>1560</v>
+      </c>
+      <c r="L27" s="34">
+        <v>113.23178299999999</v>
+      </c>
+      <c r="M27" s="34">
+        <v>233.67169999999999</v>
+      </c>
+      <c r="N27">
+        <v>1.7752838</v>
+      </c>
+      <c r="O27">
+        <v>16</v>
+      </c>
+      <c r="P27" t="s">
+        <v>1443</v>
+      </c>
+      <c r="U27" s="17">
+        <v>2018</v>
+      </c>
+      <c r="V27" s="38">
+        <v>43301</v>
+      </c>
+      <c r="W27" s="39" t="s">
+        <v>1609</v>
+      </c>
+      <c r="X27" s="44">
+        <v>113.23178299999999</v>
+      </c>
+      <c r="Y27" s="17">
+        <v>16</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>1443</v>
+      </c>
+      <c r="AB27" s="34">
+        <v>233.67169999999999</v>
+      </c>
+      <c r="AC27">
+        <v>1.7752838</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C28" s="33" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D28" t="s">
+        <v>807</v>
+      </c>
+      <c r="E28" t="s">
+        <v>808</v>
+      </c>
+      <c r="F28">
+        <v>1.0239123000000001</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H28">
+        <v>8</v>
+      </c>
+      <c r="K28" s="33" t="s">
+        <v>1559</v>
+      </c>
+      <c r="L28" s="34">
+        <v>117.889685</v>
+      </c>
+      <c r="M28" s="34">
+        <v>233.6721</v>
+      </c>
+      <c r="N28">
+        <v>1.8938547999999999</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
+      </c>
+      <c r="P28" t="s">
+        <v>1442</v>
+      </c>
+      <c r="V28" s="38">
+        <v>43301</v>
+      </c>
+      <c r="W28" s="39" t="s">
+        <v>1610</v>
+      </c>
+      <c r="X28" s="44">
+        <v>117.889685</v>
+      </c>
+      <c r="Y28" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>1442</v>
+      </c>
+      <c r="AB28" s="34">
+        <v>233.6721</v>
+      </c>
+      <c r="AC28">
+        <v>1.8938547999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C29" s="33" t="s">
+        <v>1470</v>
+      </c>
+      <c r="D29" t="s">
+        <v>810</v>
+      </c>
+      <c r="E29" t="s">
+        <v>811</v>
+      </c>
+      <c r="F29">
+        <v>1.4935601999999999</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H29">
+        <v>7</v>
+      </c>
+      <c r="K29" s="33" t="s">
+        <v>1558</v>
+      </c>
+      <c r="L29" s="34">
+        <v>88.779839999999993</v>
+      </c>
+      <c r="M29" s="34">
+        <v>233.73339999999999</v>
+      </c>
+      <c r="N29">
+        <v>1.0262792999999999</v>
+      </c>
+      <c r="O29">
+        <v>9</v>
+      </c>
+      <c r="P29" t="s">
+        <v>1441</v>
+      </c>
+      <c r="V29" s="38">
+        <v>43302</v>
+      </c>
+      <c r="W29" s="39" t="s">
+        <v>1611</v>
+      </c>
+      <c r="X29" s="44">
+        <v>88.779839999999993</v>
+      </c>
+      <c r="Y29" s="17">
+        <v>9</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>1441</v>
+      </c>
+      <c r="AB29" s="34">
+        <v>233.73339999999999</v>
+      </c>
+      <c r="AC29">
+        <v>1.0262792999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C30" s="33" t="s">
+        <v>1471</v>
+      </c>
+      <c r="D30" t="s">
+        <v>856</v>
+      </c>
+      <c r="E30" t="s">
+        <v>857</v>
+      </c>
+      <c r="F30">
+        <v>1.2380841</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1353</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="33" t="s">
+        <v>1557</v>
+      </c>
+      <c r="L30" s="34">
+        <v>94.246992000000006</v>
+      </c>
+      <c r="M30" s="34">
+        <v>233.7338</v>
+      </c>
+      <c r="N30">
+        <v>1.0192787000000001</v>
+      </c>
+      <c r="O30">
+        <v>18</v>
+      </c>
+      <c r="P30" t="s">
+        <v>1440</v>
+      </c>
+      <c r="V30" s="38">
+        <v>43302</v>
+      </c>
+      <c r="W30" s="39" t="s">
+        <v>1612</v>
+      </c>
+      <c r="X30" s="44">
+        <v>94.246992000000006</v>
+      </c>
+      <c r="Y30" s="17">
+        <v>18</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>1440</v>
+      </c>
+      <c r="AB30" s="34">
+        <v>233.7338</v>
+      </c>
+      <c r="AC30">
+        <v>1.0192787000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C31" s="33" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D31" t="s">
+        <v>853</v>
+      </c>
+      <c r="E31" t="s">
+        <v>854</v>
+      </c>
+      <c r="F31">
+        <v>1.2452220000000001</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1354</v>
+      </c>
+      <c r="H31">
+        <v>10</v>
+      </c>
+      <c r="K31" s="33" t="s">
+        <v>1556</v>
+      </c>
+      <c r="L31" s="34">
+        <v>109.00610500000001</v>
+      </c>
+      <c r="M31" s="34">
+        <v>233.73519999999999</v>
+      </c>
+      <c r="N31">
+        <v>1.0061370000000001</v>
+      </c>
+      <c r="O31">
+        <v>17</v>
+      </c>
+      <c r="P31" t="s">
+        <v>1439</v>
+      </c>
+      <c r="V31" s="38">
+        <v>43302</v>
+      </c>
+      <c r="W31" s="39" t="s">
+        <v>1613</v>
+      </c>
+      <c r="X31" s="44">
+        <v>109.00610500000001</v>
+      </c>
+      <c r="Y31" s="17">
+        <v>17</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>1439</v>
+      </c>
+      <c r="AB31" s="34">
+        <v>233.73519999999999</v>
+      </c>
+      <c r="AC31">
+        <v>1.0061370000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C32" s="33" t="s">
+        <v>1473</v>
+      </c>
+      <c r="D32" t="s">
+        <v>859</v>
+      </c>
+      <c r="E32" t="s">
+        <v>860</v>
+      </c>
+      <c r="F32">
+        <v>1.2735544999999999</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="K32" s="33" t="s">
+        <v>1555</v>
+      </c>
+      <c r="L32" s="34">
+        <v>95.862441000000004</v>
+      </c>
+      <c r="M32" s="34">
+        <v>247.71709999999999</v>
+      </c>
+      <c r="N32">
+        <v>1.7980571000000001</v>
+      </c>
+      <c r="O32">
+        <v>7</v>
+      </c>
+      <c r="P32" t="s">
+        <v>1438</v>
+      </c>
+      <c r="U32" s="17">
+        <v>2019</v>
+      </c>
+      <c r="V32" s="38">
+        <v>43481</v>
+      </c>
+      <c r="W32" s="39" t="s">
+        <v>1614</v>
+      </c>
+      <c r="X32" s="44">
+        <v>95.862441000000004</v>
+      </c>
+      <c r="Y32" s="17">
+        <v>7</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>1438</v>
+      </c>
+      <c r="AB32" s="34">
+        <v>247.71709999999999</v>
+      </c>
+      <c r="AC32">
+        <v>1.7980571000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C33" s="33" t="s">
+        <v>1474</v>
+      </c>
+      <c r="D33" t="s">
+        <v>837</v>
+      </c>
+      <c r="E33" t="s">
+        <v>838</v>
+      </c>
+      <c r="F33">
+        <v>1.2205336</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1356</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="K33" s="33" t="s">
+        <v>1554</v>
+      </c>
+      <c r="L33" s="34">
+        <v>212.22310200000001</v>
+      </c>
+      <c r="M33" s="34">
+        <v>247.7276</v>
+      </c>
+      <c r="N33">
+        <v>1.3547161000000001</v>
+      </c>
+      <c r="O33">
+        <v>5</v>
+      </c>
+      <c r="P33" t="s">
+        <v>1437</v>
+      </c>
+      <c r="V33" s="38">
+        <v>43481</v>
+      </c>
+      <c r="W33" s="39" t="s">
+        <v>1615</v>
+      </c>
+      <c r="X33" s="44">
+        <v>212.22310200000001</v>
+      </c>
+      <c r="Y33" s="17">
+        <v>5</v>
+      </c>
+      <c r="Z33" t="s">
+        <v>1437</v>
+      </c>
+      <c r="AB33" s="34">
+        <v>247.7276</v>
+      </c>
+      <c r="AC33">
+        <v>1.3547161000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C34" s="33" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D34" t="s">
+        <v>831</v>
+      </c>
+      <c r="E34" t="s">
+        <v>832</v>
+      </c>
+      <c r="F34">
+        <v>1.202771</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="K34" s="33" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L34" s="34">
+        <v>218.78438399999999</v>
+      </c>
+      <c r="M34" s="34">
+        <v>247.72819999999999</v>
+      </c>
+      <c r="N34">
+        <v>1.3697168</v>
+      </c>
+      <c r="O34">
+        <v>8</v>
+      </c>
+      <c r="P34" t="s">
+        <v>1436</v>
+      </c>
+      <c r="V34" s="38">
+        <v>43481</v>
+      </c>
+      <c r="W34" s="39" t="s">
+        <v>1616</v>
+      </c>
+      <c r="X34" s="44">
+        <v>218.78438399999999</v>
+      </c>
+      <c r="Y34" s="17">
+        <v>8</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>1436</v>
+      </c>
+      <c r="AB34" s="34">
+        <v>247.72819999999999</v>
+      </c>
+      <c r="AC34">
+        <v>1.3697168</v>
+      </c>
+    </row>
+    <row r="35" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C35" s="33" t="s">
+        <v>1476</v>
+      </c>
+      <c r="D35" t="s">
+        <v>825</v>
+      </c>
+      <c r="E35" t="s">
+        <v>826</v>
+      </c>
+      <c r="F35">
+        <v>1.1717900000000001</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1358</v>
+      </c>
+      <c r="H35">
+        <v>8</v>
+      </c>
+      <c r="K35" s="33" t="s">
+        <v>1552</v>
+      </c>
+      <c r="L35" s="34">
+        <v>233.53926100000001</v>
+      </c>
+      <c r="M35" s="34">
+        <v>247.7295</v>
+      </c>
+      <c r="N35">
+        <v>1.4138792</v>
+      </c>
+      <c r="O35">
+        <v>3</v>
+      </c>
+      <c r="P35" t="s">
+        <v>1435</v>
+      </c>
+      <c r="V35" s="38">
+        <v>43481</v>
+      </c>
+      <c r="W35" s="39" t="s">
+        <v>1617</v>
+      </c>
+      <c r="X35" s="44">
+        <v>233.53926100000001</v>
+      </c>
+      <c r="Y35" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>1435</v>
+      </c>
+      <c r="AB35" s="34">
+        <v>247.7295</v>
+      </c>
+      <c r="AC35">
+        <v>1.4138792</v>
+      </c>
+    </row>
+    <row r="36" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C36" s="33" t="s">
+        <v>1477</v>
+      </c>
+      <c r="D36" t="s">
+        <v>834</v>
+      </c>
+      <c r="E36" t="s">
+        <v>835</v>
+      </c>
+      <c r="F36">
+        <v>1.1510309999999999</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+      <c r="K36" s="33" t="s">
+        <v>1551</v>
+      </c>
+      <c r="L36" s="34">
+        <v>241.26149899999999</v>
+      </c>
+      <c r="M36" s="34">
+        <v>247.7302</v>
+      </c>
+      <c r="N36">
+        <v>1.4515434</v>
+      </c>
+      <c r="O36">
+        <v>6</v>
+      </c>
+      <c r="P36" t="s">
+        <v>1434</v>
+      </c>
+      <c r="V36" s="38">
+        <v>43481</v>
+      </c>
+      <c r="W36" s="39" t="s">
+        <v>1618</v>
+      </c>
+      <c r="X36" s="44">
+        <v>241.26149899999999</v>
+      </c>
+      <c r="Y36" s="17">
+        <v>6</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>1434</v>
+      </c>
+      <c r="AB36" s="34">
+        <v>247.7302</v>
+      </c>
+      <c r="AC36">
+        <v>1.4515434</v>
+      </c>
+    </row>
+    <row r="37" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C37" s="33" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D37" t="s">
+        <v>828</v>
+      </c>
+      <c r="E37" t="s">
+        <v>829</v>
+      </c>
+      <c r="F37">
+        <v>1.100063</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H37">
+        <v>2</v>
+      </c>
+      <c r="K37" s="33" t="s">
+        <v>1550</v>
+      </c>
+      <c r="L37" s="34">
+        <v>278.36605300000002</v>
+      </c>
+      <c r="M37" s="34">
+        <v>247.7336</v>
+      </c>
+      <c r="N37">
+        <v>1.7327911</v>
+      </c>
+      <c r="O37">
+        <v>4</v>
+      </c>
+      <c r="P37" t="s">
+        <v>1433</v>
+      </c>
+      <c r="V37" s="38">
+        <v>43481</v>
+      </c>
+      <c r="W37" s="39" t="s">
+        <v>1619</v>
+      </c>
+      <c r="X37" s="44">
+        <v>278.36605300000002</v>
+      </c>
+      <c r="Y37" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>1433</v>
+      </c>
+      <c r="AB37" s="34">
+        <v>247.7336</v>
+      </c>
+      <c r="AC37">
+        <v>1.7327911</v>
+      </c>
+    </row>
+    <row r="38" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C38" s="33" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D38" t="s">
+        <v>843</v>
+      </c>
+      <c r="E38" t="s">
+        <v>844</v>
+      </c>
+      <c r="F38">
+        <v>1.2806987000000001</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1361</v>
+      </c>
+      <c r="H38">
+        <v>4</v>
+      </c>
+      <c r="K38" s="33" t="s">
+        <v>1549</v>
+      </c>
+      <c r="L38" s="34">
+        <v>285.62165299999998</v>
+      </c>
+      <c r="M38" s="34">
+        <v>247.73419999999999</v>
+      </c>
+      <c r="N38">
+        <v>1.8353286</v>
+      </c>
+      <c r="O38">
+        <v>3</v>
+      </c>
+      <c r="P38" t="s">
+        <v>1432</v>
+      </c>
+      <c r="V38" s="38">
+        <v>43481</v>
+      </c>
+      <c r="W38" s="39" t="s">
+        <v>1620</v>
+      </c>
+      <c r="X38" s="44">
+        <v>285.62165299999998</v>
+      </c>
+      <c r="Y38" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>1432</v>
+      </c>
+      <c r="AB38" s="34">
+        <v>247.73419999999999</v>
+      </c>
+      <c r="AC38">
+        <v>1.8353286</v>
+      </c>
+    </row>
+    <row r="39" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C39" s="33" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D39" t="s">
+        <v>846</v>
+      </c>
+      <c r="E39" t="s">
+        <v>847</v>
+      </c>
+      <c r="F39">
+        <v>1.4454194</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1362</v>
+      </c>
+      <c r="H39">
+        <v>4</v>
+      </c>
+      <c r="K39" s="33" t="s">
+        <v>1548</v>
+      </c>
+      <c r="L39" s="34">
+        <v>242.98397700000001</v>
+      </c>
+      <c r="M39" s="34">
+        <v>247.7954</v>
+      </c>
+      <c r="N39">
+        <v>1.8176920999999999</v>
+      </c>
+      <c r="O39">
+        <v>7</v>
+      </c>
+      <c r="P39" t="s">
+        <v>1431</v>
+      </c>
+      <c r="V39" s="38">
+        <v>43482</v>
+      </c>
+      <c r="W39" s="39" t="s">
+        <v>1621</v>
+      </c>
+      <c r="X39" s="44">
+        <v>242.98397700000001</v>
+      </c>
+      <c r="Y39" s="17">
+        <v>7</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>1431</v>
+      </c>
+      <c r="AB39" s="34">
+        <v>247.7954</v>
+      </c>
+      <c r="AC39">
+        <v>1.8176920999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C40" s="33" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D40" t="s">
+        <v>849</v>
+      </c>
+      <c r="E40" t="s">
+        <v>850</v>
+      </c>
+      <c r="F40">
+        <v>1.4898098</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1363</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="33" t="s">
+        <v>1547</v>
+      </c>
+      <c r="L40" s="34">
+        <v>248.89652000000001</v>
+      </c>
+      <c r="M40" s="34">
+        <v>247.79599999999999</v>
+      </c>
+      <c r="N40">
+        <v>1.7403309</v>
+      </c>
+      <c r="O40">
+        <v>6</v>
+      </c>
+      <c r="P40" t="s">
+        <v>1430</v>
+      </c>
+      <c r="V40" s="38">
+        <v>43482</v>
+      </c>
+      <c r="W40" s="39" t="s">
+        <v>1622</v>
+      </c>
+      <c r="X40" s="44">
+        <v>248.89652000000001</v>
+      </c>
+      <c r="Y40" s="17">
+        <v>6</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>1430</v>
+      </c>
+      <c r="AB40" s="34">
+        <v>247.79599999999999</v>
+      </c>
+      <c r="AC40">
+        <v>1.7403309</v>
+      </c>
+    </row>
+    <row r="41" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C41" s="33" t="s">
+        <v>1482</v>
+      </c>
+      <c r="D41" t="s">
+        <v>822</v>
+      </c>
+      <c r="E41" t="s">
+        <v>823</v>
+      </c>
+      <c r="F41">
+        <v>1.0252433999999999</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1364</v>
+      </c>
+      <c r="H41">
+        <v>3</v>
+      </c>
+      <c r="K41" s="33" t="s">
+        <v>1546</v>
+      </c>
+      <c r="L41" s="34">
+        <v>278.739349</v>
+      </c>
+      <c r="M41" s="34">
+        <v>247.7987</v>
+      </c>
+      <c r="N41">
+        <v>1.4954050000000001</v>
+      </c>
+      <c r="O41">
+        <v>11</v>
+      </c>
+      <c r="P41" t="s">
+        <v>1429</v>
+      </c>
+      <c r="V41" s="38">
+        <v>43482</v>
+      </c>
+      <c r="W41" s="39" t="s">
+        <v>1623</v>
+      </c>
+      <c r="X41" s="44">
+        <v>278.739349</v>
+      </c>
+      <c r="Y41" s="17">
+        <v>11</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>1429</v>
+      </c>
+      <c r="AB41" s="34">
+        <v>247.7987</v>
+      </c>
+      <c r="AC41">
+        <v>1.4954050000000001</v>
+      </c>
+    </row>
+    <row r="42" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C42" s="33" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D42" t="s">
+        <v>822</v>
+      </c>
+      <c r="E42" t="s">
+        <v>823</v>
+      </c>
+      <c r="F42">
+        <v>1.0252433999999999</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="K42" s="33" t="s">
+        <v>1545</v>
+      </c>
+      <c r="L42" s="34">
+        <v>284.94896199999999</v>
+      </c>
+      <c r="M42" s="34">
+        <v>247.79920000000001</v>
+      </c>
+      <c r="N42">
+        <v>1.4576948999999999</v>
+      </c>
+      <c r="O42">
+        <v>16</v>
+      </c>
+      <c r="P42" t="s">
+        <v>1428</v>
+      </c>
+      <c r="V42" s="38">
+        <v>43482</v>
+      </c>
+      <c r="W42" s="39" t="s">
+        <v>1624</v>
+      </c>
+      <c r="X42" s="44">
+        <v>284.94896199999999</v>
+      </c>
+      <c r="Y42" s="17">
+        <v>16</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>1428</v>
+      </c>
+      <c r="AB42" s="34">
+        <v>247.79920000000001</v>
+      </c>
+      <c r="AC42">
+        <v>1.4576948999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C43" s="33" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D43" t="s">
+        <v>840</v>
+      </c>
+      <c r="E43" t="s">
+        <v>841</v>
+      </c>
+      <c r="F43">
+        <v>1.646409</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1366</v>
+      </c>
+      <c r="H43">
+        <v>4</v>
+      </c>
+      <c r="K43" s="33" t="s">
+        <v>1544</v>
+      </c>
+      <c r="L43" s="34">
+        <v>310.17282399999999</v>
+      </c>
+      <c r="M43" s="34">
+        <v>247.8015</v>
+      </c>
+      <c r="N43">
+        <v>1.3717834</v>
+      </c>
+      <c r="O43">
+        <v>12</v>
+      </c>
+      <c r="P43" t="s">
+        <v>1427</v>
+      </c>
+      <c r="V43" s="38">
+        <v>43482</v>
+      </c>
+      <c r="W43" s="39" t="s">
+        <v>1625</v>
+      </c>
+      <c r="X43" s="44">
+        <v>310.17282399999999</v>
+      </c>
+      <c r="Y43" s="17">
+        <v>12</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>1427</v>
+      </c>
+      <c r="AB43" s="34">
+        <v>247.8015</v>
+      </c>
+      <c r="AC43">
+        <v>1.3717834</v>
+      </c>
+    </row>
+    <row r="44" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C44" s="33" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D44" t="s">
+        <v>895</v>
+      </c>
+      <c r="E44" t="s">
+        <v>896</v>
+      </c>
+      <c r="F44">
+        <v>1.056799</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1367</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="K44" s="33" t="s">
+        <v>1543</v>
+      </c>
+      <c r="L44" s="34">
+        <v>316.80369899999999</v>
+      </c>
+      <c r="M44" s="34">
+        <v>247.8021</v>
+      </c>
+      <c r="N44">
+        <v>1.3527285</v>
+      </c>
+      <c r="O44">
+        <v>13</v>
+      </c>
+      <c r="P44" t="s">
+        <v>1426</v>
+      </c>
+      <c r="V44" s="38">
+        <v>43482</v>
+      </c>
+      <c r="W44" s="39" t="s">
+        <v>1626</v>
+      </c>
+      <c r="X44" s="44">
+        <v>316.80369899999999</v>
+      </c>
+      <c r="Y44" s="17">
+        <v>13</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>1426</v>
+      </c>
+      <c r="AB44" s="34">
+        <v>247.8021</v>
+      </c>
+      <c r="AC44">
+        <v>1.3527285</v>
+      </c>
+    </row>
+    <row r="45" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C45" s="33" t="s">
+        <v>1486</v>
+      </c>
+      <c r="D45" t="s">
+        <v>898</v>
+      </c>
+      <c r="E45" t="s">
+        <v>899</v>
+      </c>
+      <c r="F45">
+        <v>1.1725570000000001</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1368</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+      <c r="K45" s="35" t="s">
+        <v>1542</v>
+      </c>
+      <c r="L45" s="36">
+        <v>60.875352999999997</v>
+      </c>
+      <c r="M45" s="36">
+        <v>247.8115</v>
+      </c>
+      <c r="N45" s="37">
+        <v>1.6794370999999999</v>
+      </c>
+      <c r="O45" s="37">
+        <v>5</v>
+      </c>
+      <c r="P45" s="37" t="s">
+        <v>1425</v>
+      </c>
+      <c r="Q45" s="37" t="s">
+        <v>1586</v>
+      </c>
+      <c r="S45" s="37" t="s">
+        <v>1587</v>
+      </c>
+      <c r="V45" s="38">
+        <v>43482</v>
+      </c>
+      <c r="W45" s="39" t="s">
+        <v>1627</v>
+      </c>
+      <c r="X45" s="45">
+        <v>60.875352999999997</v>
+      </c>
+      <c r="Y45" s="41">
+        <v>5</v>
+      </c>
+      <c r="Z45" s="43" t="s">
+        <v>1425</v>
+      </c>
+      <c r="AB45" s="42">
+        <v>247.8115</v>
+      </c>
+      <c r="AC45" s="43">
+        <v>1.6794370999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C46" s="33" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D46" t="s">
+        <v>901</v>
+      </c>
+      <c r="E46" t="s">
+        <v>902</v>
+      </c>
+      <c r="F46">
+        <v>1.4673160000000001</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H46">
+        <v>10</v>
+      </c>
+      <c r="K46" s="33" t="s">
+        <v>1541</v>
+      </c>
+      <c r="L46" s="34">
+        <v>32.875202000000002</v>
+      </c>
+      <c r="M46" s="34">
+        <v>291.21159999999998</v>
+      </c>
+      <c r="N46">
+        <v>1.6473275999999999</v>
+      </c>
+      <c r="O46">
+        <v>13</v>
+      </c>
+      <c r="P46" t="s">
+        <v>1422</v>
+      </c>
+      <c r="U46" s="17">
+        <v>2020</v>
+      </c>
+      <c r="V46" s="38">
+        <v>44016</v>
+      </c>
+      <c r="W46" s="39" t="s">
+        <v>1628</v>
+      </c>
+      <c r="X46" s="44">
+        <v>32.875202000000002</v>
+      </c>
+      <c r="Y46" s="17">
+        <v>13</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>1422</v>
+      </c>
+      <c r="AB46" s="34">
+        <v>291.21159999999998</v>
+      </c>
+      <c r="AC46">
+        <v>1.6473275999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C47" s="33" t="s">
+        <v>1488</v>
+      </c>
+      <c r="D47" t="s">
+        <v>877</v>
+      </c>
+      <c r="E47" t="s">
+        <v>878</v>
+      </c>
+      <c r="F47">
+        <v>1.3792546999999999</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H47">
+        <v>14</v>
+      </c>
+      <c r="K47" s="33" t="s">
+        <v>1540</v>
+      </c>
+      <c r="L47" s="34">
+        <v>165.47091399999999</v>
+      </c>
+      <c r="M47" s="34">
+        <v>291.2244</v>
+      </c>
+      <c r="N47">
+        <v>1.4473488999999999</v>
+      </c>
+      <c r="O47">
+        <v>11</v>
+      </c>
+      <c r="P47" t="s">
+        <v>1421</v>
+      </c>
+      <c r="V47" s="38">
+        <v>44016</v>
+      </c>
+      <c r="W47" s="39" t="s">
+        <v>1629</v>
+      </c>
+      <c r="X47" s="44">
+        <v>165.47091399999999</v>
+      </c>
+      <c r="Y47" s="17">
+        <v>11</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>1421</v>
+      </c>
+      <c r="AB47" s="34">
+        <v>291.2244</v>
+      </c>
+      <c r="AC47">
+        <v>1.4473488999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C48" s="33" t="s">
+        <v>1489</v>
+      </c>
+      <c r="D48" t="s">
+        <v>874</v>
+      </c>
+      <c r="E48" t="s">
+        <v>875</v>
+      </c>
+      <c r="F48">
+        <v>1.2536700999999999</v>
+      </c>
+      <c r="G48" t="s">
+        <v>1371</v>
+      </c>
+      <c r="H48">
+        <v>10</v>
+      </c>
+      <c r="K48" s="33" t="s">
+        <v>1539</v>
+      </c>
+      <c r="L48" s="34">
+        <v>190.896421</v>
+      </c>
+      <c r="M48" s="34">
+        <v>291.29669999999999</v>
+      </c>
+      <c r="N48">
+        <v>1.5576570000000001</v>
+      </c>
+      <c r="O48">
+        <v>4</v>
+      </c>
+      <c r="P48" t="s">
+        <v>1420</v>
+      </c>
+      <c r="V48" s="38">
+        <v>44017</v>
+      </c>
+      <c r="W48" s="39" t="s">
+        <v>1630</v>
+      </c>
+      <c r="X48" s="44">
+        <v>190.896421</v>
+      </c>
+      <c r="Y48" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AB48" s="34">
+        <v>291.29669999999999</v>
+      </c>
+      <c r="AC48">
+        <v>1.5576570000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C49" s="33" t="s">
+        <v>1490</v>
+      </c>
+      <c r="D49" t="s">
+        <v>880</v>
+      </c>
+      <c r="E49" t="s">
+        <v>881</v>
+      </c>
+      <c r="F49">
+        <v>1.5390637</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1372</v>
+      </c>
+      <c r="H49">
+        <v>14</v>
+      </c>
+      <c r="K49" s="33" t="s">
+        <v>1538</v>
+      </c>
+      <c r="L49" s="34">
+        <v>195.73506499999999</v>
+      </c>
+      <c r="M49" s="34">
+        <v>291.29719999999998</v>
+      </c>
+      <c r="N49">
+        <v>1.5276727000000001</v>
+      </c>
+      <c r="O49">
+        <v>11</v>
+      </c>
+      <c r="P49" t="s">
+        <v>1412</v>
+      </c>
+      <c r="V49" s="38">
+        <v>44017</v>
+      </c>
+      <c r="W49" s="39" t="s">
+        <v>1631</v>
+      </c>
+      <c r="X49" s="44">
+        <v>195.73506499999999</v>
+      </c>
+      <c r="Y49" s="17">
+        <v>11</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>1412</v>
+      </c>
+      <c r="AB49" s="34">
+        <v>291.29719999999998</v>
+      </c>
+      <c r="AC49">
+        <v>1.5276727000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C50" s="33" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D50" t="s">
+        <v>883</v>
+      </c>
+      <c r="E50" t="s">
+        <v>884</v>
+      </c>
+      <c r="F50">
+        <v>1.1874081000000001</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H50">
+        <v>10</v>
+      </c>
+      <c r="K50" s="35" t="s">
+        <v>1537</v>
+      </c>
+      <c r="L50" s="36">
+        <v>16.039380000000001</v>
+      </c>
+      <c r="M50" s="36">
+        <v>291.31459999999998</v>
+      </c>
+      <c r="N50" s="37">
+        <v>2.1405261000000002</v>
+      </c>
+      <c r="O50" s="37">
+        <v>8</v>
+      </c>
+      <c r="P50" s="37" t="s">
+        <v>1419</v>
+      </c>
+      <c r="Q50" s="37" t="s">
+        <v>1586</v>
+      </c>
+      <c r="S50" s="37" t="s">
+        <v>1587</v>
+      </c>
+      <c r="V50" s="38">
+        <v>44017</v>
+      </c>
+      <c r="W50" s="39" t="s">
+        <v>1632</v>
+      </c>
+      <c r="X50" s="45">
+        <v>16.039380000000001</v>
+      </c>
+      <c r="Y50" s="41">
+        <v>8</v>
+      </c>
+      <c r="Z50" s="43" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AB50" s="42">
+        <v>291.31459999999998</v>
+      </c>
+      <c r="AC50" s="43">
+        <v>2.1405261000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C51" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D51" t="s">
+        <v>886</v>
+      </c>
+      <c r="E51" t="s">
+        <v>887</v>
+      </c>
+      <c r="F51">
+        <v>1.4707878000000001</v>
+      </c>
+      <c r="G51" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H51">
+        <v>12</v>
+      </c>
+      <c r="K51" s="33" t="s">
+        <v>1536</v>
+      </c>
+      <c r="L51" s="34">
+        <v>117.794659</v>
+      </c>
+      <c r="M51" s="34">
+        <v>301.92140000000001</v>
+      </c>
+      <c r="N51">
+        <v>1.5353939000000001</v>
+      </c>
+      <c r="O51">
+        <v>4</v>
+      </c>
+      <c r="P51" t="s">
+        <v>1416</v>
+      </c>
+      <c r="V51" s="38">
+        <v>44142</v>
+      </c>
+      <c r="W51" s="39" t="s">
+        <v>1633</v>
+      </c>
+      <c r="X51" s="44">
+        <v>117.794659</v>
+      </c>
+      <c r="Y51" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>1416</v>
+      </c>
+      <c r="AB51" s="34">
+        <v>301.92140000000001</v>
+      </c>
+      <c r="AC51">
+        <v>1.5353939000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C52" s="33" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D52" t="s">
+        <v>868</v>
+      </c>
+      <c r="E52" t="s">
+        <v>869</v>
+      </c>
+      <c r="F52">
+        <v>1.1898799</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1375</v>
+      </c>
+      <c r="H52">
+        <v>6</v>
+      </c>
+      <c r="K52" s="33" t="s">
+        <v>1535</v>
+      </c>
+      <c r="L52" s="34">
+        <v>136.37627599999999</v>
+      </c>
+      <c r="M52" s="34">
+        <v>301.92320000000001</v>
+      </c>
+      <c r="N52">
+        <v>1.6940672000000001</v>
+      </c>
+      <c r="O52">
+        <v>6</v>
+      </c>
+      <c r="P52" t="s">
+        <v>1415</v>
+      </c>
+      <c r="V52" s="38">
+        <v>44142</v>
+      </c>
+      <c r="W52" s="39" t="s">
+        <v>1634</v>
+      </c>
+      <c r="X52" s="44">
+        <v>136.37627599999999</v>
+      </c>
+      <c r="Y52" s="17">
+        <v>6</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>1415</v>
+      </c>
+      <c r="AB52" s="34">
+        <v>301.92320000000001</v>
+      </c>
+      <c r="AC52">
+        <v>1.6940672000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C53" s="33" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D53" t="s">
+        <v>871</v>
+      </c>
+      <c r="E53" t="s">
+        <v>872</v>
+      </c>
+      <c r="F53">
+        <v>1.1728333</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H53">
+        <v>3</v>
+      </c>
+      <c r="K53" s="33" t="s">
+        <v>1534</v>
+      </c>
+      <c r="L53" s="34">
+        <v>136.00538</v>
+      </c>
+      <c r="M53" s="34">
+        <v>301.99419999999998</v>
+      </c>
+      <c r="N53">
+        <v>1.8621312999999999</v>
+      </c>
+      <c r="O53">
+        <v>3</v>
+      </c>
+      <c r="P53" t="s">
+        <v>1414</v>
+      </c>
+      <c r="V53" s="38">
+        <v>44143</v>
+      </c>
+      <c r="W53" s="39" t="s">
+        <v>1635</v>
+      </c>
+      <c r="X53" s="44">
+        <v>136.00538</v>
+      </c>
+      <c r="Y53" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z53" t="s">
+        <v>1414</v>
+      </c>
+      <c r="AB53" s="34">
+        <v>301.99419999999998</v>
+      </c>
+      <c r="AC53">
+        <v>1.8621312999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C54" s="33" t="s">
+        <v>1495</v>
+      </c>
+      <c r="D54" t="s">
+        <v>907</v>
+      </c>
+      <c r="E54" t="s">
+        <v>908</v>
+      </c>
+      <c r="F54">
+        <v>1.4134035</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1377</v>
+      </c>
+      <c r="H54">
+        <v>2</v>
+      </c>
+      <c r="K54" s="33" t="s">
+        <v>1533</v>
+      </c>
+      <c r="L54" s="34">
+        <v>211.08145500000001</v>
+      </c>
+      <c r="M54" s="34">
+        <v>302.17930000000001</v>
+      </c>
+      <c r="N54">
+        <v>1.5929922000000001</v>
+      </c>
+      <c r="O54">
+        <v>11</v>
+      </c>
+      <c r="P54" t="s">
+        <v>1413</v>
+      </c>
+      <c r="V54" s="38">
+        <v>44145</v>
+      </c>
+      <c r="W54" s="39" t="s">
+        <v>1636</v>
+      </c>
+      <c r="X54" s="44">
+        <v>211.08145500000001</v>
+      </c>
+      <c r="Y54" s="17">
+        <v>11</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>1413</v>
+      </c>
+      <c r="AB54" s="34">
+        <v>302.17930000000001</v>
+      </c>
+      <c r="AC54">
+        <v>1.5929922000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C55" s="33" t="s">
+        <v>1496</v>
+      </c>
+      <c r="D55" t="s">
+        <v>904</v>
+      </c>
+      <c r="E55" t="s">
+        <v>905</v>
+      </c>
+      <c r="F55">
+        <v>1.4774377999999999</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1378</v>
+      </c>
+      <c r="H55">
+        <v>6</v>
+      </c>
+      <c r="K55" s="33" t="s">
+        <v>1532</v>
+      </c>
+      <c r="L55" s="34">
+        <v>212.39917199999999</v>
+      </c>
+      <c r="M55" s="34">
+        <v>302.25049999999999</v>
+      </c>
+      <c r="N55">
+        <v>1.7808611999999999</v>
+      </c>
+      <c r="O55">
+        <v>11</v>
+      </c>
+      <c r="P55" t="s">
+        <v>1412</v>
+      </c>
+      <c r="V55" s="38">
+        <v>44146</v>
+      </c>
+      <c r="W55" s="39" t="s">
+        <v>1637</v>
+      </c>
+      <c r="X55" s="44">
+        <v>212.39917199999999</v>
+      </c>
+      <c r="Y55" s="17">
+        <v>11</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>1412</v>
+      </c>
+      <c r="AB55" s="34">
+        <v>302.25049999999999</v>
+      </c>
+      <c r="AC55">
+        <v>1.7808611999999999</v>
+      </c>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C56" s="33" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D56" t="s">
+        <v>910</v>
+      </c>
+      <c r="E56" t="s">
+        <v>911</v>
+      </c>
+      <c r="F56">
+        <v>2.1235175000000002</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1379</v>
+      </c>
+      <c r="H56">
+        <v>6</v>
+      </c>
+      <c r="K56" s="33" t="s">
+        <v>1531</v>
+      </c>
+      <c r="L56">
+        <v>142.90604300000001</v>
+      </c>
+      <c r="M56">
+        <v>305.87889999999999</v>
+      </c>
+      <c r="N56">
+        <v>1.8972617000000001</v>
+      </c>
+      <c r="O56">
+        <v>7</v>
+      </c>
+      <c r="P56" t="s">
+        <v>1411</v>
+      </c>
+      <c r="V56" s="38">
+        <v>44188</v>
+      </c>
+      <c r="W56" s="39" t="s">
+        <v>1638</v>
+      </c>
+      <c r="X56" s="44">
+        <v>142.90604300000001</v>
+      </c>
+      <c r="Y56" s="17">
+        <v>7</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>1411</v>
+      </c>
+      <c r="AB56">
+        <v>305.87889999999999</v>
+      </c>
+      <c r="AC56">
+        <v>1.8972617000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C57" s="33" t="s">
+        <v>1498</v>
+      </c>
+      <c r="D57" t="s">
+        <v>913</v>
+      </c>
+      <c r="E57" t="s">
+        <v>914</v>
+      </c>
+      <c r="F57">
+        <v>1.1041605000000001</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="K57" s="33" t="s">
+        <v>1530</v>
+      </c>
+      <c r="L57">
+        <v>155.634738</v>
+      </c>
+      <c r="M57">
+        <v>305.88010000000003</v>
+      </c>
+      <c r="N57">
+        <v>2.1324662000000001</v>
+      </c>
+      <c r="O57">
+        <v>2</v>
+      </c>
+      <c r="P57" t="s">
+        <v>1410</v>
+      </c>
+      <c r="V57" s="38">
+        <v>44188</v>
+      </c>
+      <c r="W57" s="39" t="s">
+        <v>1639</v>
+      </c>
+      <c r="X57" s="44">
+        <v>155.634738</v>
+      </c>
+      <c r="Y57" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>1410</v>
+      </c>
+      <c r="AB57">
+        <v>305.88010000000003</v>
+      </c>
+      <c r="AC57">
+        <v>2.1324662000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C58" s="33" t="s">
+        <v>1499</v>
+      </c>
+      <c r="D58" t="s">
+        <v>916</v>
+      </c>
+      <c r="E58" t="s">
+        <v>917</v>
+      </c>
+      <c r="F58">
+        <v>1.0926659000000001</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1381</v>
+      </c>
+      <c r="H58">
+        <v>3</v>
+      </c>
+      <c r="K58" s="33" t="s">
+        <v>1529</v>
+      </c>
+      <c r="L58">
+        <v>152.32777899999999</v>
+      </c>
+      <c r="M58">
+        <v>305.9513</v>
+      </c>
+      <c r="N58">
+        <v>1.3545707</v>
+      </c>
+      <c r="O58">
+        <v>9</v>
+      </c>
+      <c r="P58" t="s">
+        <v>1409</v>
+      </c>
+      <c r="V58" s="38">
+        <v>44188</v>
+      </c>
+      <c r="W58" s="39" t="s">
+        <v>1640</v>
+      </c>
+      <c r="X58" s="44">
+        <v>152.32777899999999</v>
+      </c>
+      <c r="Y58" s="17">
+        <v>9</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>1409</v>
+      </c>
+      <c r="AB58">
+        <v>305.9513</v>
+      </c>
+      <c r="AC58">
+        <v>1.3545707</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C59" s="33" t="s">
+        <v>1500</v>
+      </c>
+      <c r="D59" t="s">
+        <v>919</v>
+      </c>
+      <c r="E59" t="s">
+        <v>920</v>
+      </c>
+      <c r="F59">
+        <v>1.1012309</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1382</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="K59" s="33" t="s">
+        <v>1528</v>
+      </c>
+      <c r="L59">
+        <v>157.972419</v>
+      </c>
+      <c r="M59">
+        <v>305.95190000000002</v>
+      </c>
+      <c r="N59">
+        <v>1.3397516</v>
+      </c>
+      <c r="O59">
+        <v>15</v>
+      </c>
+      <c r="P59" t="s">
+        <v>1408</v>
+      </c>
+      <c r="V59" s="38">
+        <v>44188</v>
+      </c>
+      <c r="W59" s="39" t="s">
+        <v>1641</v>
+      </c>
+      <c r="X59" s="44">
+        <v>157.972419</v>
+      </c>
+      <c r="Y59" s="17">
+        <v>15</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>1408</v>
+      </c>
+      <c r="AB59">
+        <v>305.95190000000002</v>
+      </c>
+      <c r="AC59">
+        <v>1.3397516</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C60" s="33" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D60" t="s">
+        <v>922</v>
+      </c>
+      <c r="E60" t="s">
+        <v>923</v>
+      </c>
+      <c r="F60">
+        <v>1.5934718999999999</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1383</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="K60" s="33" t="s">
+        <v>1527</v>
+      </c>
+      <c r="L60">
+        <v>175.982685</v>
+      </c>
+      <c r="M60">
+        <v>305.95370000000003</v>
+      </c>
+      <c r="N60">
+        <v>1.3096884</v>
+      </c>
+      <c r="O60">
+        <v>5</v>
+      </c>
+      <c r="P60" t="s">
+        <v>1407</v>
+      </c>
+      <c r="V60" s="38">
+        <v>44189</v>
+      </c>
+      <c r="W60" s="39" t="s">
+        <v>1642</v>
+      </c>
+      <c r="X60" s="44">
+        <v>175.982685</v>
+      </c>
+      <c r="Y60" s="17">
+        <v>5</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>1407</v>
+      </c>
+      <c r="AB60">
+        <v>305.95370000000003</v>
+      </c>
+      <c r="AC60">
+        <v>1.3096884</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C61" s="33" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D61" t="s">
+        <v>889</v>
+      </c>
+      <c r="E61" t="s">
+        <v>890</v>
+      </c>
+      <c r="F61">
+        <v>1.2154286000000001</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1384</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="K61" s="33" t="s">
+        <v>1526</v>
+      </c>
+      <c r="L61">
+        <v>218.951786</v>
+      </c>
+      <c r="M61">
+        <v>320.4101</v>
+      </c>
+      <c r="N61">
+        <v>2.2228183000000001</v>
+      </c>
+      <c r="O61">
+        <v>10</v>
+      </c>
+      <c r="P61" t="s">
+        <v>1406</v>
+      </c>
+      <c r="U61" s="17">
+        <v>2021</v>
+      </c>
+      <c r="V61" s="38">
+        <v>44354</v>
+      </c>
+      <c r="W61" s="39" t="s">
+        <v>1643</v>
+      </c>
+      <c r="X61" s="44">
+        <v>218.951786</v>
+      </c>
+      <c r="Y61" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>1406</v>
+      </c>
+      <c r="AB61">
+        <v>320.4101</v>
+      </c>
+      <c r="AC61">
+        <v>2.2228183000000001</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C62" s="33" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D62" t="s">
+        <v>892</v>
+      </c>
+      <c r="E62" t="s">
+        <v>893</v>
+      </c>
+      <c r="F62">
+        <v>1.7519902999999999</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H62">
+        <v>3</v>
+      </c>
+      <c r="K62" s="33" t="s">
+        <v>1525</v>
+      </c>
+      <c r="L62">
+        <v>44.999026000000001</v>
+      </c>
+      <c r="M62">
+        <v>320.42899999999997</v>
+      </c>
+      <c r="N62">
+        <v>1.2615983</v>
+      </c>
+      <c r="O62">
+        <v>14</v>
+      </c>
+      <c r="P62" t="s">
+        <v>1405</v>
+      </c>
+      <c r="V62" s="38">
+        <v>44354</v>
+      </c>
+      <c r="W62" s="39" t="s">
+        <v>1644</v>
+      </c>
+      <c r="X62" s="44">
+        <v>44.999026000000001</v>
+      </c>
+      <c r="Y62" s="17">
+        <v>14</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>1405</v>
+      </c>
+      <c r="AB62">
+        <v>320.42899999999997</v>
+      </c>
+      <c r="AC62">
+        <v>1.2615983</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C63" s="33" t="s">
+        <v>1504</v>
+      </c>
+      <c r="D63" t="s">
+        <v>931</v>
+      </c>
+      <c r="E63" t="s">
+        <v>932</v>
+      </c>
+      <c r="F63">
+        <v>1.5719418999999999</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1386</v>
+      </c>
+      <c r="H63">
+        <v>18</v>
+      </c>
+      <c r="K63" s="33" t="s">
+        <v>1524</v>
+      </c>
+      <c r="L63">
+        <v>22.068781999999999</v>
+      </c>
+      <c r="M63">
+        <v>320.49970000000002</v>
+      </c>
+      <c r="N63">
+        <v>1.8916166000000001</v>
+      </c>
+      <c r="O63">
+        <v>10</v>
+      </c>
+      <c r="P63" t="s">
+        <v>1404</v>
+      </c>
+      <c r="V63" s="38">
+        <v>44355</v>
+      </c>
+      <c r="W63" s="39" t="s">
+        <v>1645</v>
+      </c>
+      <c r="X63" s="44">
+        <v>22.068781999999999</v>
+      </c>
+      <c r="Y63" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>1404</v>
+      </c>
+      <c r="AB63">
+        <v>320.49970000000002</v>
+      </c>
+      <c r="AC63">
+        <v>1.8916166000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C64" s="33" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D64" t="s">
+        <v>931</v>
+      </c>
+      <c r="E64" t="s">
+        <v>934</v>
+      </c>
+      <c r="F64">
+        <v>1.5199448</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H64">
+        <v>18</v>
+      </c>
+      <c r="K64" s="33" t="s">
+        <v>1523</v>
+      </c>
+      <c r="L64">
+        <v>209.25638900000001</v>
+      </c>
+      <c r="M64">
+        <v>320.51859999999999</v>
+      </c>
+      <c r="N64">
+        <v>1.3366358</v>
+      </c>
+      <c r="O64">
+        <v>11</v>
+      </c>
+      <c r="P64" t="s">
+        <v>1403</v>
+      </c>
+      <c r="V64" s="38">
+        <v>44355</v>
+      </c>
+      <c r="W64" s="39" t="s">
+        <v>1646</v>
+      </c>
+      <c r="X64" s="44">
+        <v>209.25638900000001</v>
+      </c>
+      <c r="Y64" s="17">
+        <v>11</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>1403</v>
+      </c>
+      <c r="AB64">
+        <v>320.51859999999999</v>
+      </c>
+      <c r="AC64">
+        <v>1.3366358</v>
+      </c>
+    </row>
+    <row r="65" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C65" s="33" t="s">
+        <v>1506</v>
+      </c>
+      <c r="D65" t="s">
+        <v>962</v>
+      </c>
+      <c r="E65" t="s">
+        <v>963</v>
+      </c>
+      <c r="F65">
+        <v>1.3515691999999999</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1388</v>
+      </c>
+      <c r="H65">
+        <v>18</v>
+      </c>
+      <c r="K65" s="33" t="s">
+        <v>1522</v>
+      </c>
+      <c r="L65">
+        <v>293.87015100000002</v>
+      </c>
+      <c r="M65">
+        <v>324.29579999999999</v>
+      </c>
+      <c r="N65">
+        <v>1.6192648000000001</v>
+      </c>
+      <c r="O65">
+        <v>10</v>
+      </c>
+      <c r="P65" t="s">
+        <v>1374</v>
+      </c>
+      <c r="V65" s="38">
+        <v>44398</v>
+      </c>
+      <c r="W65" s="39" t="s">
+        <v>1647</v>
+      </c>
+      <c r="X65" s="44">
+        <v>293.87015100000002</v>
+      </c>
+      <c r="Y65" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AB65">
+        <v>324.29579999999999</v>
+      </c>
+      <c r="AC65">
+        <v>1.6192648000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C66" s="33" t="s">
+        <v>1507</v>
+      </c>
+      <c r="D66" t="s">
+        <v>962</v>
+      </c>
+      <c r="E66" t="s">
+        <v>965</v>
+      </c>
+      <c r="F66">
+        <v>1.7066178000000001</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1389</v>
+      </c>
+      <c r="H66">
+        <v>4</v>
+      </c>
+      <c r="K66" s="33" t="s">
+        <v>1521</v>
+      </c>
+      <c r="L66">
+        <v>57.878064999999999</v>
+      </c>
+      <c r="M66">
+        <v>324.30840000000001</v>
+      </c>
+      <c r="N66">
+        <v>1.1973085999999999</v>
+      </c>
+      <c r="O66">
+        <v>7</v>
+      </c>
+      <c r="P66" t="s">
+        <v>1402</v>
+      </c>
+      <c r="V66" s="38">
+        <v>44398</v>
+      </c>
+      <c r="W66" s="39" t="s">
+        <v>1648</v>
+      </c>
+      <c r="X66" s="44">
+        <v>57.878064999999999</v>
+      </c>
+      <c r="Y66" s="17">
+        <v>7</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>1402</v>
+      </c>
+      <c r="AB66">
+        <v>324.30840000000001</v>
+      </c>
+      <c r="AC66">
+        <v>1.1973085999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C67" s="33" t="s">
+        <v>1508</v>
+      </c>
+      <c r="D67" t="s">
+        <v>925</v>
+      </c>
+      <c r="E67" t="s">
+        <v>926</v>
+      </c>
+      <c r="F67">
+        <v>1.2583127999999999</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H67">
+        <v>7</v>
+      </c>
+      <c r="K67" s="33" t="s">
+        <v>1520</v>
+      </c>
+      <c r="L67">
+        <v>63.028948</v>
+      </c>
+      <c r="M67">
+        <v>324.30900000000003</v>
+      </c>
+      <c r="N67">
+        <v>1.2068447</v>
+      </c>
+      <c r="O67">
+        <v>6</v>
+      </c>
+      <c r="P67" t="s">
+        <v>1401</v>
+      </c>
+      <c r="V67" s="38">
+        <v>44398</v>
+      </c>
+      <c r="W67" s="39" t="s">
+        <v>1649</v>
+      </c>
+      <c r="X67" s="44">
+        <v>63.028948</v>
+      </c>
+      <c r="Y67" s="17">
+        <v>6</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>1401</v>
+      </c>
+      <c r="AB67">
+        <v>324.30900000000003</v>
+      </c>
+      <c r="AC67">
+        <v>1.2068447</v>
+      </c>
+    </row>
+    <row r="68" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C68" s="33" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D68" t="s">
+        <v>928</v>
+      </c>
+      <c r="E68" t="s">
+        <v>929</v>
+      </c>
+      <c r="F68">
+        <v>1.6065252000000001</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1391</v>
+      </c>
+      <c r="H68">
+        <v>10</v>
+      </c>
+      <c r="K68" s="33" t="s">
+        <v>1519</v>
+      </c>
+      <c r="L68">
+        <v>82.616562000000002</v>
+      </c>
+      <c r="M68">
+        <v>324.3109</v>
+      </c>
+      <c r="N68">
+        <v>1.2608678</v>
+      </c>
+      <c r="O68">
+        <v>10</v>
+      </c>
+      <c r="P68" t="s">
+        <v>1400</v>
+      </c>
+      <c r="V68" s="38">
+        <v>44398</v>
+      </c>
+      <c r="W68" s="39" t="s">
+        <v>1650</v>
+      </c>
+      <c r="X68" s="44">
+        <v>82.616562000000002</v>
+      </c>
+      <c r="Y68" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>1400</v>
+      </c>
+      <c r="AB68">
+        <v>324.3109</v>
+      </c>
+      <c r="AC68">
+        <v>1.2608678</v>
+      </c>
+    </row>
+    <row r="69" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C69" s="33" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D69" t="s">
+        <v>956</v>
+      </c>
+      <c r="E69" t="s">
+        <v>957</v>
+      </c>
+      <c r="F69">
+        <v>1.6240193000000001</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1392</v>
+      </c>
+      <c r="H69">
+        <v>11</v>
+      </c>
+      <c r="K69" s="33" t="s">
+        <v>1518</v>
+      </c>
+      <c r="L69">
+        <v>106.559065</v>
+      </c>
+      <c r="M69">
+        <v>324.3134</v>
+      </c>
+      <c r="N69">
+        <v>1.3805523</v>
+      </c>
+      <c r="O69">
+        <v>4</v>
+      </c>
+      <c r="P69" t="s">
+        <v>1399</v>
+      </c>
+      <c r="V69" s="38">
+        <v>44398</v>
+      </c>
+      <c r="W69" s="39" t="s">
+        <v>1651</v>
+      </c>
+      <c r="X69" s="44">
+        <v>106.559065</v>
+      </c>
+      <c r="Y69" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>1399</v>
+      </c>
+      <c r="AB69">
+        <v>324.3134</v>
+      </c>
+      <c r="AC69">
+        <v>1.3805523</v>
+      </c>
+    </row>
+    <row r="70" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C70" s="33" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D70" t="s">
+        <v>959</v>
+      </c>
+      <c r="E70" t="s">
+        <v>960</v>
+      </c>
+      <c r="F70">
+        <v>1.2725857</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H70">
+        <v>11</v>
+      </c>
+      <c r="K70" s="33" t="s">
+        <v>1517</v>
+      </c>
+      <c r="L70">
+        <v>133.36061100000001</v>
+      </c>
+      <c r="M70">
+        <v>324.31610000000001</v>
+      </c>
+      <c r="N70">
+        <v>1.6068905</v>
+      </c>
+      <c r="O70">
+        <v>18</v>
+      </c>
+      <c r="P70" t="s">
+        <v>1398</v>
+      </c>
+      <c r="V70" s="38">
+        <v>44398</v>
+      </c>
+      <c r="W70" s="39" t="s">
+        <v>1652</v>
+      </c>
+      <c r="X70" s="44">
+        <v>133.36061100000001</v>
+      </c>
+      <c r="Y70" s="17">
+        <v>18</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>1398</v>
+      </c>
+      <c r="AB70">
+        <v>324.31610000000001</v>
+      </c>
+      <c r="AC70">
+        <v>1.6068905</v>
+      </c>
+    </row>
+    <row r="71" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C71" s="33" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D71" t="s">
+        <v>942</v>
+      </c>
+      <c r="E71" t="s">
+        <v>943</v>
+      </c>
+      <c r="F71">
+        <v>1.5616235999999999</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1394</v>
+      </c>
+      <c r="H71">
+        <v>14</v>
+      </c>
+      <c r="K71" s="33" t="s">
+        <v>1516</v>
+      </c>
+      <c r="L71">
+        <v>82.831462999999999</v>
+      </c>
+      <c r="M71">
+        <v>324.3843</v>
+      </c>
+      <c r="N71">
+        <v>1.6111401000000001</v>
+      </c>
+      <c r="O71">
+        <v>18</v>
+      </c>
+      <c r="P71" t="s">
+        <v>1372</v>
+      </c>
+      <c r="V71" s="38">
+        <v>44399</v>
+      </c>
+      <c r="W71" s="39" t="s">
+        <v>1653</v>
+      </c>
+      <c r="X71" s="44">
+        <v>82.831462999999999</v>
+      </c>
+      <c r="Y71" s="17">
+        <v>18</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>1372</v>
+      </c>
+      <c r="AB71">
+        <v>324.3843</v>
+      </c>
+      <c r="AC71">
+        <v>1.6111401000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C72" s="33" t="s">
+        <v>1513</v>
+      </c>
+      <c r="D72" t="s">
+        <v>945</v>
+      </c>
+      <c r="E72" t="s">
+        <v>946</v>
+      </c>
+      <c r="F72">
+        <v>1.1843096</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H72">
+        <v>12</v>
+      </c>
+      <c r="K72" s="33" t="s">
+        <v>1515</v>
+      </c>
+      <c r="L72">
+        <v>114.522211</v>
+      </c>
+      <c r="M72">
+        <v>324.38749999999999</v>
+      </c>
+      <c r="N72">
+        <v>1.3503057000000001</v>
+      </c>
+      <c r="O72">
+        <v>18</v>
+      </c>
+      <c r="P72" t="s">
+        <v>1397</v>
+      </c>
+      <c r="V72" s="38">
+        <v>44399</v>
+      </c>
+      <c r="W72" s="39" t="s">
+        <v>1654</v>
+      </c>
+      <c r="X72" s="44">
+        <v>114.522211</v>
+      </c>
+      <c r="Y72" s="17">
+        <v>18</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>1397</v>
+      </c>
+      <c r="AB72">
+        <v>324.38749999999999</v>
+      </c>
+      <c r="AC72">
+        <v>1.3503057000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C73" s="33" t="s">
+        <v>1514</v>
+      </c>
+      <c r="D73" t="s">
+        <v>948</v>
+      </c>
+      <c r="E73" t="s">
+        <v>949</v>
+      </c>
+      <c r="F73">
+        <v>1.2036353</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1396</v>
+      </c>
+      <c r="H73">
+        <v>4</v>
+      </c>
+      <c r="K73" s="33" t="s">
+        <v>1514</v>
+      </c>
+      <c r="L73">
+        <v>153.94811899999999</v>
+      </c>
+      <c r="M73">
+        <v>324.39159999999998</v>
+      </c>
+      <c r="N73">
+        <v>1.2036353</v>
+      </c>
+      <c r="O73">
+        <v>4</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1396</v>
+      </c>
+      <c r="V73" s="38">
+        <v>44399</v>
+      </c>
+      <c r="W73" s="39" t="s">
+        <v>1655</v>
+      </c>
+      <c r="X73" s="44">
+        <v>153.94811899999999</v>
+      </c>
+      <c r="Y73" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>1396</v>
+      </c>
+      <c r="AB73">
+        <v>324.39159999999998</v>
+      </c>
+      <c r="AC73">
+        <v>1.2036353</v>
+      </c>
+    </row>
+    <row r="74" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C74" s="33" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D74" t="s">
+        <v>951</v>
+      </c>
+      <c r="E74" t="s">
+        <v>952</v>
+      </c>
+      <c r="F74">
+        <v>1.3503057000000001</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1397</v>
+      </c>
+      <c r="H74">
+        <v>18</v>
+      </c>
+      <c r="K74" s="33" t="s">
+        <v>1513</v>
+      </c>
+      <c r="L74">
+        <v>168.43770900000001</v>
+      </c>
+      <c r="M74">
+        <v>324.39299999999997</v>
+      </c>
+      <c r="N74">
+        <v>1.1843096</v>
+      </c>
+      <c r="O74">
+        <v>12</v>
+      </c>
+      <c r="P74" t="s">
+        <v>1395</v>
+      </c>
+      <c r="V74" s="38">
+        <v>44399</v>
+      </c>
+      <c r="W74" s="39" t="s">
+        <v>1656</v>
+      </c>
+      <c r="X74" s="44">
+        <v>168.43770900000001</v>
+      </c>
+      <c r="Y74" s="17">
+        <v>12</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>1395</v>
+      </c>
+      <c r="AB74">
+        <v>324.39299999999997</v>
+      </c>
+      <c r="AC74">
+        <v>1.1843096</v>
+      </c>
+    </row>
+    <row r="75" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C75" s="33" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D75" t="s">
+        <v>954</v>
+      </c>
+      <c r="E75" t="s">
+        <v>955</v>
+      </c>
+      <c r="F75">
+        <v>1.6111401000000001</v>
+      </c>
+      <c r="G75" t="s">
+        <v>1372</v>
+      </c>
+      <c r="H75">
+        <v>18</v>
+      </c>
+      <c r="K75" s="33" t="s">
+        <v>1512</v>
+      </c>
+      <c r="L75">
+        <v>277.08584300000001</v>
+      </c>
+      <c r="M75">
+        <v>324.40410000000003</v>
+      </c>
+      <c r="N75">
+        <v>1.5616235999999999</v>
+      </c>
+      <c r="O75">
+        <v>14</v>
+      </c>
+      <c r="P75" t="s">
+        <v>1394</v>
+      </c>
+      <c r="V75" s="38">
+        <v>44399</v>
+      </c>
+      <c r="W75" s="39" t="s">
+        <v>1657</v>
+      </c>
+      <c r="X75" s="44">
+        <v>277.08584300000001</v>
+      </c>
+      <c r="Y75" s="17">
+        <v>14</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>1394</v>
+      </c>
+      <c r="AB75">
+        <v>324.40410000000003</v>
+      </c>
+      <c r="AC75">
+        <v>1.5616235999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C76" s="33" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D76" t="s">
+        <v>973</v>
+      </c>
+      <c r="E76" t="s">
+        <v>974</v>
+      </c>
+      <c r="F76">
+        <v>1.6068905</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H76">
+        <v>18</v>
+      </c>
+      <c r="K76" s="33" t="s">
+        <v>1511</v>
+      </c>
+      <c r="L76">
+        <v>258.09946100000002</v>
+      </c>
+      <c r="M76">
+        <v>328.29939999999999</v>
+      </c>
+      <c r="N76">
+        <v>1.2725857</v>
+      </c>
+      <c r="O76">
+        <v>11</v>
+      </c>
+      <c r="P76" t="s">
+        <v>1393</v>
+      </c>
+      <c r="V76" s="38">
+        <v>44443</v>
+      </c>
+      <c r="W76" s="39" t="s">
+        <v>1658</v>
+      </c>
+      <c r="X76" s="44">
+        <v>258.09946100000002</v>
+      </c>
+      <c r="Y76" s="17">
+        <v>11</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>1393</v>
+      </c>
+      <c r="AB76">
+        <v>328.29939999999999</v>
+      </c>
+      <c r="AC76">
+        <v>1.2725857</v>
+      </c>
+    </row>
+    <row r="77" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C77" s="33" t="s">
+        <v>1518</v>
+      </c>
+      <c r="D77" t="s">
+        <v>976</v>
+      </c>
+      <c r="E77" t="s">
+        <v>977</v>
+      </c>
+      <c r="F77">
+        <v>1.3805523</v>
+      </c>
+      <c r="G77" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H77">
+        <v>4</v>
+      </c>
+      <c r="K77" s="33" t="s">
+        <v>1510</v>
+      </c>
+      <c r="L77">
+        <v>311.27162700000002</v>
+      </c>
+      <c r="M77">
+        <v>328.3048</v>
+      </c>
+      <c r="N77">
+        <v>1.6240193000000001</v>
+      </c>
+      <c r="O77">
+        <v>11</v>
+      </c>
+      <c r="P77" t="s">
+        <v>1392</v>
+      </c>
+      <c r="V77" s="38">
+        <v>44443</v>
+      </c>
+      <c r="W77" s="39" t="s">
+        <v>1659</v>
+      </c>
+      <c r="X77" s="44">
+        <v>311.27162700000002</v>
+      </c>
+      <c r="Y77" s="17">
+        <v>11</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>1392</v>
+      </c>
+      <c r="AB77">
+        <v>328.3048</v>
+      </c>
+      <c r="AC77">
+        <v>1.6240193000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C78" s="33" t="s">
+        <v>1519</v>
+      </c>
+      <c r="D78" t="s">
+        <v>979</v>
+      </c>
+      <c r="E78" t="s">
+        <v>980</v>
+      </c>
+      <c r="F78">
+        <v>1.2608678</v>
+      </c>
+      <c r="G78" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H78">
+        <v>10</v>
+      </c>
+      <c r="K78" s="33" t="s">
+        <v>1509</v>
+      </c>
+      <c r="L78">
+        <v>267.252565</v>
+      </c>
+      <c r="M78">
+        <v>328.37400000000002</v>
+      </c>
+      <c r="N78">
+        <v>1.6065252000000001</v>
+      </c>
+      <c r="O78">
+        <v>10</v>
+      </c>
+      <c r="P78" t="s">
+        <v>1391</v>
+      </c>
+      <c r="V78" s="38">
+        <v>44444</v>
+      </c>
+      <c r="W78" s="39" t="s">
+        <v>1660</v>
+      </c>
+      <c r="X78" s="44">
+        <v>267.252565</v>
+      </c>
+      <c r="Y78" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>1391</v>
+      </c>
+      <c r="AB78">
+        <v>328.37400000000002</v>
+      </c>
+      <c r="AC78">
+        <v>1.6065252000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C79" s="33" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D79" t="s">
+        <v>982</v>
+      </c>
+      <c r="E79" t="s">
+        <v>983</v>
+      </c>
+      <c r="F79">
+        <v>1.2068447</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H79">
+        <v>6</v>
+      </c>
+      <c r="K79" s="33" t="s">
+        <v>1508</v>
+      </c>
+      <c r="L79">
+        <v>323.81498099999999</v>
+      </c>
+      <c r="M79">
+        <v>328.37979999999999</v>
+      </c>
+      <c r="N79">
+        <v>1.2583127999999999</v>
+      </c>
+      <c r="O79">
+        <v>7</v>
+      </c>
+      <c r="P79" t="s">
+        <v>1390</v>
+      </c>
+      <c r="V79" s="38">
+        <v>44444</v>
+      </c>
+      <c r="W79" s="39" t="s">
+        <v>1661</v>
+      </c>
+      <c r="X79" s="44">
+        <v>323.81498099999999</v>
+      </c>
+      <c r="Y79" s="17">
+        <v>7</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>1390</v>
+      </c>
+      <c r="AB79">
+        <v>328.37979999999999</v>
+      </c>
+      <c r="AC79">
+        <v>1.2583127999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C80" s="33" t="s">
+        <v>1521</v>
+      </c>
+      <c r="D80" t="s">
+        <v>982</v>
+      </c>
+      <c r="E80" t="s">
+        <v>985</v>
+      </c>
+      <c r="F80">
+        <v>1.1973085999999999</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H80">
+        <v>7</v>
+      </c>
+      <c r="K80" s="33" t="s">
+        <v>1507</v>
+      </c>
+      <c r="L80">
+        <v>357.371241</v>
+      </c>
+      <c r="M80">
+        <v>332.1139</v>
+      </c>
+      <c r="N80">
+        <v>1.7066178000000001</v>
+      </c>
+      <c r="O80">
+        <v>4</v>
+      </c>
+      <c r="P80" t="s">
+        <v>1389</v>
+      </c>
+      <c r="V80" s="38">
+        <v>44486</v>
+      </c>
+      <c r="W80" s="39" t="s">
+        <v>1662</v>
+      </c>
+      <c r="X80" s="44">
+        <v>357.371241</v>
+      </c>
+      <c r="Y80" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>1389</v>
+      </c>
+      <c r="AB80">
+        <v>332.1139</v>
+      </c>
+      <c r="AC80">
+        <v>1.7066178000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C81" s="33" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D81" t="s">
+        <v>987</v>
+      </c>
+      <c r="E81" t="s">
+        <v>988</v>
+      </c>
+      <c r="F81">
+        <v>1.6192648000000001</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H81">
+        <v>10</v>
+      </c>
+      <c r="K81" s="33" t="s">
+        <v>1506</v>
+      </c>
+      <c r="L81">
+        <v>158.51996500000001</v>
+      </c>
+      <c r="M81">
+        <v>332.13049999999998</v>
+      </c>
+      <c r="N81">
+        <v>1.3515691999999999</v>
+      </c>
+      <c r="O81">
+        <v>18</v>
+      </c>
+      <c r="P81" t="s">
+        <v>1388</v>
+      </c>
+      <c r="V81" s="38">
+        <v>44486</v>
+      </c>
+      <c r="W81" s="39" t="s">
+        <v>1663</v>
+      </c>
+      <c r="X81" s="44">
+        <v>158.51996500000001</v>
+      </c>
+      <c r="Y81" s="17">
+        <v>18</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>1388</v>
+      </c>
+      <c r="AB81">
+        <v>332.13049999999998</v>
+      </c>
+      <c r="AC81">
+        <v>1.3515691999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C82" s="33" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D82" t="s">
+        <v>936</v>
+      </c>
+      <c r="E82" t="s">
+        <v>937</v>
+      </c>
+      <c r="F82">
+        <v>1.3366358</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1403</v>
+      </c>
+      <c r="H82">
+        <v>11</v>
+      </c>
+      <c r="K82" s="33" t="s">
+        <v>1505</v>
+      </c>
+      <c r="L82">
+        <v>163.311892</v>
+      </c>
+      <c r="M82">
+        <v>332.20499999999998</v>
+      </c>
+      <c r="N82">
+        <v>1.5199448</v>
+      </c>
+      <c r="O82">
+        <v>18</v>
+      </c>
+      <c r="P82" t="s">
+        <v>1387</v>
+      </c>
+      <c r="V82" s="38">
+        <v>44487</v>
+      </c>
+      <c r="W82" s="39" t="s">
+        <v>1664</v>
+      </c>
+      <c r="X82" s="44">
+        <v>163.311892</v>
+      </c>
+      <c r="Y82" s="17">
+        <v>18</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>1387</v>
+      </c>
+      <c r="AB82">
+        <v>332.20499999999998</v>
+      </c>
+      <c r="AC82">
+        <v>1.5199448</v>
+      </c>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C83" s="33" t="s">
+        <v>1524</v>
+      </c>
+      <c r="D83" t="s">
+        <v>939</v>
+      </c>
+      <c r="E83" t="s">
+        <v>940</v>
+      </c>
+      <c r="F83">
+        <v>1.8916166000000001</v>
+      </c>
+      <c r="G83" t="s">
+        <v>1404</v>
+      </c>
+      <c r="H83">
+        <v>10</v>
+      </c>
+      <c r="K83" s="33" t="s">
+        <v>1504</v>
+      </c>
+      <c r="L83">
+        <v>337.379231</v>
+      </c>
+      <c r="M83">
+        <v>332.22289999999998</v>
+      </c>
+      <c r="N83">
+        <v>1.5719418999999999</v>
+      </c>
+      <c r="O83">
+        <v>18</v>
+      </c>
+      <c r="P83" t="s">
+        <v>1386</v>
+      </c>
+      <c r="V83" s="38">
+        <v>44487</v>
+      </c>
+      <c r="W83" s="39" t="s">
+        <v>1665</v>
+      </c>
+      <c r="X83" s="44">
+        <v>337.379231</v>
+      </c>
+      <c r="Y83" s="17">
+        <v>18</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AB83">
+        <v>332.22289999999998</v>
+      </c>
+      <c r="AC83">
+        <v>1.5719418999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C84" s="33" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D84" t="s">
+        <v>967</v>
+      </c>
+      <c r="E84" t="s">
+        <v>968</v>
+      </c>
+      <c r="F84">
+        <v>1.2615983</v>
+      </c>
+      <c r="G84" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H84">
+        <v>14</v>
+      </c>
+      <c r="K84" s="33" t="s">
+        <v>1503</v>
+      </c>
+      <c r="L84">
+        <v>84.721587</v>
+      </c>
+      <c r="M84">
+        <v>340.11579999999998</v>
+      </c>
+      <c r="N84">
+        <v>1.7519902999999999</v>
+      </c>
+      <c r="O84">
+        <v>3</v>
+      </c>
+      <c r="P84" t="s">
+        <v>1385</v>
+      </c>
+      <c r="U84" s="17">
+        <v>2022</v>
+      </c>
+      <c r="V84" s="38">
+        <v>44575</v>
+      </c>
+      <c r="W84" s="39" t="s">
+        <v>1666</v>
+      </c>
+      <c r="X84" s="44">
+        <v>84.721587</v>
+      </c>
+      <c r="Y84" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>1385</v>
+      </c>
+      <c r="AB84">
+        <v>340.11579999999998</v>
+      </c>
+      <c r="AC84">
+        <v>1.7519902999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C85" s="33" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D85" t="s">
+        <v>970</v>
+      </c>
+      <c r="E85" t="s">
+        <v>971</v>
+      </c>
+      <c r="F85">
+        <v>2.2228183000000001</v>
+      </c>
+      <c r="G85" t="s">
+        <v>1406</v>
+      </c>
+      <c r="H85">
+        <v>10</v>
+      </c>
+      <c r="K85" s="33" t="s">
+        <v>1502</v>
+      </c>
+      <c r="L85">
+        <v>90.916430000000005</v>
+      </c>
+      <c r="M85">
+        <v>340.19110000000001</v>
+      </c>
+      <c r="N85">
+        <v>1.2154286000000001</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85" t="s">
+        <v>1384</v>
+      </c>
+      <c r="V85" s="38">
+        <v>44576</v>
+      </c>
+      <c r="W85" s="39" t="s">
+        <v>1667</v>
+      </c>
+      <c r="X85" s="44">
+        <v>90.916430000000005</v>
+      </c>
+      <c r="Y85" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>1384</v>
+      </c>
+      <c r="AB85">
+        <v>340.19110000000001</v>
+      </c>
+      <c r="AC85">
+        <v>1.2154286000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C86" s="33" t="s">
+        <v>1527</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E86" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F86">
+        <v>1.3096884</v>
+      </c>
+      <c r="G86" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H86">
+        <v>5</v>
+      </c>
+      <c r="K86" s="33" t="s">
+        <v>1501</v>
+      </c>
+      <c r="L86">
+        <v>238.14970400000001</v>
+      </c>
+      <c r="M86">
+        <v>347.77100000000002</v>
+      </c>
+      <c r="N86">
+        <v>1.5934718999999999</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86" t="s">
+        <v>1383</v>
+      </c>
+      <c r="V86" s="38">
+        <v>44659</v>
+      </c>
+      <c r="W86" s="39" t="s">
+        <v>1668</v>
+      </c>
+      <c r="X86" s="44">
+        <v>238.14970400000001</v>
+      </c>
+      <c r="Y86" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>1383</v>
+      </c>
+      <c r="AB86">
+        <v>347.77100000000002</v>
+      </c>
+      <c r="AC86">
+        <v>1.5934718999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C87" s="33" t="s">
+        <v>1528</v>
+      </c>
+      <c r="D87" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E87" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F87">
+        <v>1.3397516</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H87">
+        <v>15</v>
+      </c>
+      <c r="K87" s="33" t="s">
+        <v>1500</v>
+      </c>
+      <c r="L87">
+        <v>329.18794100000002</v>
+      </c>
+      <c r="M87">
+        <v>347.78050000000002</v>
+      </c>
+      <c r="N87">
+        <v>1.1012309</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87" t="s">
+        <v>1382</v>
+      </c>
+      <c r="V87" s="38">
+        <v>44659</v>
+      </c>
+      <c r="W87" s="39" t="s">
+        <v>1669</v>
+      </c>
+      <c r="X87" s="44">
+        <v>329.18794100000002</v>
+      </c>
+      <c r="Y87" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>1382</v>
+      </c>
+      <c r="AB87">
+        <v>347.78050000000002</v>
+      </c>
+      <c r="AC87">
+        <v>1.1012309</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C88" s="33" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E88" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F88">
+        <v>1.3545707</v>
+      </c>
+      <c r="G88" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H88">
+        <v>9</v>
+      </c>
+      <c r="K88" s="33" t="s">
+        <v>1499</v>
+      </c>
+      <c r="L88">
+        <v>2.3099759999999998</v>
+      </c>
+      <c r="M88">
+        <v>347.78399999999999</v>
+      </c>
+      <c r="N88">
+        <v>1.0926659000000001</v>
+      </c>
+      <c r="O88">
+        <v>3</v>
+      </c>
+      <c r="P88" t="s">
+        <v>1381</v>
+      </c>
+      <c r="V88" s="38">
+        <v>44659</v>
+      </c>
+      <c r="W88" s="39" t="s">
+        <v>1670</v>
+      </c>
+      <c r="X88" s="44">
+        <v>2.3099759999999998</v>
+      </c>
+      <c r="Y88" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>1381</v>
+      </c>
+      <c r="AB88">
+        <v>347.78399999999999</v>
+      </c>
+      <c r="AC88">
+        <v>1.0926659000000001</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C89" s="33" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E89" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F89">
+        <v>2.1324662000000001</v>
+      </c>
+      <c r="G89" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H89">
+        <v>2</v>
+      </c>
+      <c r="K89" s="33" t="s">
+        <v>1498</v>
+      </c>
+      <c r="L89">
+        <v>12.860825999999999</v>
+      </c>
+      <c r="M89">
+        <v>347.7851</v>
+      </c>
+      <c r="N89">
+        <v>1.1041605000000001</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89" t="s">
+        <v>1380</v>
+      </c>
+      <c r="V89" s="38">
+        <v>44659</v>
+      </c>
+      <c r="W89" s="39" t="s">
+        <v>1671</v>
+      </c>
+      <c r="X89" s="44">
+        <v>12.860825999999999</v>
+      </c>
+      <c r="Y89" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>1380</v>
+      </c>
+      <c r="AB89">
+        <v>347.7851</v>
+      </c>
+      <c r="AC89">
+        <v>1.1041605000000001</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C90" s="33" t="s">
+        <v>1531</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E90" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F90">
+        <v>1.8972617000000001</v>
+      </c>
+      <c r="G90" t="s">
+        <v>1411</v>
+      </c>
+      <c r="H90">
+        <v>7</v>
+      </c>
+      <c r="K90" s="33" t="s">
+        <v>1497</v>
+      </c>
+      <c r="L90">
+        <v>358.174398</v>
+      </c>
+      <c r="M90">
+        <v>347.8587</v>
+      </c>
+      <c r="N90">
+        <v>2.1235175000000002</v>
+      </c>
+      <c r="O90">
+        <v>6</v>
+      </c>
+      <c r="P90" t="s">
+        <v>1379</v>
+      </c>
+      <c r="V90" s="38">
+        <v>44660</v>
+      </c>
+      <c r="W90" s="39" t="s">
+        <v>1672</v>
+      </c>
+      <c r="X90" s="44">
+        <v>358.174398</v>
+      </c>
+      <c r="Y90" s="17">
+        <v>6</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>1379</v>
+      </c>
+      <c r="AB90">
+        <v>347.8587</v>
+      </c>
+      <c r="AC90">
+        <v>2.1235175000000002</v>
+      </c>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C91" s="33" t="s">
+        <v>1532</v>
+      </c>
+      <c r="D91" t="s">
+        <v>998</v>
+      </c>
+      <c r="E91" t="s">
+        <v>999</v>
+      </c>
+      <c r="F91">
+        <v>1.7808611999999999</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H91">
+        <v>11</v>
+      </c>
+      <c r="K91" s="33" t="s">
+        <v>1496</v>
+      </c>
+      <c r="L91">
+        <v>37.257142999999999</v>
+      </c>
+      <c r="M91">
+        <v>347.86270000000002</v>
+      </c>
+      <c r="N91">
+        <v>1.4774377999999999</v>
+      </c>
+      <c r="O91">
+        <v>6</v>
+      </c>
+      <c r="P91" t="s">
+        <v>1378</v>
+      </c>
+      <c r="V91" s="38">
+        <v>44660</v>
+      </c>
+      <c r="W91" s="39" t="s">
+        <v>1673</v>
+      </c>
+      <c r="X91" s="44">
+        <v>37.257142999999999</v>
+      </c>
+      <c r="Y91" s="17">
+        <v>6</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>1378</v>
+      </c>
+      <c r="AB91">
+        <v>347.86270000000002</v>
+      </c>
+      <c r="AC91">
+        <v>1.4774377999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C92" s="33" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D92" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E92" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F92">
+        <v>1.5929922000000001</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H92">
+        <v>11</v>
+      </c>
+      <c r="K92" s="33" t="s">
+        <v>1495</v>
+      </c>
+      <c r="L92">
+        <v>233.004841</v>
+      </c>
+      <c r="M92">
+        <v>347.88319999999999</v>
+      </c>
+      <c r="N92">
+        <v>1.4134035</v>
+      </c>
+      <c r="O92">
+        <v>2</v>
+      </c>
+      <c r="P92" t="s">
+        <v>1377</v>
+      </c>
+      <c r="V92" s="38">
+        <v>44660</v>
+      </c>
+      <c r="W92" s="39" t="s">
+        <v>1674</v>
+      </c>
+      <c r="X92" s="44">
+        <v>233.004841</v>
+      </c>
+      <c r="Y92" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>1377</v>
+      </c>
+      <c r="AB92">
+        <v>347.88319999999999</v>
+      </c>
+      <c r="AC92">
+        <v>1.4134035</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C93" s="33" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D93" t="s">
+        <v>989</v>
+      </c>
+      <c r="E93" t="s">
+        <v>990</v>
+      </c>
+      <c r="F93">
+        <v>1.8621312999999999</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H93">
+        <v>3</v>
+      </c>
+      <c r="K93" s="33" t="s">
+        <v>1494</v>
+      </c>
+      <c r="L93">
+        <v>316.32023400000003</v>
+      </c>
+      <c r="M93">
+        <v>351.69049999999999</v>
+      </c>
+      <c r="N93">
+        <v>1.1728333</v>
+      </c>
+      <c r="O93">
+        <v>3</v>
+      </c>
+      <c r="P93" t="s">
+        <v>1376</v>
+      </c>
+      <c r="V93" s="38">
+        <v>44702</v>
+      </c>
+      <c r="W93" s="39" t="s">
+        <v>1675</v>
+      </c>
+      <c r="X93" s="44">
+        <v>316.32023400000003</v>
+      </c>
+      <c r="Y93" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>1376</v>
+      </c>
+      <c r="AB93">
+        <v>351.69049999999999</v>
+      </c>
+      <c r="AC93">
+        <v>1.1728333</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C94" s="33" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D94" t="s">
+        <v>992</v>
+      </c>
+      <c r="E94" t="s">
+        <v>993</v>
+      </c>
+      <c r="F94">
+        <v>1.6940672000000001</v>
+      </c>
+      <c r="G94" t="s">
+        <v>1415</v>
+      </c>
+      <c r="H94">
+        <v>6</v>
+      </c>
+      <c r="K94" s="33" t="s">
+        <v>1493</v>
+      </c>
+      <c r="L94">
+        <v>337.41383400000001</v>
+      </c>
+      <c r="M94">
+        <v>351.7681</v>
+      </c>
+      <c r="N94">
+        <v>1.1898799</v>
+      </c>
+      <c r="O94">
+        <v>6</v>
+      </c>
+      <c r="P94" t="s">
+        <v>1375</v>
+      </c>
+      <c r="V94" s="38">
+        <v>44703</v>
+      </c>
+      <c r="W94" s="39" t="s">
+        <v>1676</v>
+      </c>
+      <c r="X94" s="44">
+        <v>337.41383400000001</v>
+      </c>
+      <c r="Y94" s="17">
+        <v>6</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>1375</v>
+      </c>
+      <c r="AB94">
+        <v>351.7681</v>
+      </c>
+      <c r="AC94">
+        <v>1.1898799</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C95" s="33" t="s">
+        <v>1536</v>
+      </c>
+      <c r="D95" t="s">
+        <v>995</v>
+      </c>
+      <c r="E95" t="s">
+        <v>996</v>
+      </c>
+      <c r="F95">
+        <v>1.5353939000000001</v>
+      </c>
+      <c r="G95" t="s">
+        <v>1416</v>
+      </c>
+      <c r="H95">
+        <v>4</v>
+      </c>
+      <c r="K95" s="33" t="s">
+        <v>1492</v>
+      </c>
+      <c r="L95">
+        <v>69.342743999999996</v>
+      </c>
+      <c r="M95">
+        <v>356.03800000000001</v>
+      </c>
+      <c r="N95">
+        <v>1.4707878000000001</v>
+      </c>
+      <c r="O95">
+        <v>12</v>
+      </c>
+      <c r="P95" t="s">
+        <v>1374</v>
+      </c>
+      <c r="V95" s="38">
+        <v>44750</v>
+      </c>
+      <c r="W95" s="39" t="s">
+        <v>1677</v>
+      </c>
+      <c r="X95" s="44">
+        <v>69.342743999999996</v>
+      </c>
+      <c r="Y95" s="17">
+        <v>12</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AB95">
+        <v>356.03800000000001</v>
+      </c>
+      <c r="AC95">
+        <v>1.4707878000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C96" s="33" t="s">
+        <v>1537</v>
+      </c>
+      <c r="D96" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E96" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F96">
+        <v>2.1405261000000002</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H96">
+        <v>8</v>
+      </c>
+      <c r="K96" s="33" t="s">
+        <v>1491</v>
+      </c>
+      <c r="L96">
+        <v>244.990847</v>
+      </c>
+      <c r="M96">
+        <v>356.05650000000003</v>
+      </c>
+      <c r="N96">
+        <v>1.1874081000000001</v>
+      </c>
+      <c r="O96">
+        <v>10</v>
+      </c>
+      <c r="P96" t="s">
+        <v>1373</v>
+      </c>
+      <c r="V96" s="38">
+        <v>44750</v>
+      </c>
+      <c r="W96" s="39" t="s">
+        <v>1678</v>
+      </c>
+      <c r="X96" s="44">
+        <v>244.990847</v>
+      </c>
+      <c r="Y96" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>1373</v>
+      </c>
+      <c r="AB96">
+        <v>356.05650000000003</v>
+      </c>
+      <c r="AC96">
+        <v>1.1874081000000001</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C97" s="33" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E97" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F97">
+        <v>1.5276727000000001</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H97">
+        <v>11</v>
+      </c>
+      <c r="K97" s="33" t="s">
+        <v>1490</v>
+      </c>
+      <c r="L97">
+        <v>211.62418600000001</v>
+      </c>
+      <c r="M97">
+        <v>356.1284</v>
+      </c>
+      <c r="N97">
+        <v>1.5390637</v>
+      </c>
+      <c r="O97">
+        <v>14</v>
+      </c>
+      <c r="P97" t="s">
+        <v>1372</v>
+      </c>
+      <c r="V97" s="38">
+        <v>44751</v>
+      </c>
+      <c r="W97" s="39" t="s">
+        <v>1679</v>
+      </c>
+      <c r="X97" s="44">
+        <v>211.62418600000001</v>
+      </c>
+      <c r="Y97" s="17">
+        <v>14</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>1372</v>
+      </c>
+      <c r="AB97">
+        <v>356.1284</v>
+      </c>
+      <c r="AC97">
+        <v>1.5390637</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C98" s="33" t="s">
+        <v>1539</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E98" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F98">
+        <v>1.5576570000000001</v>
+      </c>
+      <c r="G98" t="s">
+        <v>1420</v>
+      </c>
+      <c r="H98">
+        <v>4</v>
+      </c>
+      <c r="K98" s="33" t="s">
+        <v>1489</v>
+      </c>
+      <c r="L98">
+        <v>46.195385000000002</v>
+      </c>
+      <c r="M98">
+        <v>356.14879999999999</v>
+      </c>
+      <c r="N98">
+        <v>1.2536700999999999</v>
+      </c>
+      <c r="O98">
+        <v>10</v>
+      </c>
+      <c r="P98" t="s">
+        <v>1371</v>
+      </c>
+      <c r="V98" s="38">
+        <v>44751</v>
+      </c>
+      <c r="W98" s="39" t="s">
+        <v>1680</v>
+      </c>
+      <c r="X98" s="44">
+        <v>46.195385000000002</v>
+      </c>
+      <c r="Y98" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>1371</v>
+      </c>
+      <c r="AB98">
+        <v>356.14879999999999</v>
+      </c>
+      <c r="AC98">
+        <v>1.2536700999999999</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C99" s="33" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D99" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E99" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F99">
+        <v>1.4473488999999999</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1421</v>
+      </c>
+      <c r="H99">
+        <v>11</v>
+      </c>
+      <c r="K99" s="33" t="s">
+        <v>1488</v>
+      </c>
+      <c r="L99">
+        <v>64.518039999999999</v>
+      </c>
+      <c r="M99">
+        <v>356.1508</v>
+      </c>
+      <c r="N99">
+        <v>1.3792546999999999</v>
+      </c>
+      <c r="O99">
+        <v>14</v>
+      </c>
+      <c r="P99" t="s">
+        <v>1370</v>
+      </c>
+      <c r="V99" s="38">
+        <v>44751</v>
+      </c>
+      <c r="W99" s="39" t="s">
+        <v>1681</v>
+      </c>
+      <c r="X99" s="44">
+        <v>64.518039999999999</v>
+      </c>
+      <c r="Y99" s="17">
+        <v>14</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>1370</v>
+      </c>
+      <c r="AB99">
+        <v>356.1508</v>
+      </c>
+      <c r="AC99">
+        <v>1.3792546999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C100" s="33" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D100" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E100" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F100">
+        <v>1.6473275999999999</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1422</v>
+      </c>
+      <c r="H100">
+        <v>13</v>
+      </c>
+      <c r="K100" s="33" t="s">
+        <v>1487</v>
+      </c>
+      <c r="L100">
+        <v>94.178218000000001</v>
+      </c>
+      <c r="M100">
+        <v>359.70460000000003</v>
+      </c>
+      <c r="N100">
+        <v>1.4673160000000001</v>
+      </c>
+      <c r="O100">
+        <v>10</v>
+      </c>
+      <c r="P100" t="s">
+        <v>1369</v>
+      </c>
+      <c r="V100" s="38">
+        <v>44790</v>
+      </c>
+      <c r="W100" s="39" t="s">
+        <v>1682</v>
+      </c>
+      <c r="X100" s="44">
+        <v>94.178218000000001</v>
+      </c>
+      <c r="Y100" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>1369</v>
+      </c>
+      <c r="AB100">
+        <v>359.70460000000003</v>
+      </c>
+      <c r="AC100">
+        <v>1.4673160000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C101" s="33" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D101" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E101" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F101">
+        <v>1.6794370999999999</v>
+      </c>
+      <c r="G101" t="s">
+        <v>1425</v>
+      </c>
+      <c r="H101">
+        <v>5</v>
+      </c>
+      <c r="K101" s="33" t="s">
+        <v>1486</v>
+      </c>
+      <c r="L101">
+        <v>70.494882000000004</v>
+      </c>
+      <c r="M101">
+        <v>359.77769999999998</v>
+      </c>
+      <c r="N101">
+        <v>1.1725570000000001</v>
+      </c>
+      <c r="O101">
+        <v>2</v>
+      </c>
+      <c r="P101" t="s">
+        <v>1368</v>
+      </c>
+      <c r="V101" s="38">
+        <v>44791</v>
+      </c>
+      <c r="W101" s="39" t="s">
+        <v>1683</v>
+      </c>
+      <c r="X101" s="44">
+        <v>70.494882000000004</v>
+      </c>
+      <c r="Y101" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z101" t="s">
+        <v>1368</v>
+      </c>
+      <c r="AB101">
+        <v>359.77769999999998</v>
+      </c>
+      <c r="AC101">
+        <v>1.1725570000000001</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C102" s="33" t="s">
+        <v>1543</v>
+      </c>
+      <c r="D102" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E102" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F102">
+        <v>1.3527285</v>
+      </c>
+      <c r="G102" t="s">
+        <v>1426</v>
+      </c>
+      <c r="H102">
+        <v>13</v>
+      </c>
+      <c r="K102" s="33" t="s">
+        <v>1485</v>
+      </c>
+      <c r="L102">
+        <v>119.245712</v>
+      </c>
+      <c r="M102">
+        <v>359.78280000000001</v>
+      </c>
+      <c r="N102">
+        <v>1.056799</v>
+      </c>
+      <c r="O102">
+        <v>5</v>
+      </c>
+      <c r="P102" t="s">
+        <v>1367</v>
+      </c>
+      <c r="V102" s="38">
+        <v>44791</v>
+      </c>
+      <c r="W102" s="39" t="s">
+        <v>1684</v>
+      </c>
+      <c r="X102" s="44">
+        <v>119.245712</v>
+      </c>
+      <c r="Y102" s="17">
+        <v>5</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>1367</v>
+      </c>
+      <c r="AB102">
+        <v>359.78280000000001</v>
+      </c>
+      <c r="AC102">
+        <v>1.056799</v>
+      </c>
+    </row>
+    <row r="103" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C103" s="33" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E103" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F103">
+        <v>1.3717834</v>
+      </c>
+      <c r="G103" t="s">
+        <v>1427</v>
+      </c>
+      <c r="H103">
+        <v>12</v>
+      </c>
+      <c r="K103" s="33" t="s">
+        <v>1484</v>
+      </c>
+      <c r="L103">
+        <v>2.033623</v>
+      </c>
+      <c r="M103">
+        <v>24.622399999999999</v>
+      </c>
+      <c r="N103">
+        <v>1.646409</v>
+      </c>
+      <c r="O103">
+        <v>4</v>
+      </c>
+      <c r="P103" t="s">
+        <v>1366</v>
+      </c>
+      <c r="U103" s="17">
+        <v>2023</v>
+      </c>
+      <c r="V103" s="38">
+        <v>45062</v>
+      </c>
+      <c r="W103" s="39" t="s">
+        <v>1685</v>
+      </c>
+      <c r="X103" s="44">
+        <v>2.033623</v>
+      </c>
+      <c r="Y103" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>1366</v>
+      </c>
+      <c r="AB103">
+        <v>24.622399999999999</v>
+      </c>
+      <c r="AC103">
+        <v>1.646409</v>
+      </c>
+    </row>
+    <row r="104" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C104" s="33" t="s">
+        <v>1545</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E104" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F104">
+        <v>1.4576948999999999</v>
+      </c>
+      <c r="G104" t="s">
+        <v>1428</v>
+      </c>
+      <c r="H104">
+        <v>16</v>
+      </c>
+      <c r="K104" s="33" t="s">
+        <v>1483</v>
+      </c>
+      <c r="L104">
+        <v>153.717107</v>
+      </c>
+      <c r="M104">
+        <v>24.638300000000001</v>
+      </c>
+      <c r="N104">
+        <v>1.0252433999999999</v>
+      </c>
+      <c r="O104">
+        <v>2</v>
+      </c>
+      <c r="P104" t="s">
+        <v>1365</v>
+      </c>
+      <c r="V104" s="38">
+        <v>45062</v>
+      </c>
+      <c r="W104" s="39" t="s">
+        <v>1686</v>
+      </c>
+      <c r="X104" s="44">
+        <v>153.717107</v>
+      </c>
+      <c r="Y104" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>1365</v>
+      </c>
+      <c r="AB104">
+        <v>24.638300000000001</v>
+      </c>
+      <c r="AC104">
+        <v>1.0252433999999999</v>
+      </c>
+    </row>
+    <row r="105" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C105" s="33" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D105" t="s">
+        <v>1039</v>
+      </c>
+      <c r="E105" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F105">
+        <v>1.4954050000000001</v>
+      </c>
+      <c r="G105" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H105">
+        <v>11</v>
+      </c>
+      <c r="K105" s="33" t="s">
+        <v>1482</v>
+      </c>
+      <c r="L105">
+        <v>153.890401</v>
+      </c>
+      <c r="M105">
+        <v>24.638400000000001</v>
+      </c>
+      <c r="N105">
+        <v>1.0252433999999999</v>
+      </c>
+      <c r="O105">
+        <v>3</v>
+      </c>
+      <c r="P105" t="s">
+        <v>1364</v>
+      </c>
+      <c r="V105" s="38">
+        <v>45062</v>
+      </c>
+      <c r="W105" s="39" t="s">
+        <v>1687</v>
+      </c>
+      <c r="X105" s="44">
+        <v>153.890401</v>
+      </c>
+      <c r="Y105" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>1364</v>
+      </c>
+      <c r="AB105">
+        <v>24.638400000000001</v>
+      </c>
+      <c r="AC105">
+        <v>1.0252433999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C106" s="33" t="s">
+        <v>1547</v>
+      </c>
+      <c r="D106" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E106" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F106">
+        <v>1.7403309</v>
+      </c>
+      <c r="G106" t="s">
+        <v>1430</v>
+      </c>
+      <c r="H106">
+        <v>6</v>
+      </c>
+      <c r="K106" s="33" t="s">
+        <v>1481</v>
+      </c>
+      <c r="L106">
+        <v>161.996329</v>
+      </c>
+      <c r="M106">
+        <v>24.7149</v>
+      </c>
+      <c r="N106">
+        <v>1.4898098</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106" t="s">
+        <v>1363</v>
+      </c>
+      <c r="V106" s="38">
+        <v>45063</v>
+      </c>
+      <c r="W106" s="39" t="s">
+        <v>1688</v>
+      </c>
+      <c r="X106" s="44">
+        <v>161.996329</v>
+      </c>
+      <c r="Y106" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>1363</v>
+      </c>
+      <c r="AB106">
+        <v>24.7149</v>
+      </c>
+      <c r="AC106">
+        <v>1.4898098</v>
+      </c>
+    </row>
+    <row r="107" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C107" s="33" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D107" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E107" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F107">
+        <v>1.8176920999999999</v>
+      </c>
+      <c r="G107" t="s">
+        <v>1431</v>
+      </c>
+      <c r="H107">
+        <v>7</v>
+      </c>
+      <c r="K107" s="33" t="s">
+        <v>1480</v>
+      </c>
+      <c r="L107">
+        <v>167.260323</v>
+      </c>
+      <c r="M107">
+        <v>24.715499999999999</v>
+      </c>
+      <c r="N107">
+        <v>1.4454194</v>
+      </c>
+      <c r="O107">
+        <v>4</v>
+      </c>
+      <c r="P107" t="s">
+        <v>1362</v>
+      </c>
+      <c r="V107" s="38">
+        <v>45063</v>
+      </c>
+      <c r="W107" s="39" t="s">
+        <v>1689</v>
+      </c>
+      <c r="X107" s="44">
+        <v>167.260323</v>
+      </c>
+      <c r="Y107" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>1362</v>
+      </c>
+      <c r="AB107">
+        <v>24.715499999999999</v>
+      </c>
+      <c r="AC107">
+        <v>1.4454194</v>
+      </c>
+    </row>
+    <row r="108" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C108" s="33" t="s">
+        <v>1549</v>
+      </c>
+      <c r="D108" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E108" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F108">
+        <v>1.8353286</v>
+      </c>
+      <c r="G108" t="s">
+        <v>1432</v>
+      </c>
+      <c r="H108">
+        <v>3</v>
+      </c>
+      <c r="K108" s="33" t="s">
+        <v>1479</v>
+      </c>
+      <c r="L108">
+        <v>186.87130500000001</v>
+      </c>
+      <c r="M108">
+        <v>24.717500000000001</v>
+      </c>
+      <c r="N108">
+        <v>1.2806987000000001</v>
+      </c>
+      <c r="O108">
+        <v>4</v>
+      </c>
+      <c r="P108" t="s">
+        <v>1361</v>
+      </c>
+      <c r="V108" s="38">
+        <v>45063</v>
+      </c>
+      <c r="W108" s="39" t="s">
+        <v>1690</v>
+      </c>
+      <c r="X108" s="44">
+        <v>186.87130500000001</v>
+      </c>
+      <c r="Y108" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>1361</v>
+      </c>
+      <c r="AB108">
+        <v>24.717500000000001</v>
+      </c>
+      <c r="AC108">
+        <v>1.2806987000000001</v>
+      </c>
+    </row>
+    <row r="109" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C109" s="33" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D109" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E109" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F109">
+        <v>1.7327911</v>
+      </c>
+      <c r="G109" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H109">
+        <v>4</v>
+      </c>
+      <c r="K109" s="33" t="s">
+        <v>1478</v>
+      </c>
+      <c r="L109">
+        <v>337.38773200000003</v>
+      </c>
+      <c r="M109">
+        <v>24.7334</v>
+      </c>
+      <c r="N109">
+        <v>1.100063</v>
+      </c>
+      <c r="O109">
+        <v>2</v>
+      </c>
+      <c r="P109" t="s">
+        <v>1360</v>
+      </c>
+      <c r="V109" s="38">
+        <v>45063</v>
+      </c>
+      <c r="W109" s="39" t="s">
+        <v>1691</v>
+      </c>
+      <c r="X109" s="44">
+        <v>337.38773200000003</v>
+      </c>
+      <c r="Y109" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>1360</v>
+      </c>
+      <c r="AB109">
+        <v>24.7334</v>
+      </c>
+      <c r="AC109">
+        <v>1.100063</v>
+      </c>
+    </row>
+    <row r="110" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C110" s="33" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D110" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E110" t="s">
+        <v>1052</v>
+      </c>
+      <c r="F110">
+        <v>1.4515434</v>
+      </c>
+      <c r="G110" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H110">
+        <v>6</v>
+      </c>
+      <c r="K110" s="33" t="s">
+        <v>1477</v>
+      </c>
+      <c r="L110">
+        <v>351.22514100000001</v>
+      </c>
+      <c r="M110">
+        <v>24.7348</v>
+      </c>
+      <c r="N110">
+        <v>1.1510309999999999</v>
+      </c>
+      <c r="O110">
+        <v>3</v>
+      </c>
+      <c r="P110" t="s">
+        <v>1359</v>
+      </c>
+      <c r="V110" s="38">
+        <v>45063</v>
+      </c>
+      <c r="W110" s="39" t="s">
+        <v>1692</v>
+      </c>
+      <c r="X110" s="44">
+        <v>351.22514100000001</v>
+      </c>
+      <c r="Y110" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>1359</v>
+      </c>
+      <c r="AB110">
+        <v>24.7348</v>
+      </c>
+      <c r="AC110">
+        <v>1.1510309999999999</v>
+      </c>
+    </row>
+    <row r="111" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C111" s="33" t="s">
+        <v>1552</v>
+      </c>
+      <c r="D111" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E111" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F111">
+        <v>1.4138792</v>
+      </c>
+      <c r="G111" t="s">
+        <v>1435</v>
+      </c>
+      <c r="H111">
+        <v>3</v>
+      </c>
+      <c r="K111" s="33" t="s">
+        <v>1476</v>
+      </c>
+      <c r="L111">
+        <v>356.613788</v>
+      </c>
+      <c r="M111">
+        <v>24.735399999999998</v>
+      </c>
+      <c r="N111">
+        <v>1.1717900000000001</v>
+      </c>
+      <c r="O111">
+        <v>8</v>
+      </c>
+      <c r="P111" t="s">
+        <v>1358</v>
+      </c>
+      <c r="V111" s="38">
+        <v>45063</v>
+      </c>
+      <c r="W111" s="39" t="s">
+        <v>1693</v>
+      </c>
+      <c r="X111" s="44">
+        <v>356.613788</v>
+      </c>
+      <c r="Y111" s="17">
+        <v>8</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>1358</v>
+      </c>
+      <c r="AB111">
+        <v>24.735399999999998</v>
+      </c>
+      <c r="AC111">
+        <v>1.1717900000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C112" s="33" t="s">
+        <v>1553</v>
+      </c>
+      <c r="D112" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E112" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F112">
+        <v>1.3697168</v>
+      </c>
+      <c r="G112" t="s">
+        <v>1436</v>
+      </c>
+      <c r="H112">
+        <v>8</v>
+      </c>
+      <c r="K112" s="33" t="s">
+        <v>1475</v>
+      </c>
+      <c r="L112">
+        <v>1.1114250000000001</v>
+      </c>
+      <c r="M112">
+        <v>24.735900000000001</v>
+      </c>
+      <c r="N112">
+        <v>1.202771</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112" t="s">
+        <v>1357</v>
+      </c>
+      <c r="V112" s="38">
+        <v>45063</v>
+      </c>
+      <c r="W112" s="39" t="s">
+        <v>1694</v>
+      </c>
+      <c r="X112" s="44">
+        <v>1.1114250000000001</v>
+      </c>
+      <c r="Y112" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>1357</v>
+      </c>
+      <c r="AB112">
+        <v>24.735900000000001</v>
+      </c>
+      <c r="AC112">
+        <v>1.202771</v>
+      </c>
+    </row>
+    <row r="113" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C113" s="33" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D113" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E113" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F113">
+        <v>1.3547161000000001</v>
+      </c>
+      <c r="G113" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H113">
+        <v>5</v>
+      </c>
+      <c r="K113" s="33" t="s">
+        <v>1474</v>
+      </c>
+      <c r="L113">
+        <v>5.6290199999999997</v>
+      </c>
+      <c r="M113">
+        <v>24.7363</v>
+      </c>
+      <c r="N113">
+        <v>1.2205336</v>
+      </c>
+      <c r="O113">
+        <v>2</v>
+      </c>
+      <c r="P113" t="s">
+        <v>1356</v>
+      </c>
+      <c r="V113" s="38">
+        <v>45063</v>
+      </c>
+      <c r="W113" s="39" t="s">
+        <v>1695</v>
+      </c>
+      <c r="X113" s="44">
+        <v>5.6290199999999997</v>
+      </c>
+      <c r="Y113" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>1356</v>
+      </c>
+      <c r="AB113">
+        <v>24.7363</v>
+      </c>
+      <c r="AC113">
+        <v>1.2205336</v>
+      </c>
+    </row>
+    <row r="114" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C114" s="33" t="s">
+        <v>1555</v>
+      </c>
+      <c r="D114" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E114" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F114">
+        <v>1.7980571000000001</v>
+      </c>
+      <c r="G114" t="s">
+        <v>1438</v>
+      </c>
+      <c r="H114">
+        <v>7</v>
+      </c>
+      <c r="K114" s="33" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L114">
+        <v>278.63028800000001</v>
+      </c>
+      <c r="M114">
+        <v>28.0944</v>
+      </c>
+      <c r="N114">
+        <v>1.2735544999999999</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114" t="s">
+        <v>1355</v>
+      </c>
+      <c r="V114" s="38">
+        <v>45100</v>
+      </c>
+      <c r="W114" s="39" t="s">
+        <v>1696</v>
+      </c>
+      <c r="X114" s="44">
+        <v>278.63028800000001</v>
+      </c>
+      <c r="Y114" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>1355</v>
+      </c>
+      <c r="AB114">
+        <v>28.0944</v>
+      </c>
+      <c r="AC114">
+        <v>1.2735544999999999</v>
+      </c>
+    </row>
+    <row r="115" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C115" s="33" t="s">
+        <v>1556</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E115" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F115">
+        <v>1.0061370000000001</v>
+      </c>
+      <c r="G115" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H115">
+        <v>17</v>
+      </c>
+      <c r="K115" s="33" t="s">
+        <v>1472</v>
+      </c>
+      <c r="L115">
+        <v>283.73881799999998</v>
+      </c>
+      <c r="M115">
+        <v>28.094999999999999</v>
+      </c>
+      <c r="N115">
+        <v>1.2452220000000001</v>
+      </c>
+      <c r="O115">
+        <v>10</v>
+      </c>
+      <c r="P115" t="s">
+        <v>1354</v>
+      </c>
+      <c r="V115" s="38">
+        <v>45100</v>
+      </c>
+      <c r="W115" s="39" t="s">
+        <v>1697</v>
+      </c>
+      <c r="X115" s="44">
+        <v>283.73881799999998</v>
+      </c>
+      <c r="Y115" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>1354</v>
+      </c>
+      <c r="AB115">
+        <v>28.094999999999999</v>
+      </c>
+      <c r="AC115">
+        <v>1.2452220000000001</v>
+      </c>
+    </row>
+    <row r="116" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C116" s="33" t="s">
+        <v>1557</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E116" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F116">
+        <v>1.0192787000000001</v>
+      </c>
+      <c r="G116" t="s">
+        <v>1440</v>
+      </c>
+      <c r="H116">
+        <v>18</v>
+      </c>
+      <c r="K116" s="33" t="s">
+        <v>1471</v>
+      </c>
+      <c r="L116">
+        <v>251.59982199999999</v>
+      </c>
+      <c r="M116">
+        <v>28.204999999999998</v>
+      </c>
+      <c r="N116">
+        <v>1.2380841</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116" t="s">
+        <v>1353</v>
+      </c>
+      <c r="V116" s="38">
+        <v>45101</v>
+      </c>
+      <c r="W116" s="39" t="s">
+        <v>1698</v>
+      </c>
+      <c r="X116" s="44">
+        <v>251.59982199999999</v>
+      </c>
+      <c r="Y116" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>1353</v>
+      </c>
+      <c r="AB116">
+        <v>28.204999999999998</v>
+      </c>
+      <c r="AC116">
+        <v>1.2380841</v>
+      </c>
+    </row>
+    <row r="117" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C117" s="33" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D117" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E117" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F117">
+        <v>1.0262792999999999</v>
+      </c>
+      <c r="G117" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H117">
+        <v>9</v>
+      </c>
+      <c r="K117" s="33" t="s">
+        <v>1470</v>
+      </c>
+      <c r="L117">
+        <v>331.75628</v>
+      </c>
+      <c r="M117">
+        <v>38.394300000000001</v>
+      </c>
+      <c r="N117">
+        <v>1.4935601999999999</v>
+      </c>
+      <c r="O117">
+        <v>7</v>
+      </c>
+      <c r="P117" t="s">
+        <v>1352</v>
+      </c>
+      <c r="V117" s="38">
+        <v>45213</v>
+      </c>
+      <c r="W117" s="39" t="s">
+        <v>1699</v>
+      </c>
+      <c r="X117" s="44">
+        <v>331.75628</v>
+      </c>
+      <c r="Y117" s="17">
+        <v>7</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>1352</v>
+      </c>
+      <c r="AB117">
+        <v>38.394300000000001</v>
+      </c>
+      <c r="AC117">
+        <v>1.4935601999999999</v>
+      </c>
+    </row>
+    <row r="118" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C118" s="33" t="s">
+        <v>1559</v>
+      </c>
+      <c r="D118" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E118" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F118">
+        <v>1.8938547999999999</v>
+      </c>
+      <c r="G118" t="s">
+        <v>1442</v>
+      </c>
+      <c r="H118">
+        <v>2</v>
+      </c>
+      <c r="K118" s="33" t="s">
+        <v>1469</v>
+      </c>
+      <c r="L118">
+        <v>330.42452500000002</v>
+      </c>
+      <c r="M118">
+        <v>38.4694</v>
+      </c>
+      <c r="N118">
+        <v>1.0239123000000001</v>
+      </c>
+      <c r="O118">
+        <v>8</v>
+      </c>
+      <c r="P118" t="s">
+        <v>1351</v>
+      </c>
+      <c r="V118" s="38">
+        <v>45214</v>
+      </c>
+      <c r="W118" s="39" t="s">
+        <v>1700</v>
+      </c>
+      <c r="X118" s="44">
+        <v>330.42452500000002</v>
+      </c>
+      <c r="Y118" s="17">
+        <v>8</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>1351</v>
+      </c>
+      <c r="AB118">
+        <v>38.4694</v>
+      </c>
+      <c r="AC118">
+        <v>1.0239123000000001</v>
+      </c>
+    </row>
+    <row r="119" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C119" s="33" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E119" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F119">
+        <v>1.7752838</v>
+      </c>
+      <c r="G119" t="s">
+        <v>1443</v>
+      </c>
+      <c r="H119">
+        <v>16</v>
+      </c>
+      <c r="K119" s="33" t="s">
+        <v>1468</v>
+      </c>
+      <c r="L119">
+        <v>43.874856999999999</v>
+      </c>
+      <c r="M119">
+        <v>42.005699999999997</v>
+      </c>
+      <c r="N119">
+        <v>1.0354473</v>
+      </c>
+      <c r="O119">
+        <v>15</v>
+      </c>
+      <c r="P119" t="s">
+        <v>1350</v>
+      </c>
+      <c r="V119" s="38">
+        <v>45253</v>
+      </c>
+      <c r="W119" s="39" t="s">
+        <v>1701</v>
+      </c>
+      <c r="X119" s="44">
+        <v>43.874856999999999</v>
+      </c>
+      <c r="Y119" s="17">
+        <v>15</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>1350</v>
+      </c>
+      <c r="AB119">
+        <v>42.005699999999997</v>
+      </c>
+      <c r="AC119">
+        <v>1.0354473</v>
+      </c>
+    </row>
+    <row r="120" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C120" s="33" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D120" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E120" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F120">
+        <v>1.1658386000000001</v>
+      </c>
+      <c r="G120" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H120">
+        <v>3</v>
+      </c>
+      <c r="K120" s="33" t="s">
+        <v>1467</v>
+      </c>
+      <c r="L120">
+        <v>72.982608999999997</v>
+      </c>
+      <c r="M120">
+        <v>42.008699999999997</v>
+      </c>
+      <c r="N120">
+        <v>1.1126522999999999</v>
+      </c>
+      <c r="O120">
+        <v>10</v>
+      </c>
+      <c r="P120" t="s">
+        <v>1349</v>
+      </c>
+      <c r="V120" s="38">
+        <v>45253</v>
+      </c>
+      <c r="W120" s="39" t="s">
+        <v>1702</v>
+      </c>
+      <c r="X120" s="44">
+        <v>72.982608999999997</v>
+      </c>
+      <c r="Y120" s="17">
+        <v>10</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>1349</v>
+      </c>
+      <c r="AB120">
+        <v>42.008699999999997</v>
+      </c>
+      <c r="AC120">
+        <v>1.1126522999999999</v>
+      </c>
+    </row>
+    <row r="121" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C121" s="33" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D121" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F121">
+        <v>1.1806829000000001</v>
+      </c>
+      <c r="G121" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H121">
+        <v>2</v>
+      </c>
+      <c r="K121" s="33" t="s">
+        <v>1466</v>
+      </c>
+      <c r="L121">
+        <v>49.554664000000002</v>
+      </c>
+      <c r="M121">
+        <v>42.081200000000003</v>
+      </c>
+      <c r="N121">
+        <v>1.3698440000000001</v>
+      </c>
+      <c r="O121">
+        <v>5</v>
+      </c>
+      <c r="P121" t="s">
+        <v>1348</v>
+      </c>
+      <c r="V121" s="38">
+        <v>45254</v>
+      </c>
+      <c r="W121" s="39" t="s">
+        <v>1703</v>
+      </c>
+      <c r="X121" s="44">
+        <v>49.554664000000002</v>
+      </c>
+      <c r="Y121" s="17">
+        <v>5</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>1348</v>
+      </c>
+      <c r="AB121">
+        <v>42.081200000000003</v>
+      </c>
+      <c r="AC121">
+        <v>1.3698440000000001</v>
+      </c>
+    </row>
+    <row r="122" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C122" s="33" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E122" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F122">
+        <v>1.2610512</v>
+      </c>
+      <c r="G122" t="s">
+        <v>1446</v>
+      </c>
+      <c r="H122">
+        <v>3</v>
+      </c>
+      <c r="K122" s="33" t="s">
+        <v>1465</v>
+      </c>
+      <c r="L122">
+        <v>237.37157099999999</v>
+      </c>
+      <c r="M122">
+        <v>45.171199999999999</v>
+      </c>
+      <c r="N122">
+        <v>1.2263607999999999</v>
+      </c>
+      <c r="O122">
+        <v>13</v>
+      </c>
+      <c r="P122" t="s">
+        <v>1347</v>
+      </c>
+      <c r="V122" s="38">
+        <v>45288</v>
+      </c>
+      <c r="W122" s="39" t="s">
+        <v>1704</v>
+      </c>
+      <c r="X122" s="44">
+        <v>237.37157099999999</v>
+      </c>
+      <c r="Y122" s="17">
+        <v>13</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>1347</v>
+      </c>
+      <c r="AB122">
+        <v>45.171199999999999</v>
+      </c>
+      <c r="AC122">
+        <v>1.2263607999999999</v>
+      </c>
+    </row>
+    <row r="123" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C123" s="33" t="s">
+        <v>1564</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E123" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F123">
+        <v>1.280257</v>
+      </c>
+      <c r="G123" t="s">
+        <v>1447</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="K123" s="33" t="s">
+        <v>1464</v>
+      </c>
+      <c r="L123">
+        <v>222.74681200000001</v>
+      </c>
+      <c r="M123">
+        <v>45.244500000000002</v>
+      </c>
+      <c r="N123">
+        <v>1.1644471999999999</v>
+      </c>
+      <c r="O123">
+        <v>3</v>
+      </c>
+      <c r="P123" t="s">
+        <v>1346</v>
+      </c>
+      <c r="V123" s="38">
+        <v>45289</v>
+      </c>
+      <c r="W123" s="39" t="s">
+        <v>1705</v>
+      </c>
+      <c r="X123" s="44">
+        <v>222.74681200000001</v>
+      </c>
+      <c r="Y123" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>1346</v>
+      </c>
+      <c r="AB123">
+        <v>45.244500000000002</v>
+      </c>
+      <c r="AC123">
+        <v>1.1644471999999999</v>
+      </c>
+    </row>
+    <row r="124" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C124" s="33" t="s">
+        <v>1565</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E124" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F124">
+        <v>1.5042374999999999</v>
+      </c>
+      <c r="G124" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H124">
+        <v>3</v>
+      </c>
+      <c r="K124" s="33" t="s">
+        <v>1322</v>
+      </c>
+      <c r="L124">
+        <v>186.97795199999999</v>
+      </c>
+      <c r="M124">
+        <v>65.969099999999997</v>
+      </c>
+      <c r="N124">
+        <v>1.0105976000000001</v>
+      </c>
+      <c r="O124">
+        <v>11</v>
+      </c>
+      <c r="P124" t="s">
+        <v>1345</v>
+      </c>
+      <c r="U124" s="17">
+        <v>2024</v>
+      </c>
+      <c r="V124" s="38">
+        <v>45520</v>
+      </c>
+      <c r="W124" s="39" t="s">
+        <v>1706</v>
+      </c>
+      <c r="X124" s="44">
+        <v>186.97795199999999</v>
+      </c>
+      <c r="Y124" s="17">
+        <v>11</v>
+      </c>
+      <c r="Z124" t="s">
+        <v>1345</v>
+      </c>
+      <c r="AB124">
+        <v>65.969099999999997</v>
+      </c>
+      <c r="AC124">
+        <v>1.0105976000000001</v>
+      </c>
+    </row>
+    <row r="125" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C125" s="33" t="s">
+        <v>1566</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F125">
+        <v>1.2899497574800001</v>
+      </c>
+      <c r="G125" t="s">
+        <v>1449</v>
+      </c>
+      <c r="H125">
+        <v>2</v>
+      </c>
+      <c r="K125" s="33" t="s">
+        <v>1318</v>
+      </c>
+      <c r="L125">
+        <v>202.819016</v>
+      </c>
+      <c r="M125">
+        <v>65.970699999999994</v>
+      </c>
+      <c r="N125">
+        <v>1.0322026</v>
+      </c>
+      <c r="O125">
+        <v>9</v>
+      </c>
+      <c r="P125" t="s">
+        <v>1344</v>
+      </c>
+      <c r="V125" s="38">
+        <v>45520</v>
+      </c>
+      <c r="W125" s="39" t="s">
+        <v>1707</v>
+      </c>
+      <c r="X125" s="44">
+        <v>202.819016</v>
+      </c>
+      <c r="Y125" s="17">
+        <v>9</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>1344</v>
+      </c>
+      <c r="AB125">
+        <v>65.970699999999994</v>
+      </c>
+      <c r="AC125">
+        <v>1.0322026</v>
+      </c>
+    </row>
+    <row r="126" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C126" s="33" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D126" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F126">
+        <v>1.2397396000000001</v>
+      </c>
+      <c r="G126" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H126">
+        <v>14</v>
+      </c>
+      <c r="K126" s="33" t="s">
+        <v>1317</v>
+      </c>
+      <c r="L126">
+        <v>245.32023899999999</v>
+      </c>
+      <c r="M126">
+        <v>65.975099999999998</v>
+      </c>
+      <c r="N126">
+        <v>1.1622017</v>
+      </c>
+      <c r="O126">
+        <v>5</v>
+      </c>
+      <c r="P126" t="s">
+        <v>1343</v>
+      </c>
+      <c r="V126" s="38">
+        <v>45520</v>
+      </c>
+      <c r="W126" s="39" t="s">
+        <v>1708</v>
+      </c>
+      <c r="X126" s="44">
+        <v>245.32023899999999</v>
+      </c>
+      <c r="Y126" s="17">
+        <v>5</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>1343</v>
+      </c>
+      <c r="AB126">
+        <v>65.975099999999998</v>
+      </c>
+      <c r="AC126">
+        <v>1.1622017</v>
+      </c>
+    </row>
+    <row r="127" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C127" s="33" t="s">
+        <v>1568</v>
+      </c>
+      <c r="D127" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F127">
+        <v>1.3277483000000001</v>
+      </c>
+      <c r="G127" t="s">
+        <v>1451</v>
+      </c>
+      <c r="H127">
+        <v>14</v>
+      </c>
+      <c r="K127" s="33" t="s">
+        <v>1320</v>
+      </c>
+      <c r="L127">
+        <v>245.354792</v>
+      </c>
+      <c r="M127">
+        <v>65.975099999999998</v>
+      </c>
+      <c r="N127">
+        <v>1.1615051000000001</v>
+      </c>
+      <c r="O127">
+        <v>8</v>
+      </c>
+      <c r="P127" t="s">
+        <v>1342</v>
+      </c>
+      <c r="V127" s="38">
+        <v>45520</v>
+      </c>
+      <c r="W127" s="39" t="s">
+        <v>1709</v>
+      </c>
+      <c r="X127" s="44">
+        <v>245.354792</v>
+      </c>
+      <c r="Y127" s="17">
+        <v>8</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>1342</v>
+      </c>
+      <c r="AB127">
+        <v>65.975099999999998</v>
+      </c>
+      <c r="AC127">
+        <v>1.1615051000000001</v>
+      </c>
+    </row>
+    <row r="128" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C128" s="33" t="s">
+        <v>1569</v>
+      </c>
+      <c r="D128" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E128" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F128">
+        <v>1.4952688999999999</v>
+      </c>
+      <c r="G128" t="s">
+        <v>1452</v>
+      </c>
+      <c r="H128">
+        <v>16</v>
+      </c>
+      <c r="K128" s="33" t="s">
+        <v>1313</v>
+      </c>
+      <c r="L128">
+        <v>211.51073600000001</v>
+      </c>
+      <c r="M128">
+        <v>66.044799999999995</v>
+      </c>
+      <c r="N128">
+        <v>1.3062362999999999</v>
+      </c>
+      <c r="O128">
+        <v>5</v>
+      </c>
+      <c r="P128" t="s">
+        <v>1341</v>
+      </c>
+      <c r="V128" s="38">
+        <v>45521</v>
+      </c>
+      <c r="W128" s="39" t="s">
+        <v>1710</v>
+      </c>
+      <c r="X128" s="44">
+        <v>211.51073600000001</v>
+      </c>
+      <c r="Y128" s="17">
+        <v>5</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>1341</v>
+      </c>
+      <c r="AB128">
+        <v>66.044799999999995</v>
+      </c>
+      <c r="AC128">
+        <v>1.3062362999999999</v>
+      </c>
+    </row>
+    <row r="129" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C129" s="33" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D129" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E129" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F129">
+        <v>1.2547427</v>
+      </c>
+      <c r="G129" t="s">
+        <v>1453</v>
+      </c>
+      <c r="H129">
+        <v>15</v>
+      </c>
+      <c r="K129" s="33" t="s">
+        <v>1307</v>
+      </c>
+      <c r="L129">
+        <v>227.96908199999999</v>
+      </c>
+      <c r="M129">
+        <v>66.046400000000006</v>
+      </c>
+      <c r="N129">
+        <v>1.2049342999999999</v>
+      </c>
+      <c r="O129">
+        <v>4</v>
+      </c>
+      <c r="P129" t="s">
+        <v>1340</v>
+      </c>
+      <c r="V129" s="38">
+        <v>45521</v>
+      </c>
+      <c r="W129" s="39" t="s">
+        <v>1711</v>
+      </c>
+      <c r="X129" s="44">
+        <v>227.96908199999999</v>
+      </c>
+      <c r="Y129" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z129" t="s">
+        <v>1340</v>
+      </c>
+      <c r="AB129">
+        <v>66.046400000000006</v>
+      </c>
+      <c r="AC129">
+        <v>1.2049342999999999</v>
+      </c>
+    </row>
+    <row r="130" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C130" s="33" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D130" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E130" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F130">
+        <v>1.1663190000000001</v>
+      </c>
+      <c r="G130" t="s">
+        <v>1451</v>
+      </c>
+      <c r="H130">
+        <v>15</v>
+      </c>
+      <c r="K130" s="33" t="s">
+        <v>1308</v>
+      </c>
+      <c r="L130">
+        <v>258.16062799999997</v>
+      </c>
+      <c r="M130">
+        <v>66.049499999999995</v>
+      </c>
+      <c r="N130">
+        <v>1.078786</v>
+      </c>
+      <c r="O130">
+        <v>5</v>
+      </c>
+      <c r="P130" t="s">
+        <v>1339</v>
+      </c>
+      <c r="V130" s="38">
+        <v>45521</v>
+      </c>
+      <c r="W130" s="39" t="s">
+        <v>1712</v>
+      </c>
+      <c r="X130" s="44">
+        <v>258.16062799999997</v>
+      </c>
+      <c r="Y130" s="17">
+        <v>5</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AB130">
+        <v>66.049499999999995</v>
+      </c>
+      <c r="AC130">
+        <v>1.078786</v>
+      </c>
+    </row>
+    <row r="131" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C131" s="33" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D131" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E131" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F131">
+        <v>1.6155265999999999</v>
+      </c>
+      <c r="G131" t="s">
+        <v>1454</v>
+      </c>
+      <c r="H131">
+        <v>8</v>
+      </c>
+      <c r="K131" s="33" t="s">
+        <v>1315</v>
+      </c>
+      <c r="L131">
+        <v>264.41854799999999</v>
+      </c>
+      <c r="M131">
+        <v>71.841499999999996</v>
+      </c>
+      <c r="N131">
+        <v>1.4519206</v>
+      </c>
+      <c r="O131">
+        <v>7</v>
+      </c>
+      <c r="P131" t="s">
+        <v>1338</v>
+      </c>
+      <c r="V131" s="38">
+        <v>45587</v>
+      </c>
+      <c r="W131" s="39" t="s">
+        <v>1713</v>
+      </c>
+      <c r="X131" s="44">
+        <v>264.41854799999999</v>
+      </c>
+      <c r="Y131" s="17">
+        <v>7</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>1338</v>
+      </c>
+      <c r="AB131">
+        <v>71.841499999999996</v>
+      </c>
+      <c r="AC131">
+        <v>1.4519206</v>
+      </c>
+    </row>
+    <row r="132" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C132" s="33" t="s">
+        <v>1573</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E132" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F132">
+        <v>1.6854796999999999</v>
+      </c>
+      <c r="G132" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H132">
+        <v>7</v>
+      </c>
+      <c r="K132" s="33" t="s">
+        <v>1321</v>
+      </c>
+      <c r="L132">
+        <v>36.420659000000001</v>
+      </c>
+      <c r="M132">
+        <v>71.854799999999997</v>
+      </c>
+      <c r="N132">
+        <v>1.004407</v>
+      </c>
+      <c r="O132">
+        <v>16</v>
+      </c>
+      <c r="P132" t="s">
+        <v>1337</v>
+      </c>
+      <c r="V132" s="38">
+        <v>45587</v>
+      </c>
+      <c r="W132" s="39" t="s">
+        <v>1714</v>
+      </c>
+      <c r="X132" s="44">
+        <v>36.420659000000001</v>
+      </c>
+      <c r="Y132" s="17">
+        <v>16</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>1337</v>
+      </c>
+      <c r="AB132">
+        <v>71.854799999999997</v>
+      </c>
+      <c r="AC132">
+        <v>1.004407</v>
+      </c>
+    </row>
+    <row r="133" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C133" s="33" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E133" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F133">
+        <v>1.1026252000000001</v>
+      </c>
+      <c r="G133" t="s">
+        <v>1456</v>
+      </c>
+      <c r="H133">
+        <v>6</v>
+      </c>
+      <c r="K133" s="33" t="s">
+        <v>1324</v>
+      </c>
+      <c r="L133">
+        <v>41.574987999999998</v>
+      </c>
+      <c r="M133">
+        <v>71.855400000000003</v>
+      </c>
+      <c r="N133">
+        <v>1.0083826</v>
+      </c>
+      <c r="O133">
+        <v>4</v>
+      </c>
+      <c r="P133" t="s">
+        <v>1336</v>
+      </c>
+      <c r="V133" s="38">
+        <v>45587</v>
+      </c>
+      <c r="W133" s="39" t="s">
+        <v>1715</v>
+      </c>
+      <c r="X133" s="44">
+        <v>41.574987999999998</v>
+      </c>
+      <c r="Y133" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>1336</v>
+      </c>
+      <c r="AB133">
+        <v>71.855400000000003</v>
+      </c>
+      <c r="AC133">
+        <v>1.0083826</v>
+      </c>
+    </row>
+    <row r="134" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C134" s="33" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E134" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F134">
+        <v>1.0357352</v>
+      </c>
+      <c r="G134" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H134">
+        <v>9</v>
+      </c>
+      <c r="K134" s="33" t="s">
+        <v>1309</v>
+      </c>
+      <c r="L134">
+        <v>66.044062999999994</v>
+      </c>
+      <c r="M134">
+        <v>71.930400000000006</v>
+      </c>
+      <c r="N134">
+        <v>1.3307070999999999</v>
+      </c>
+      <c r="O134">
+        <v>9</v>
+      </c>
+      <c r="P134" t="s">
+        <v>1335</v>
+      </c>
+      <c r="V134" s="38">
+        <v>45588</v>
+      </c>
+      <c r="W134" s="39" t="s">
+        <v>1716</v>
+      </c>
+      <c r="X134" s="44">
+        <v>66.044062999999994</v>
+      </c>
+      <c r="Y134" s="17">
+        <v>9</v>
+      </c>
+      <c r="Z134" t="s">
+        <v>1335</v>
+      </c>
+      <c r="AB134">
+        <v>71.930400000000006</v>
+      </c>
+      <c r="AC134">
+        <v>1.3307070999999999</v>
+      </c>
+    </row>
+    <row r="135" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C135" s="33" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E135" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F135">
+        <v>1.0283884999999999</v>
+      </c>
+      <c r="G135" t="s">
+        <v>1458</v>
+      </c>
+      <c r="H135">
+        <v>9</v>
+      </c>
+      <c r="K135" s="33" t="s">
+        <v>1311</v>
+      </c>
+      <c r="L135">
+        <v>230.32954699999999</v>
+      </c>
+      <c r="M135">
+        <v>71.946899999999999</v>
+      </c>
+      <c r="N135">
+        <v>1.0823919</v>
+      </c>
+      <c r="O135">
+        <v>12</v>
+      </c>
+      <c r="P135" t="s">
+        <v>1334</v>
+      </c>
+      <c r="V135" s="38">
+        <v>45588</v>
+      </c>
+      <c r="W135" s="39" t="s">
+        <v>1717</v>
+      </c>
+      <c r="X135" s="44">
+        <v>230.32954699999999</v>
+      </c>
+      <c r="Y135" s="17">
+        <v>12</v>
+      </c>
+      <c r="Z135" t="s">
+        <v>1334</v>
+      </c>
+      <c r="AB135">
+        <v>71.946899999999999</v>
+      </c>
+      <c r="AC135">
+        <v>1.0823919</v>
+      </c>
+    </row>
+    <row r="136" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C136" s="33" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E136" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F136">
+        <v>1.0366308</v>
+      </c>
+      <c r="G136" t="s">
+        <v>1459</v>
+      </c>
+      <c r="H136">
+        <v>9</v>
+      </c>
+      <c r="K136" s="33" t="s">
+        <v>1323</v>
+      </c>
+      <c r="L136">
+        <v>18.191288</v>
+      </c>
+      <c r="M136">
+        <v>74.640600000000006</v>
+      </c>
+      <c r="N136">
+        <v>1.1013264</v>
+      </c>
+      <c r="O136">
+        <v>4</v>
+      </c>
+      <c r="P136" t="s">
+        <v>1333</v>
+      </c>
+      <c r="V136" s="38">
+        <v>45619</v>
+      </c>
+      <c r="W136" s="39" t="s">
+        <v>1718</v>
+      </c>
+      <c r="X136" s="44">
+        <v>18.191288</v>
+      </c>
+      <c r="Y136" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z136" t="s">
+        <v>1333</v>
+      </c>
+      <c r="AB136">
+        <v>74.640600000000006</v>
+      </c>
+      <c r="AC136">
+        <v>1.1013264</v>
+      </c>
+    </row>
+    <row r="137" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C137" s="33" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D137" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E137" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F137">
+        <v>1.0457704000000001</v>
+      </c>
+      <c r="G137" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H137">
+        <v>4</v>
+      </c>
+      <c r="K137" s="33" t="s">
+        <v>1319</v>
+      </c>
+      <c r="L137">
+        <v>18.622608</v>
+      </c>
+      <c r="M137">
+        <v>74.640600000000006</v>
+      </c>
+      <c r="N137">
+        <v>1.0998911</v>
+      </c>
+      <c r="O137">
+        <v>4</v>
+      </c>
+      <c r="P137" t="s">
+        <v>1332</v>
+      </c>
+      <c r="V137" s="38">
+        <v>45619</v>
+      </c>
+      <c r="W137" s="39" t="s">
+        <v>1719</v>
+      </c>
+      <c r="X137" s="44">
+        <v>18.622608</v>
+      </c>
+      <c r="Y137" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>1332</v>
+      </c>
+      <c r="AB137">
+        <v>74.640600000000006</v>
+      </c>
+      <c r="AC137">
+        <v>1.0998911</v>
+      </c>
+    </row>
+    <row r="138" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C138" s="33" t="s">
+        <v>1579</v>
+      </c>
+      <c r="D138" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E138" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F138">
+        <v>1.8897699396000001</v>
+      </c>
+      <c r="G138" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H138">
+        <v>9</v>
+      </c>
+      <c r="K138" s="33" t="s">
+        <v>1314</v>
+      </c>
+      <c r="L138">
+        <v>19.046527000000001</v>
+      </c>
+      <c r="M138">
+        <v>74.640699999999995</v>
+      </c>
+      <c r="N138">
+        <v>1.0986370000000001</v>
+      </c>
+      <c r="O138">
+        <v>5</v>
+      </c>
+      <c r="P138" t="s">
+        <v>1331</v>
+      </c>
+      <c r="V138" s="38">
+        <v>45619</v>
+      </c>
+      <c r="W138" s="39" t="s">
+        <v>1720</v>
+      </c>
+      <c r="X138" s="44">
+        <v>19.046527000000001</v>
+      </c>
+      <c r="Y138" s="17">
+        <v>5</v>
+      </c>
+      <c r="Z138" t="s">
+        <v>1331</v>
+      </c>
+      <c r="AB138">
+        <v>74.640699999999995</v>
+      </c>
+      <c r="AC138">
+        <v>1.0986370000000001</v>
+      </c>
+    </row>
+    <row r="139" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C139" s="33" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D139" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E139" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F139">
+        <v>1.3443974320600001</v>
+      </c>
+      <c r="G139" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H139">
+        <v>9</v>
+      </c>
+      <c r="K139" s="33" t="s">
+        <v>1316</v>
+      </c>
+      <c r="L139">
+        <v>19.532447000000001</v>
+      </c>
+      <c r="M139">
+        <v>74.640699999999995</v>
+      </c>
+      <c r="N139">
+        <v>1.0968245999999999</v>
+      </c>
+      <c r="O139">
+        <v>4</v>
+      </c>
+      <c r="P139" t="s">
+        <v>1330</v>
+      </c>
+      <c r="V139" s="38">
+        <v>45619</v>
+      </c>
+      <c r="W139" s="39" t="s">
+        <v>1721</v>
+      </c>
+      <c r="X139" s="44">
+        <v>19.532447000000001</v>
+      </c>
+      <c r="Y139" s="17">
+        <v>4</v>
+      </c>
+      <c r="Z139" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AB139">
+        <v>74.640699999999995</v>
+      </c>
+      <c r="AC139">
+        <v>1.0968245999999999</v>
+      </c>
+    </row>
+    <row r="140" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="C140" s="33" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D140" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E140" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F140">
+        <v>1.30832837642</v>
+      </c>
+      <c r="G140" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H140">
+        <v>6</v>
+      </c>
+      <c r="K140" s="33" t="s">
+        <v>1312</v>
+      </c>
+      <c r="L140">
+        <v>11.507963999999999</v>
+      </c>
+      <c r="M140">
+        <v>74.7483</v>
+      </c>
+      <c r="N140">
+        <v>1.7299635</v>
+      </c>
+      <c r="O140">
+        <v>3</v>
+      </c>
+      <c r="P140" t="s">
+        <v>1329</v>
+      </c>
+      <c r="V140" s="38">
+        <v>45620</v>
+      </c>
+      <c r="W140" s="39" t="s">
+        <v>1722</v>
+      </c>
+      <c r="X140" s="44">
+        <v>11.507963999999999</v>
+      </c>
+      <c r="Y140" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>1329</v>
+      </c>
+      <c r="AB140">
+        <v>74.7483</v>
+      </c>
+      <c r="AC140">
+        <v>1.7299635</v>
+      </c>
+    </row>
+    <row r="141" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="K141" s="33" t="s">
+        <v>1310</v>
+      </c>
+      <c r="L141">
+        <v>13.011063999999999</v>
+      </c>
+      <c r="M141">
+        <v>74.748400000000004</v>
+      </c>
+      <c r="N141">
+        <v>1.7573915</v>
+      </c>
+      <c r="O141">
+        <v>2</v>
+      </c>
+      <c r="P141" t="s">
+        <v>1328</v>
+      </c>
+      <c r="V141" s="38">
+        <v>45620</v>
+      </c>
+      <c r="W141" s="39" t="s">
+        <v>1723</v>
+      </c>
+      <c r="X141" s="44">
+        <v>13.011063999999999</v>
+      </c>
+      <c r="Y141" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>1328</v>
+      </c>
+      <c r="AB141">
+        <v>74.748400000000004</v>
+      </c>
+      <c r="AC141">
+        <v>1.7573915</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E0F62D-2532-DA4F-A430-21FA5E7B188F}">
   <dimension ref="B3:K71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -16001,7 +25484,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82270826-5002-ED4E-9B2F-58BEBCE77D81}">
   <dimension ref="B2:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -16597,7 +26080,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65F536E7-4B42-6340-884B-D7A73BFA65B3}">
   <dimension ref="C2:J72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -17165,7 +26648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9684DBA-9A78-4440-A5A7-01DDBF82BB79}">
   <dimension ref="B3:H72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
